--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="424">
   <si>
     <t>AgentCode</t>
   </si>
@@ -726,9 +726,6 @@
     <t>City</t>
   </si>
   <si>
-    <t>PIN</t>
-  </si>
-  <si>
     <t>Landmark</t>
   </si>
   <si>
@@ -918,6 +915,9 @@
     <t>Group Channel</t>
   </si>
   <si>
+    <t>Master Individual Agent (MIA)</t>
+  </si>
+  <si>
     <t>Single</t>
   </si>
   <si>
@@ -1050,7 +1050,247 @@
     <t>Zonal Head Agentsss</t>
   </si>
   <si>
-    <t>Supervisory Agent</t>
+    <t>AG035</t>
+  </si>
+  <si>
+    <t>NomineeName</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>PercentageShare</t>
+  </si>
+  <si>
+    <t>NomineeAge</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>John Doe Jr.</t>
+  </si>
+  <si>
+    <t>Jane Doe</t>
+  </si>
+  <si>
+    <t>Mary Smith</t>
+  </si>
+  <si>
+    <t>Robert Brown</t>
+  </si>
+  <si>
+    <t>Alice Wilson</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>AccountHolderName</t>
+  </si>
+  <si>
+    <t>AccountNumber</t>
+  </si>
+  <si>
+    <t>IFSC</t>
+  </si>
+  <si>
+    <t>MICR</t>
+  </si>
+  <si>
+    <t>BankName</t>
+  </si>
+  <si>
+    <t>AccountType</t>
+  </si>
+  <si>
+    <t>ActiveSince</t>
+  </si>
+  <si>
+    <t>FactoringHouse</t>
+  </si>
+  <si>
+    <t>PreferredPaymentMode</t>
+  </si>
+  <si>
+    <t>Ramesh Kumar</t>
+  </si>
+  <si>
+    <t>HDFC0001234</t>
+  </si>
+  <si>
+    <t>HDFC Bank</t>
+  </si>
+  <si>
+    <t>Andheri East</t>
+  </si>
+  <si>
+    <t>HDFC Factoring</t>
+  </si>
+  <si>
+    <t>Suresh Patel</t>
+  </si>
+  <si>
+    <t>ICIC0005678</t>
+  </si>
+  <si>
+    <t>ICICI Bank</t>
+  </si>
+  <si>
+    <t>Ahmedabad Main</t>
+  </si>
+  <si>
+    <t>ICICI Factors</t>
+  </si>
+  <si>
+    <t>Anita Sharma</t>
+  </si>
+  <si>
+    <t>SBIN0000456</t>
+  </si>
+  <si>
+    <t>State Bank of India</t>
+  </si>
+  <si>
+    <t>Connaught Place</t>
+  </si>
+  <si>
+    <t>SBI Factoring</t>
+  </si>
+  <si>
+    <t>Vijay Rao</t>
+  </si>
+  <si>
+    <t>AXIS0000789</t>
+  </si>
+  <si>
+    <t>Axis Bank</t>
+  </si>
+  <si>
+    <t>Begumpet</t>
+  </si>
+  <si>
+    <t>Axis Factors</t>
+  </si>
+  <si>
+    <t>BankAccBranchName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>PanNumber</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>MobileNo</t>
+  </si>
+  <si>
+    <t>WorkContactNo</t>
+  </si>
+  <si>
+    <t>ResidenceContactNo</t>
+  </si>
+  <si>
+    <t>BloodGroup</t>
+  </si>
+  <si>
+    <t>BirthPlace</t>
+  </si>
+  <si>
+    <t>MartialStatus</t>
+  </si>
+  <si>
+    <t>EducationCode</t>
+  </si>
+  <si>
+    <t>EducationLevel</t>
+  </si>
+  <si>
+    <t>WorkProfile</t>
+  </si>
+  <si>
+    <t>AnnualIncome</t>
+  </si>
+  <si>
+    <t>WorkExpMonths</t>
+  </si>
+  <si>
+    <t>ABCDE1234F</t>
+  </si>
+  <si>
+    <t>ramesh.kumar@email.com</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>Sales Executive</t>
+  </si>
+  <si>
+    <t>FGHIJ5678K</t>
+  </si>
+  <si>
+    <t>suresh.patel@email.com</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Post Graduate</t>
+  </si>
+  <si>
+    <t>Branch Manager</t>
+  </si>
+  <si>
+    <t>KLMNO9012P</t>
+  </si>
+  <si>
+    <t>anita.sharma@email.com</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Relationship Officer</t>
+  </si>
+  <si>
+    <t>PQRST3456U</t>
+  </si>
+  <si>
+    <t>vijay.rao@email.com</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>MBA</t>
+  </si>
+  <si>
+    <t>Regional Lead</t>
+  </si>
+  <si>
+    <t>Pin</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1136,6 +1376,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1440,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DC6"/>
+  <dimension ref="A1:EE6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -1544,9 +1785,37 @@
     <col min="105" max="105" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="107" max="107" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="15" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="12" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="9" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="13" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1865,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>16</v>
@@ -1806,70 +2075,154 @@
         <v>234</v>
       </c>
       <c r="CI1" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="CJ1" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="CJ1" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="CK1" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="CL1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CM1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CN1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CP1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="CP1" s="3" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="CQ1" s="3" t="s">
+      <c r="CR1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CS1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="CS1" s="3" t="s">
+      <c r="CT1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="CT1" s="3" t="s">
+      <c r="CU1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="CU1" s="3" t="s">
+      <c r="CV1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="CV1" s="3" t="s">
+      <c r="CW1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CW1" s="3" t="s">
+      <c r="CX1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="CX1" s="3" t="s">
+      <c r="CY1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="CY1" s="3" t="s">
+      <c r="CZ1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="CZ1" s="3" t="s">
+      <c r="DA1" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="DA1" s="3" t="s">
+      <c r="DB1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="DB1" s="3" t="s">
+      <c r="DC1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="DC1" s="3" t="s">
-        <v>270</v>
+      <c r="DD1" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="DE1" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="DF1" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="DG1" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="DH1" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="DJ1" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="DK1" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="DL1" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="DM1" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="DN1" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="DO1" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="DP1" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="DQ1" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="DR1" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="DS1" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="DT1" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DU1" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="DV1" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="DW1" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="DX1" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="DY1" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="DZ1" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="EA1" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="EB1" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="EC1" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="ED1" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="EE1" s="3" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="2" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>335</v>
       </c>
@@ -1891,6 +2244,9 @@
       <c r="G2" t="s">
         <v>106</v>
       </c>
+      <c r="I2" s="2">
+        <v>33270</v>
+      </c>
       <c r="J2" t="s">
         <v>108</v>
       </c>
@@ -1913,7 +2269,7 @@
         <v>130</v>
       </c>
       <c r="Q2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R2" s="2">
         <v>40605</v>
@@ -1928,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W2">
         <v>123456789012</v>
@@ -2105,46 +2461,46 @@
         <v>135</v>
       </c>
       <c r="CE2" t="s">
+        <v>236</v>
+      </c>
+      <c r="CF2" t="s">
         <v>237</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>238</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>239</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>240</v>
       </c>
       <c r="CI2">
         <v>23728283</v>
       </c>
       <c r="CJ2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CK2" t="s">
-        <v>343</v>
+        <v>298</v>
       </c>
       <c r="CL2" t="s">
+        <v>270</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>275</v>
+      </c>
+      <c r="CN2" t="s">
         <v>271</v>
       </c>
-      <c r="CM2" t="s">
-        <v>276</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>272</v>
-      </c>
       <c r="CO2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="CP2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="CQ2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="CR2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="CS2" t="s">
         <v>299</v>
@@ -2156,7 +2512,7 @@
         <v>309</v>
       </c>
       <c r="CV2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="CW2" t="s">
         <v>326</v>
@@ -2179,8 +2535,92 @@
       <c r="DC2" t="s">
         <v>319</v>
       </c>
+      <c r="DD2" t="s">
+        <v>351</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>350</v>
+      </c>
+      <c r="DF2">
+        <v>100</v>
+      </c>
+      <c r="DG2">
+        <v>12</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>366</v>
+      </c>
+      <c r="DI2">
+        <v>123456789012</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>367</v>
+      </c>
+      <c r="DK2">
+        <v>400240001</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>368</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>369</v>
+      </c>
+      <c r="DN2">
+        <v>1</v>
+      </c>
+      <c r="DO2" s="6">
+        <v>44941</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>370</v>
+      </c>
+      <c r="DQ2">
+        <v>1</v>
+      </c>
+      <c r="DR2" s="6">
+        <v>33005</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>401</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>402</v>
+      </c>
+      <c r="DU2">
+        <v>9876543210</v>
+      </c>
+      <c r="DV2">
+        <v>2240001234</v>
+      </c>
+      <c r="DW2">
+        <v>2240005678</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>403</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>236</v>
+      </c>
+      <c r="DZ2">
+        <v>1</v>
+      </c>
+      <c r="EA2">
+        <v>3</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>404</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>405</v>
+      </c>
+      <c r="ED2">
+        <v>450000</v>
+      </c>
+      <c r="EE2">
+        <v>72</v>
+      </c>
     </row>
-    <row r="3" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>336</v>
       </c>
@@ -2227,7 +2667,7 @@
         <v>131</v>
       </c>
       <c r="Q3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R3" s="2">
         <v>42594</v>
@@ -2242,7 +2682,10 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>244</v>
+        <v>243</v>
+      </c>
+      <c r="W3">
+        <v>123456789012</v>
       </c>
       <c r="X3" t="s">
         <v>138</v>
@@ -2416,46 +2859,46 @@
         <v>135</v>
       </c>
       <c r="CE3" t="s">
+        <v>236</v>
+      </c>
+      <c r="CF3" t="s">
         <v>237</v>
       </c>
-      <c r="CF3" t="s">
+      <c r="CG3" t="s">
         <v>238</v>
       </c>
-      <c r="CG3" t="s">
+      <c r="CH3" t="s">
         <v>239</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>240</v>
       </c>
       <c r="CI3">
         <v>23728283</v>
       </c>
       <c r="CJ3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CK3" t="s">
         <v>339</v>
       </c>
       <c r="CL3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="CM3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="CN3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="CO3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CP3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="CQ3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CR3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="CS3" t="s">
         <v>300</v>
@@ -2490,10 +2933,94 @@
       <c r="DC3" t="s">
         <v>320</v>
       </c>
+      <c r="DD3" t="s">
+        <v>352</v>
+      </c>
+      <c r="DE3" t="s">
+        <v>349</v>
+      </c>
+      <c r="DF3">
+        <v>10</v>
+      </c>
+      <c r="DG3">
+        <v>45</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>371</v>
+      </c>
+      <c r="DI3">
+        <v>987654321098</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DK3">
+        <v>380002002</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>373</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>374</v>
+      </c>
+      <c r="DN3">
+        <v>1</v>
+      </c>
+      <c r="DO3" s="6">
+        <v>44875</v>
+      </c>
+      <c r="DP3" t="s">
+        <v>375</v>
+      </c>
+      <c r="DQ3">
+        <v>1</v>
+      </c>
+      <c r="DR3" s="6">
+        <v>33005</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>401</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>402</v>
+      </c>
+      <c r="DU3">
+        <v>9876543210</v>
+      </c>
+      <c r="DV3">
+        <v>2240001234</v>
+      </c>
+      <c r="DW3">
+        <v>2240005678</v>
+      </c>
+      <c r="DX3" t="s">
+        <v>403</v>
+      </c>
+      <c r="DY3" t="s">
+        <v>236</v>
+      </c>
+      <c r="DZ3">
+        <v>1</v>
+      </c>
+      <c r="EA3">
+        <v>3</v>
+      </c>
+      <c r="EB3" t="s">
+        <v>404</v>
+      </c>
+      <c r="EC3" t="s">
+        <v>405</v>
+      </c>
+      <c r="ED3">
+        <v>450000</v>
+      </c>
+      <c r="EE3">
+        <v>72</v>
+      </c>
     </row>
-    <row r="4" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
         <v>83</v>
@@ -2538,7 +3065,7 @@
         <v>132</v>
       </c>
       <c r="Q4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R4" s="2">
         <v>38373</v>
@@ -2553,7 +3080,10 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="W4">
+        <v>123456789012</v>
       </c>
       <c r="X4" t="s">
         <v>139</v>
@@ -2727,46 +3257,46 @@
         <v>135</v>
       </c>
       <c r="CE4" t="s">
+        <v>236</v>
+      </c>
+      <c r="CF4" t="s">
         <v>237</v>
       </c>
-      <c r="CF4" t="s">
+      <c r="CG4" t="s">
         <v>238</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CH4" t="s">
         <v>239</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>240</v>
       </c>
       <c r="CI4">
         <v>23728283</v>
       </c>
       <c r="CJ4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CK4" t="s">
         <v>340</v>
       </c>
       <c r="CL4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="CM4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="CN4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="CO4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="CP4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="CQ4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="CR4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="CS4" t="s">
         <v>301</v>
@@ -2801,8 +3331,92 @@
       <c r="DC4" t="s">
         <v>320</v>
       </c>
+      <c r="DD4" t="s">
+        <v>353</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>348</v>
+      </c>
+      <c r="DF4">
+        <v>59</v>
+      </c>
+      <c r="DG4">
+        <v>23</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>371</v>
+      </c>
+      <c r="DI4">
+        <v>987654321098</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>372</v>
+      </c>
+      <c r="DK4">
+        <v>380002002</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>373</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>374</v>
+      </c>
+      <c r="DN4">
+        <v>1</v>
+      </c>
+      <c r="DO4" s="6">
+        <v>44875</v>
+      </c>
+      <c r="DP4" t="s">
+        <v>375</v>
+      </c>
+      <c r="DQ4">
+        <v>1</v>
+      </c>
+      <c r="DR4" s="6">
+        <v>31313</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>406</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>407</v>
+      </c>
+      <c r="DU4">
+        <v>9898989898</v>
+      </c>
+      <c r="DV4">
+        <v>7930001234</v>
+      </c>
+      <c r="DW4">
+        <v>7930005678</v>
+      </c>
+      <c r="DX4" t="s">
+        <v>408</v>
+      </c>
+      <c r="DY4" t="s">
+        <v>409</v>
+      </c>
+      <c r="DZ4">
+        <v>2</v>
+      </c>
+      <c r="EA4">
+        <v>4</v>
+      </c>
+      <c r="EB4" t="s">
+        <v>410</v>
+      </c>
+      <c r="EC4" t="s">
+        <v>411</v>
+      </c>
+      <c r="ED4">
+        <v>850000</v>
+      </c>
+      <c r="EE4">
+        <v>180</v>
+      </c>
     </row>
-    <row r="5" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>337</v>
       </c>
@@ -2849,7 +3463,7 @@
         <v>133</v>
       </c>
       <c r="Q5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R5" s="2">
         <v>43084</v>
@@ -2864,7 +3478,10 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>246</v>
+        <v>245</v>
+      </c>
+      <c r="W5">
+        <v>123456789012</v>
       </c>
       <c r="X5" t="s">
         <v>140</v>
@@ -3038,46 +3655,46 @@
         <v>135</v>
       </c>
       <c r="CE5" t="s">
+        <v>236</v>
+      </c>
+      <c r="CF5" t="s">
         <v>237</v>
       </c>
-      <c r="CF5" t="s">
+      <c r="CG5" t="s">
         <v>238</v>
       </c>
-      <c r="CG5" t="s">
+      <c r="CH5" t="s">
         <v>239</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>240</v>
       </c>
       <c r="CI5">
         <v>23728283</v>
       </c>
       <c r="CJ5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CK5" t="s">
         <v>341</v>
       </c>
       <c r="CL5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="CM5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="CN5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="CO5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="CP5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="CQ5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="CR5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="CS5" t="s">
         <v>302</v>
@@ -3112,8 +3729,92 @@
       <c r="DC5" t="s">
         <v>320</v>
       </c>
+      <c r="DD5" t="s">
+        <v>354</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>348</v>
+      </c>
+      <c r="DF5">
+        <v>45</v>
+      </c>
+      <c r="DG5">
+        <v>67</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>376</v>
+      </c>
+      <c r="DI5">
+        <v>456789123456</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>377</v>
+      </c>
+      <c r="DK5">
+        <v>110002003</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>378</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>379</v>
+      </c>
+      <c r="DN5">
+        <v>1</v>
+      </c>
+      <c r="DO5" s="6">
+        <v>44352</v>
+      </c>
+      <c r="DP5" t="s">
+        <v>380</v>
+      </c>
+      <c r="DQ5">
+        <v>1</v>
+      </c>
+      <c r="DR5" s="6">
+        <v>33644</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>412</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>413</v>
+      </c>
+      <c r="DU5">
+        <v>9123456789</v>
+      </c>
+      <c r="DV5">
+        <v>1145001234</v>
+      </c>
+      <c r="DW5">
+        <v>1145007890</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>414</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>415</v>
+      </c>
+      <c r="DZ5">
+        <v>1</v>
+      </c>
+      <c r="EA5">
+        <v>3</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>404</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>416</v>
+      </c>
+      <c r="ED5">
+        <v>520000</v>
+      </c>
+      <c r="EE5">
+        <v>60</v>
+      </c>
     </row>
-    <row r="6" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>338</v>
       </c>
@@ -3160,7 +3861,7 @@
         <v>134</v>
       </c>
       <c r="Q6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R6" s="2">
         <v>40686</v>
@@ -3175,7 +3876,10 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>247</v>
+        <v>246</v>
+      </c>
+      <c r="W6">
+        <v>123456789012</v>
       </c>
       <c r="X6" t="s">
         <v>141</v>
@@ -3349,46 +4053,46 @@
         <v>135</v>
       </c>
       <c r="CE6" t="s">
+        <v>236</v>
+      </c>
+      <c r="CF6" t="s">
         <v>237</v>
       </c>
-      <c r="CF6" t="s">
+      <c r="CG6" t="s">
         <v>238</v>
       </c>
-      <c r="CG6" t="s">
+      <c r="CH6" t="s">
         <v>239</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>240</v>
       </c>
       <c r="CI6">
         <v>23728283</v>
       </c>
       <c r="CJ6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CK6" t="s">
         <v>342</v>
       </c>
       <c r="CL6" t="s">
+        <v>270</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>276</v>
+      </c>
+      <c r="CN6" t="s">
         <v>271</v>
       </c>
-      <c r="CM6" t="s">
-        <v>277</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>272</v>
-      </c>
       <c r="CO6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CP6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="CQ6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="CR6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="CS6" t="s">
         <v>303</v>
@@ -3422,6 +4126,90 @@
       </c>
       <c r="DC6" t="s">
         <v>319</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>355</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>356</v>
+      </c>
+      <c r="DF6">
+        <v>36</v>
+      </c>
+      <c r="DG6">
+        <v>32</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>381</v>
+      </c>
+      <c r="DI6">
+        <v>321654987654</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>382</v>
+      </c>
+      <c r="DK6">
+        <v>500001004</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>383</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>384</v>
+      </c>
+      <c r="DN6">
+        <v>2</v>
+      </c>
+      <c r="DO6" s="6">
+        <v>43910</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>385</v>
+      </c>
+      <c r="DQ6">
+        <v>2</v>
+      </c>
+      <c r="DR6" s="6">
+        <v>32342</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>417</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>418</v>
+      </c>
+      <c r="DU6">
+        <v>9988776655</v>
+      </c>
+      <c r="DV6">
+        <v>4060001234</v>
+      </c>
+      <c r="DW6">
+        <v>4060004321</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>419</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>420</v>
+      </c>
+      <c r="DZ6">
+        <v>2</v>
+      </c>
+      <c r="EA6">
+        <v>5</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>421</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>422</v>
+      </c>
+      <c r="ED6">
+        <v>1200000</v>
+      </c>
+      <c r="EE6">
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HMS2\ExcelProcess\ExcelProcess\FileProcess\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HMS2\Jobs\Tasks\FileProcess\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -627,9 +627,6 @@
     <t>ST5</t>
   </si>
   <si>
-    <t>GroupA</t>
-  </si>
-  <si>
     <t>IFS1</t>
   </si>
   <si>
@@ -663,9 +660,6 @@
     <t>AM5</t>
   </si>
   <si>
-    <t>Vertical1</t>
-  </si>
-  <si>
     <t>BR1</t>
   </si>
   <si>
@@ -711,9 +705,6 @@
     <t>LIC005</t>
   </si>
   <si>
-    <t>Type1</t>
-  </si>
-  <si>
     <t>AddressLine1</t>
   </si>
   <si>
@@ -1026,18 +1017,6 @@
     <t>Chat Support</t>
   </si>
   <si>
-    <t>AG033</t>
-  </si>
-  <si>
-    <t>AG034</t>
-  </si>
-  <si>
-    <t>AG036</t>
-  </si>
-  <si>
-    <t>AG037</t>
-  </si>
-  <si>
     <t>xd</t>
   </si>
   <si>
@@ -1050,9 +1029,6 @@
     <t>Zonal Head Agentsss</t>
   </si>
   <si>
-    <t>AG035</t>
-  </si>
-  <si>
     <t>NomineeName</t>
   </si>
   <si>
@@ -1291,6 +1267,30 @@
   </si>
   <si>
     <t>Pin</t>
+  </si>
+  <si>
+    <t>AG041</t>
+  </si>
+  <si>
+    <t>AG042</t>
+  </si>
+  <si>
+    <t>AG043</t>
+  </si>
+  <si>
+    <t>AG044</t>
+  </si>
+  <si>
+    <t>AG045</t>
+  </si>
+  <si>
+    <t>Pharmaceutical</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>General</t>
   </si>
 </sst>
 </file>
@@ -1705,7 +1705,7 @@
     <col min="20" max="20" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.6328125" bestFit="1" customWidth="1"/>
@@ -1776,6 +1776,7 @@
     <col min="94" max="94" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="95" max="95" width="14.36328125" bestFit="1" customWidth="1"/>
     <col min="96" max="96" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="98" max="98" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="100" max="100" width="19.08984375" customWidth="1"/>
     <col min="101" max="101" width="19.08984375" bestFit="1" customWidth="1"/>
@@ -1865,7 +1866,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>16</v>
@@ -2063,168 +2064,168 @@
         <v>80</v>
       </c>
       <c r="CE1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="CF1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="CG1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="CH1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CI1" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="CJ1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="CG1" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CH1" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="CI1" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="CJ1" s="3" t="s">
-        <v>235</v>
-      </c>
       <c r="CK1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="CL1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="CM1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="CN1" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="CL1" s="3" t="s">
+      <c r="CO1" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="CM1" s="3" t="s">
+      <c r="CP1" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="CN1" s="3" t="s">
+      <c r="CQ1" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="CO1" s="3" t="s">
+      <c r="CR1" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="CP1" s="3" t="s">
+      <c r="CS1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="CQ1" s="3" t="s">
+      <c r="CT1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="CR1" s="3" t="s">
+      <c r="CU1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="CS1" s="3" t="s">
+      <c r="CV1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="CT1" s="3" t="s">
+      <c r="CW1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="CU1" s="3" t="s">
+      <c r="CX1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="CV1" s="3" t="s">
+      <c r="CY1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="CW1" s="3" t="s">
+      <c r="CZ1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="CX1" s="3" t="s">
+      <c r="DA1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="CY1" s="3" t="s">
+      <c r="DB1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="CZ1" s="3" t="s">
+      <c r="DC1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="DA1" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="DB1" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="DC1" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="DD1" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="DH1" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="DJ1" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="DK1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="DL1" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="DM1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="DN1" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="DO1" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="DP1" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="DQ1" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="DI1" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="DJ1" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="DK1" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="DL1" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="DM1" s="3" t="s">
+      <c r="DR1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="DS1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DT1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DU1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DV1" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="DW1" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="DX1" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="DY1" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="DN1" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="DO1" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="DP1" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="DQ1" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="DR1" s="3" t="s">
+      <c r="DZ1" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="DS1" s="3" t="s">
+      <c r="EA1" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="DT1" s="3" t="s">
+      <c r="EB1" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="DU1" s="3" t="s">
+      <c r="EC1" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="DV1" s="3" t="s">
+      <c r="ED1" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="DW1" s="3" t="s">
+      <c r="EE1" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="DX1" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="DY1" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="DZ1" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="EA1" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="EB1" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="EC1" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="ED1" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="EE1" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
@@ -2269,7 +2270,7 @@
         <v>130</v>
       </c>
       <c r="Q2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="R2" s="2">
         <v>40605</v>
@@ -2284,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="W2">
         <v>123456789012</v>
@@ -2371,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="BA2" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB2" t="s">
         <v>202</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>203</v>
       </c>
       <c r="BC2" t="b">
         <v>1</v>
@@ -2383,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="BE2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BF2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BG2" s="2">
         <v>42203</v>
       </c>
       <c r="BH2" t="s">
-        <v>214</v>
+        <v>421</v>
       </c>
       <c r="BI2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="BJ2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="BK2" s="2">
         <v>44715</v>
@@ -2446,10 +2447,10 @@
         <v>45424</v>
       </c>
       <c r="BZ2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="CA2" t="s">
-        <v>230</v>
+        <v>422</v>
       </c>
       <c r="CB2" s="2">
         <v>44001</v>
@@ -2461,85 +2462,85 @@
         <v>135</v>
       </c>
       <c r="CE2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>234</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>235</v>
+      </c>
+      <c r="CH2" t="s">
         <v>236</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>237</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>238</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>239</v>
       </c>
       <c r="CI2">
         <v>23728283</v>
       </c>
       <c r="CJ2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="CL2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="CM2" t="s">
+        <v>272</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>268</v>
+      </c>
+      <c r="CO2" t="s">
         <v>275</v>
       </c>
-      <c r="CN2" t="s">
-        <v>271</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>278</v>
-      </c>
       <c r="CP2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="CQ2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="CR2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="CS2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="CT2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="CU2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="CV2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="CW2" t="s">
+        <v>323</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>320</v>
+      </c>
+      <c r="CY2" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="CX2" t="s">
-        <v>323</v>
-      </c>
-      <c r="CY2" s="5" t="s">
+      <c r="CZ2" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="CZ2" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="DA2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="DB2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="DC2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="DD2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="DE2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="DF2">
         <v>100</v>
@@ -2548,22 +2549,22 @@
         <v>12</v>
       </c>
       <c r="DH2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="DI2">
         <v>123456789012</v>
       </c>
       <c r="DJ2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="DK2">
         <v>400240001</v>
       </c>
       <c r="DL2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="DM2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="DN2">
         <v>1</v>
@@ -2572,7 +2573,7 @@
         <v>44941</v>
       </c>
       <c r="DP2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="DQ2">
         <v>1</v>
@@ -2581,10 +2582,10 @@
         <v>33005</v>
       </c>
       <c r="DS2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="DT2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="DU2">
         <v>9876543210</v>
@@ -2596,10 +2597,10 @@
         <v>2240005678</v>
       </c>
       <c r="DX2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="DY2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="DZ2">
         <v>1</v>
@@ -2608,10 +2609,10 @@
         <v>3</v>
       </c>
       <c r="EB2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="EC2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="ED2">
         <v>450000</v>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="3" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>417</v>
       </c>
       <c r="B3" t="s">
         <v>82</v>
@@ -2667,7 +2668,7 @@
         <v>131</v>
       </c>
       <c r="Q3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="R3" s="2">
         <v>42594</v>
@@ -2682,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="W3">
         <v>123456789012</v>
@@ -2769,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="BA3" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB3" t="s">
         <v>202</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>203</v>
       </c>
       <c r="BC3" t="b">
         <v>1</v>
@@ -2781,22 +2782,22 @@
         <v>0</v>
       </c>
       <c r="BE3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BF3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BG3" s="2">
         <v>43907</v>
       </c>
       <c r="BH3" t="s">
+        <v>421</v>
+      </c>
+      <c r="BI3" t="s">
         <v>214</v>
       </c>
-      <c r="BI3" t="s">
-        <v>216</v>
-      </c>
       <c r="BJ3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BK3" s="2">
         <v>43783</v>
@@ -2844,10 +2845,10 @@
         <v>45700</v>
       </c>
       <c r="BZ3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="CA3" t="s">
-        <v>230</v>
+        <v>422</v>
       </c>
       <c r="CB3" s="2">
         <v>43851</v>
@@ -2859,85 +2860,85 @@
         <v>135</v>
       </c>
       <c r="CE3" t="s">
+        <v>233</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>234</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>235</v>
+      </c>
+      <c r="CH3" t="s">
         <v>236</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>237</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>238</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>239</v>
       </c>
       <c r="CI3">
         <v>23728283</v>
       </c>
       <c r="CJ3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="CL3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="CM3" t="s">
+        <v>273</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>269</v>
+      </c>
+      <c r="CO3" t="s">
         <v>276</v>
       </c>
-      <c r="CN3" t="s">
-        <v>272</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>279</v>
-      </c>
       <c r="CP3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="CQ3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="CR3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="CS3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="CT3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="CU3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="CV3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="CW3" t="s">
+        <v>324</v>
+      </c>
+      <c r="CX3" t="s">
+        <v>321</v>
+      </c>
+      <c r="CY3" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="CX3" t="s">
-        <v>324</v>
-      </c>
-      <c r="CY3" s="5" t="s">
+      <c r="CZ3" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="CZ3" s="5" t="s">
-        <v>333</v>
-      </c>
       <c r="DA3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="DB3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="DC3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="DD3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="DE3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="DF3">
         <v>10</v>
@@ -2946,22 +2947,22 @@
         <v>45</v>
       </c>
       <c r="DH3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="DI3">
         <v>987654321098</v>
       </c>
       <c r="DJ3" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="DK3">
         <v>380002002</v>
       </c>
       <c r="DL3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="DM3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="DN3">
         <v>1</v>
@@ -2970,7 +2971,7 @@
         <v>44875</v>
       </c>
       <c r="DP3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="DQ3">
         <v>1</v>
@@ -2979,10 +2980,10 @@
         <v>33005</v>
       </c>
       <c r="DS3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="DT3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="DU3">
         <v>9876543210</v>
@@ -2994,10 +2995,10 @@
         <v>2240005678</v>
       </c>
       <c r="DX3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="DY3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="DZ3">
         <v>1</v>
@@ -3006,10 +3007,10 @@
         <v>3</v>
       </c>
       <c r="EB3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="EC3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="ED3">
         <v>450000</v>
@@ -3020,7 +3021,7 @@
     </row>
     <row r="4" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>418</v>
       </c>
       <c r="B4" t="s">
         <v>83</v>
@@ -3065,7 +3066,7 @@
         <v>132</v>
       </c>
       <c r="Q4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="R4" s="2">
         <v>38373</v>
@@ -3080,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="W4">
         <v>123456789012</v>
@@ -3167,10 +3168,10 @@
         <v>0</v>
       </c>
       <c r="BA4" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB4" t="s">
         <v>202</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>203</v>
       </c>
       <c r="BC4" t="b">
         <v>1</v>
@@ -3179,22 +3180,22 @@
         <v>0</v>
       </c>
       <c r="BE4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BF4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BG4" s="2">
         <v>45886</v>
       </c>
       <c r="BH4" t="s">
-        <v>214</v>
+        <v>421</v>
       </c>
       <c r="BI4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BJ4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BK4" s="2">
         <v>44950</v>
@@ -3242,10 +3243,10 @@
         <v>45805</v>
       </c>
       <c r="BZ4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="CA4" t="s">
-        <v>230</v>
+        <v>422</v>
       </c>
       <c r="CB4" s="2">
         <v>43525</v>
@@ -3257,85 +3258,85 @@
         <v>135</v>
       </c>
       <c r="CE4" t="s">
+        <v>233</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>234</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>235</v>
+      </c>
+      <c r="CH4" t="s">
         <v>236</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>237</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>238</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>239</v>
       </c>
       <c r="CI4">
         <v>23728283</v>
       </c>
       <c r="CJ4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK4" t="s">
+        <v>333</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>267</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>274</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>270</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>277</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>282</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>287</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>292</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>298</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>303</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>308</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>312</v>
+      </c>
+      <c r="CW4" t="s">
+        <v>325</v>
+      </c>
+      <c r="CX4" t="s">
+        <v>322</v>
+      </c>
+      <c r="CY4" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="CZ4" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>315</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>318</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>317</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>345</v>
+      </c>
+      <c r="DE4" t="s">
         <v>340</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>270</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>277</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>273</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>280</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>285</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>290</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>295</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>301</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>306</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>311</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>315</v>
-      </c>
-      <c r="CW4" t="s">
-        <v>328</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>325</v>
-      </c>
-      <c r="CY4" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="CZ4" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>318</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>321</v>
-      </c>
-      <c r="DC4" t="s">
-        <v>320</v>
-      </c>
-      <c r="DD4" t="s">
-        <v>353</v>
-      </c>
-      <c r="DE4" t="s">
-        <v>348</v>
       </c>
       <c r="DF4">
         <v>59</v>
@@ -3344,22 +3345,22 @@
         <v>23</v>
       </c>
       <c r="DH4" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="DI4">
         <v>987654321098</v>
       </c>
       <c r="DJ4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="DK4">
         <v>380002002</v>
       </c>
       <c r="DL4" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="DM4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="DN4">
         <v>1</v>
@@ -3368,7 +3369,7 @@
         <v>44875</v>
       </c>
       <c r="DP4" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="DQ4">
         <v>1</v>
@@ -3377,10 +3378,10 @@
         <v>31313</v>
       </c>
       <c r="DS4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="DT4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="DU4">
         <v>9898989898</v>
@@ -3392,10 +3393,10 @@
         <v>7930005678</v>
       </c>
       <c r="DX4" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="DY4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="DZ4">
         <v>2</v>
@@ -3404,10 +3405,10 @@
         <v>4</v>
       </c>
       <c r="EB4" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="EC4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="ED4">
         <v>850000</v>
@@ -3418,7 +3419,7 @@
     </row>
     <row r="5" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>337</v>
+        <v>419</v>
       </c>
       <c r="B5" t="s">
         <v>84</v>
@@ -3463,7 +3464,7 @@
         <v>133</v>
       </c>
       <c r="Q5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="R5" s="2">
         <v>43084</v>
@@ -3478,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="W5">
         <v>123456789012</v>
@@ -3565,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="BA5" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB5" t="s">
         <v>202</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>203</v>
       </c>
       <c r="BC5" t="b">
         <v>1</v>
@@ -3577,22 +3578,22 @@
         <v>0</v>
       </c>
       <c r="BE5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BF5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BG5" s="2">
         <v>45439</v>
       </c>
       <c r="BH5" t="s">
-        <v>214</v>
+        <v>421</v>
       </c>
       <c r="BI5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BJ5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BK5" s="2">
         <v>45091</v>
@@ -3640,10 +3641,10 @@
         <v>45800</v>
       </c>
       <c r="BZ5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="CA5" t="s">
-        <v>230</v>
+        <v>422</v>
       </c>
       <c r="CB5" s="2">
         <v>43885</v>
@@ -3655,85 +3656,85 @@
         <v>135</v>
       </c>
       <c r="CE5" t="s">
+        <v>233</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>234</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>235</v>
+      </c>
+      <c r="CH5" t="s">
         <v>236</v>
-      </c>
-      <c r="CF5" t="s">
-        <v>237</v>
-      </c>
-      <c r="CG5" t="s">
-        <v>238</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>239</v>
       </c>
       <c r="CI5">
         <v>23728283</v>
       </c>
       <c r="CJ5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK5" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="CL5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="CM5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="CN5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="CO5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="CP5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="CQ5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="CR5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="CS5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="CT5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="CU5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="CV5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="CW5" t="s">
+        <v>323</v>
+      </c>
+      <c r="CX5" t="s">
+        <v>320</v>
+      </c>
+      <c r="CY5" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="CX5" t="s">
-        <v>323</v>
-      </c>
-      <c r="CY5" s="5" t="s">
+      <c r="CZ5" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="CZ5" s="5" t="s">
-        <v>332</v>
-      </c>
       <c r="DA5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="DB5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="DC5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="DD5" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="DE5" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="DF5">
         <v>45</v>
@@ -3742,22 +3743,22 @@
         <v>67</v>
       </c>
       <c r="DH5" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="DI5">
         <v>456789123456</v>
       </c>
       <c r="DJ5" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="DK5">
         <v>110002003</v>
       </c>
       <c r="DL5" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="DM5" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="DN5">
         <v>1</v>
@@ -3766,7 +3767,7 @@
         <v>44352</v>
       </c>
       <c r="DP5" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="DQ5">
         <v>1</v>
@@ -3775,10 +3776,10 @@
         <v>33644</v>
       </c>
       <c r="DS5" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="DT5" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="DU5">
         <v>9123456789</v>
@@ -3790,10 +3791,10 @@
         <v>1145007890</v>
       </c>
       <c r="DX5" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="DY5" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="DZ5">
         <v>1</v>
@@ -3802,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="EB5" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="EC5" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="ED5">
         <v>520000</v>
@@ -3816,7 +3817,7 @@
     </row>
     <row r="6" spans="1:135" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>420</v>
       </c>
       <c r="B6" t="s">
         <v>85</v>
@@ -3861,7 +3862,7 @@
         <v>134</v>
       </c>
       <c r="Q6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="R6" s="2">
         <v>40686</v>
@@ -3876,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="W6">
         <v>123456789012</v>
@@ -3963,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="BA6" t="s">
+        <v>423</v>
+      </c>
+      <c r="BB6" t="s">
         <v>202</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>203</v>
       </c>
       <c r="BC6" t="b">
         <v>1</v>
@@ -3975,22 +3976,22 @@
         <v>0</v>
       </c>
       <c r="BE6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BF6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BG6" s="2">
         <v>44259</v>
       </c>
       <c r="BH6" t="s">
-        <v>214</v>
+        <v>421</v>
       </c>
       <c r="BI6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BJ6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BK6" s="2">
         <v>44204</v>
@@ -4038,10 +4039,10 @@
         <v>45419</v>
       </c>
       <c r="BZ6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="CA6" t="s">
-        <v>230</v>
+        <v>422</v>
       </c>
       <c r="CB6" s="2">
         <v>44033</v>
@@ -4053,85 +4054,85 @@
         <v>135</v>
       </c>
       <c r="CE6" t="s">
+        <v>233</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>234</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>235</v>
+      </c>
+      <c r="CH6" t="s">
         <v>236</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>237</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>238</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>239</v>
       </c>
       <c r="CI6">
         <v>23728283</v>
       </c>
       <c r="CJ6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CK6" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="CL6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="CM6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="CN6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="CO6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="CP6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="CQ6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="CR6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="CS6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="CT6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="CU6" t="s">
+        <v>310</v>
+      </c>
+      <c r="CV6" t="s">
         <v>313</v>
       </c>
-      <c r="CV6" t="s">
+      <c r="CW6" t="s">
+        <v>324</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>321</v>
+      </c>
+      <c r="CY6" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="CZ6" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>315</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>319</v>
+      </c>
+      <c r="DC6" t="s">
         <v>316</v>
       </c>
-      <c r="CW6" t="s">
-        <v>327</v>
-      </c>
-      <c r="CX6" t="s">
-        <v>324</v>
-      </c>
-      <c r="CY6" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="CZ6" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>318</v>
-      </c>
-      <c r="DB6" t="s">
-        <v>322</v>
-      </c>
-      <c r="DC6" t="s">
-        <v>319</v>
-      </c>
       <c r="DD6" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="DE6" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="DF6">
         <v>36</v>
@@ -4140,22 +4141,22 @@
         <v>32</v>
       </c>
       <c r="DH6" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="DI6">
         <v>321654987654</v>
       </c>
       <c r="DJ6" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="DK6">
         <v>500001004</v>
       </c>
       <c r="DL6" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="DM6" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="DN6">
         <v>2</v>
@@ -4164,7 +4165,7 @@
         <v>43910</v>
       </c>
       <c r="DP6" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="DQ6">
         <v>2</v>
@@ -4173,10 +4174,10 @@
         <v>32342</v>
       </c>
       <c r="DS6" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="DT6" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="DU6">
         <v>9988776655</v>
@@ -4188,10 +4189,10 @@
         <v>4060004321</v>
       </c>
       <c r="DX6" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="DY6" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="DZ6">
         <v>2</v>
@@ -4200,10 +4201,10 @@
         <v>5</v>
       </c>
       <c r="EB6" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="EC6" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="ED6">
         <v>1200000</v>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="422">
   <si>
     <t>AgentCode</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Suffix</t>
   </si>
   <si>
-    <t>DOB</t>
-  </si>
-  <si>
     <t>Nationality</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>MaskedPanNumber</t>
   </si>
   <si>
-    <t>aadhaar_number</t>
-  </si>
-  <si>
     <t>IrdaLicenseNumber</t>
   </si>
   <si>
@@ -99,12 +93,6 @@
     <t>CreatedDate</t>
   </si>
   <si>
-    <t>ModifiedBy</t>
-  </si>
-  <si>
-    <t>ModifiedDate</t>
-  </si>
-  <si>
     <t>RowVersion</t>
   </si>
   <si>
@@ -1269,21 +1257,6 @@
     <t>Pin</t>
   </si>
   <si>
-    <t>AG041</t>
-  </si>
-  <si>
-    <t>AG042</t>
-  </si>
-  <si>
-    <t>AG043</t>
-  </si>
-  <si>
-    <t>AG044</t>
-  </si>
-  <si>
-    <t>AG045</t>
-  </si>
-  <si>
     <t>Pharmaceutical</t>
   </si>
   <si>
@@ -1291,6 +1264,27 @@
   </si>
   <si>
     <t>General</t>
+  </si>
+  <si>
+    <t>AG051</t>
+  </si>
+  <si>
+    <t>AG052</t>
+  </si>
+  <si>
+    <t>AG053</t>
+  </si>
+  <si>
+    <t>AG054</t>
+  </si>
+  <si>
+    <t>AG055</t>
+  </si>
+  <si>
+    <t>DoB</t>
+  </si>
+  <si>
+    <t>AadhaarNumber</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:EE6"/>
+  <dimension ref="A1:EC6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
@@ -1704,119 +1698,117 @@
     <col min="19" max="19" width="15.6328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.26953125" customWidth="1"/>
+    <col min="23" max="23" width="15.453125" customWidth="1"/>
     <col min="24" max="24" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.6328125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="15" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="21" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="18" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="22" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="83" max="85" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="9" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="34.1796875" customWidth="1"/>
-    <col min="90" max="90" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="19.08984375" customWidth="1"/>
-    <col min="101" max="101" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="15" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="12" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="9" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="13" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="15" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="21" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="18" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="22" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="81" max="83" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="9" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="34.1796875" customWidth="1"/>
+    <col min="88" max="88" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="19.08984375" customWidth="1"/>
+    <col min="99" max="99" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="15" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="12" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="9" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="13" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="15.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:135" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1842,441 +1834,435 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CC1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="CD1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="CE1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="CF1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="CG1" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="CH1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="CI1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CJ1" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="CK1" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="CL1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="CM1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="CN1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="CO1" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="CP1" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="CQ1" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="CR1" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="CS1" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="CT1" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="CU1" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="CV1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="CW1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="CX1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="CY1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="CZ1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="DA1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="DB1" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="DC1" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="DD1" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="DE1" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="DF1" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="DG1" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="DH1" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="DI1" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="DJ1" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="DK1" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="DL1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="DM1" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="DN1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="DO1" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="DP1" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="DQ1" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="DR1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="DS1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="DT1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="DU1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="DV1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="DW1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="DX1" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="DY1" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="DZ1" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="EA1" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="EB1" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="EC1" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:133" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CE1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="CF1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="CG1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="CH1" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="CI1" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="CJ1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="CK1" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="CL1" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="CM1" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="CN1" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="CO1" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="CP1" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="CQ1" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="CR1" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="CS1" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="CT1" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="CU1" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="CV1" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="CW1" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="CX1" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="CY1" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="CZ1" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="DA1" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="DB1" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="DC1" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="DD1" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="DE1" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="DF1" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="DG1" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="DH1" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="DI1" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="DJ1" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="DK1" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="DL1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="DM1" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="DN1" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="DO1" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="DP1" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="DQ1" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="DR1" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="DS1" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="DT1" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="DU1" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="DV1" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="DW1" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="DX1" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="DY1" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="DZ1" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="EA1" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="EB1" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="EC1" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="ED1" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="EE1" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="2" spans="1:135" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="2">
+        <v>37315</v>
+      </c>
+      <c r="J2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" t="s">
         <v>106</v>
       </c>
-      <c r="I2" s="2">
-        <v>33270</v>
-      </c>
-      <c r="J2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" t="s">
-        <v>110</v>
-      </c>
       <c r="M2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="N2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="P2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R2" s="2">
         <v>40605</v>
       </c>
       <c r="S2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T2" s="2">
         <v>43900</v>
@@ -2285,396 +2271,396 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="W2">
         <v>123456789012</v>
       </c>
       <c r="X2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="Y2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Z2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AA2" s="2">
         <v>45987</v>
       </c>
-      <c r="AD2">
+      <c r="AB2">
         <v>1</v>
       </c>
-      <c r="AE2" t="b">
+      <c r="AC2" t="b">
         <v>1</v>
       </c>
+      <c r="AD2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>149</v>
+      </c>
       <c r="AF2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AI2" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG2" s="2">
         <v>42876</v>
       </c>
-      <c r="AJ2" t="b">
+      <c r="AH2" t="b">
         <v>0</v>
       </c>
-      <c r="AK2" t="b">
+      <c r="AI2" t="b">
         <v>1</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>159</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>164</v>
+      </c>
       <c r="AL2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>168</v>
+        <v>165</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO2">
+        <v>170</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>45840</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>41399</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>182</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA2" t="b">
         <v>1</v>
       </c>
-      <c r="AP2" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>45840</v>
-      </c>
-      <c r="AS2" s="2">
-        <v>41399</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>186</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>191</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>196</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>197</v>
-      </c>
-      <c r="AZ2" t="b">
+      <c r="BB2" t="b">
         <v>0</v>
       </c>
-      <c r="BA2" t="s">
-        <v>423</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC2" t="b">
+      <c r="BC2" t="s">
+        <v>199</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>204</v>
+      </c>
+      <c r="BE2" s="2">
+        <v>42203</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>412</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>209</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>214</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>44715</v>
+      </c>
+      <c r="BJ2" s="2">
+        <v>43125</v>
+      </c>
+      <c r="BK2" s="2">
+        <v>44657</v>
+      </c>
+      <c r="BL2" s="2">
+        <v>45425</v>
+      </c>
+      <c r="BM2" s="2">
+        <v>45191</v>
+      </c>
+      <c r="BN2" s="2">
+        <v>43610</v>
+      </c>
+      <c r="BO2" s="2">
+        <v>40925</v>
+      </c>
+      <c r="BP2" s="2">
+        <v>45610</v>
+      </c>
+      <c r="BQ2" s="2">
+        <v>45708</v>
+      </c>
+      <c r="BR2" s="2">
+        <v>45654</v>
+      </c>
+      <c r="BS2" s="2">
+        <v>43866</v>
+      </c>
+      <c r="BT2" s="2">
+        <v>44161</v>
+      </c>
+      <c r="BU2" s="2">
+        <v>44837</v>
+      </c>
+      <c r="BV2" s="2">
+        <v>45247</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>45424</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>219</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>413</v>
+      </c>
+      <c r="BZ2" s="2">
+        <v>44001</v>
+      </c>
+      <c r="CA2" s="2">
+        <v>45183</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>229</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>230</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG2">
+        <v>23728283</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>234</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>291</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>263</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>268</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>264</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>271</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>276</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>281</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>286</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>292</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>297</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>302</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>233</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>319</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>316</v>
+      </c>
+      <c r="CW2" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="CX2" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>310</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>314</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>312</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>339</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>338</v>
+      </c>
+      <c r="DD2">
+        <v>100</v>
+      </c>
+      <c r="DE2">
+        <v>12</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>354</v>
+      </c>
+      <c r="DG2">
+        <v>123456789012</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>355</v>
+      </c>
+      <c r="DI2">
+        <v>400240001</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>356</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>357</v>
+      </c>
+      <c r="DL2">
         <v>1</v>
       </c>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>203</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>208</v>
-      </c>
-      <c r="BG2" s="2">
-        <v>42203</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>213</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>218</v>
-      </c>
-      <c r="BK2" s="2">
-        <v>44715</v>
-      </c>
-      <c r="BL2" s="2">
-        <v>43125</v>
-      </c>
-      <c r="BM2" s="2">
-        <v>44657</v>
-      </c>
-      <c r="BN2" s="2">
-        <v>45425</v>
-      </c>
-      <c r="BO2" s="2">
-        <v>45191</v>
-      </c>
-      <c r="BP2" s="2">
-        <v>43610</v>
-      </c>
-      <c r="BQ2" s="2">
-        <v>40925</v>
-      </c>
-      <c r="BR2" s="2">
-        <v>45610</v>
-      </c>
-      <c r="BS2" s="2">
-        <v>45708</v>
-      </c>
-      <c r="BT2" s="2">
-        <v>45654</v>
-      </c>
-      <c r="BU2" s="2">
-        <v>43866</v>
-      </c>
-      <c r="BV2" s="2">
-        <v>44161</v>
-      </c>
-      <c r="BW2" s="2">
-        <v>44837</v>
-      </c>
-      <c r="BX2" s="2">
-        <v>45247</v>
-      </c>
-      <c r="BY2" s="2">
-        <v>45424</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>223</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>422</v>
-      </c>
-      <c r="CB2" s="2">
-        <v>44001</v>
-      </c>
-      <c r="CC2" s="2">
-        <v>45183</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>135</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>233</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>234</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>236</v>
-      </c>
-      <c r="CI2">
-        <v>23728283</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>238</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>295</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>267</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>272</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>268</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>275</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>280</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>290</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>296</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>301</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>306</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>237</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>323</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>320</v>
-      </c>
-      <c r="CY2" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="CZ2" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>314</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>318</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>316</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>343</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>342</v>
-      </c>
-      <c r="DF2">
-        <v>100</v>
-      </c>
-      <c r="DG2">
-        <v>12</v>
-      </c>
-      <c r="DH2" t="s">
+      <c r="DM2" s="6">
+        <v>44941</v>
+      </c>
+      <c r="DN2" t="s">
         <v>358</v>
       </c>
-      <c r="DI2">
-        <v>123456789012</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>359</v>
-      </c>
-      <c r="DK2">
-        <v>400240001</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>360</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>361</v>
-      </c>
-      <c r="DN2">
+      <c r="DO2">
         <v>1</v>
       </c>
-      <c r="DO2" s="6">
-        <v>44941</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>362</v>
-      </c>
-      <c r="DQ2">
+      <c r="DP2" s="6">
+        <v>33005</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>389</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>390</v>
+      </c>
+      <c r="DS2">
+        <v>9876543210</v>
+      </c>
+      <c r="DT2">
+        <v>2240001234</v>
+      </c>
+      <c r="DU2">
+        <v>2240005678</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>391</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>229</v>
+      </c>
+      <c r="DX2">
         <v>1</v>
       </c>
-      <c r="DR2" s="6">
-        <v>33005</v>
-      </c>
-      <c r="DS2" t="s">
+      <c r="DY2">
+        <v>3</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>392</v>
+      </c>
+      <c r="EA2" t="s">
         <v>393</v>
       </c>
-      <c r="DT2" t="s">
-        <v>394</v>
-      </c>
-      <c r="DU2">
-        <v>9876543210</v>
-      </c>
-      <c r="DV2">
-        <v>2240001234</v>
-      </c>
-      <c r="DW2">
-        <v>2240005678</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>395</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>233</v>
-      </c>
-      <c r="DZ2">
-        <v>1</v>
-      </c>
-      <c r="EA2">
-        <v>3</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>396</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>397</v>
-      </c>
-      <c r="ED2">
+      <c r="EB2">
         <v>450000</v>
       </c>
-      <c r="EE2">
+      <c r="EC2">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:135" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="2">
+        <v>37316</v>
+      </c>
+      <c r="J3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="2">
-        <v>33270</v>
-      </c>
-      <c r="J3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K3" t="s">
-        <v>109</v>
-      </c>
-      <c r="L3" t="s">
-        <v>111</v>
-      </c>
       <c r="M3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Q3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="R3" s="2">
         <v>42594</v>
       </c>
       <c r="S3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T3" s="2">
         <v>44869</v>
@@ -2683,396 +2669,396 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="W3">
         <v>123456789012</v>
       </c>
       <c r="X3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Y3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z3" t="s">
         <v>143</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>147</v>
       </c>
       <c r="AA3" s="2">
         <v>45987</v>
       </c>
-      <c r="AD3">
+      <c r="AB3">
         <v>2</v>
       </c>
-      <c r="AE3" t="b">
+      <c r="AC3" t="b">
         <v>1</v>
       </c>
+      <c r="AD3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>150</v>
+      </c>
       <c r="AF3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>159</v>
-      </c>
-      <c r="AI3" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG3" s="2">
         <v>43672</v>
       </c>
-      <c r="AJ3" t="b">
+      <c r="AH3" t="b">
         <v>1</v>
       </c>
-      <c r="AK3" t="b">
+      <c r="AI3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>164</v>
+      </c>
       <c r="AL3" t="s">
-        <v>164</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>168</v>
+        <v>166</v>
+      </c>
+      <c r="AM3">
+        <v>2</v>
       </c>
       <c r="AN3" t="s">
-        <v>170</v>
-      </c>
-      <c r="AO3">
-        <v>2</v>
-      </c>
-      <c r="AP3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO3" t="s">
         <v>175</v>
       </c>
-      <c r="AQ3" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR3" s="2">
+      <c r="AP3" s="2">
         <v>44175</v>
       </c>
-      <c r="AS3" s="2">
+      <c r="AQ3" s="2">
         <v>42979</v>
       </c>
+      <c r="AR3" t="s">
+        <v>176</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>178</v>
+      </c>
       <c r="AT3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AU3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AV3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AW3" t="s">
-        <v>192</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>196</v>
+        <v>194</v>
+      </c>
+      <c r="AX3" t="b">
+        <v>0</v>
       </c>
       <c r="AY3" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ3" t="s">
         <v>198</v>
       </c>
-      <c r="AZ3" t="b">
+      <c r="BA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="b">
         <v>0</v>
       </c>
-      <c r="BA3" t="s">
-        <v>423</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC3" t="b">
+      <c r="BC3" t="s">
+        <v>200</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE3" s="2">
+        <v>43907</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>412</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BI3" s="2">
+        <v>43783</v>
+      </c>
+      <c r="BJ3" s="2">
+        <v>44771</v>
+      </c>
+      <c r="BK3" s="2">
+        <v>44846</v>
+      </c>
+      <c r="BL3" s="2">
+        <v>43931</v>
+      </c>
+      <c r="BM3" s="2">
+        <v>45536</v>
+      </c>
+      <c r="BN3" s="2">
+        <v>43526</v>
+      </c>
+      <c r="BO3" s="2">
+        <v>41989</v>
+      </c>
+      <c r="BP3" s="2">
+        <v>44824</v>
+      </c>
+      <c r="BQ3" s="2">
+        <v>43654</v>
+      </c>
+      <c r="BR3" s="2">
+        <v>45843</v>
+      </c>
+      <c r="BS3" s="2">
+        <v>45111</v>
+      </c>
+      <c r="BT3" s="2">
+        <v>43398</v>
+      </c>
+      <c r="BU3" s="2">
+        <v>45093</v>
+      </c>
+      <c r="BV3" s="2">
+        <v>45689</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>45700</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>413</v>
+      </c>
+      <c r="BZ3" s="2">
+        <v>43851</v>
+      </c>
+      <c r="CA3" s="2">
+        <v>45459</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>229</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>230</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG3">
+        <v>23728283</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>234</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>328</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>263</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>269</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>265</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>272</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>277</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>287</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>293</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>298</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>303</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>307</v>
+      </c>
+      <c r="CU3" t="s">
+        <v>320</v>
+      </c>
+      <c r="CV3" t="s">
+        <v>317</v>
+      </c>
+      <c r="CW3" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="CX3" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>311</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>315</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>313</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>340</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>337</v>
+      </c>
+      <c r="DD3">
+        <v>10</v>
+      </c>
+      <c r="DE3">
+        <v>45</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>359</v>
+      </c>
+      <c r="DG3">
+        <v>987654321098</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>360</v>
+      </c>
+      <c r="DI3">
+        <v>380002002</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>361</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>362</v>
+      </c>
+      <c r="DL3">
         <v>1</v>
       </c>
-      <c r="BD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>204</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>209</v>
-      </c>
-      <c r="BG3" s="2">
-        <v>43907</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>214</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>219</v>
-      </c>
-      <c r="BK3" s="2">
-        <v>43783</v>
-      </c>
-      <c r="BL3" s="2">
-        <v>44771</v>
-      </c>
-      <c r="BM3" s="2">
-        <v>44846</v>
-      </c>
-      <c r="BN3" s="2">
-        <v>43931</v>
-      </c>
-      <c r="BO3" s="2">
-        <v>45536</v>
-      </c>
-      <c r="BP3" s="2">
-        <v>43526</v>
-      </c>
-      <c r="BQ3" s="2">
-        <v>41989</v>
-      </c>
-      <c r="BR3" s="2">
-        <v>44824</v>
-      </c>
-      <c r="BS3" s="2">
-        <v>43654</v>
-      </c>
-      <c r="BT3" s="2">
-        <v>45843</v>
-      </c>
-      <c r="BU3" s="2">
-        <v>45111</v>
-      </c>
-      <c r="BV3" s="2">
-        <v>43398</v>
-      </c>
-      <c r="BW3" s="2">
-        <v>45093</v>
-      </c>
-      <c r="BX3" s="2">
-        <v>45689</v>
-      </c>
-      <c r="BY3" s="2">
-        <v>45700</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>224</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>422</v>
-      </c>
-      <c r="CB3" s="2">
-        <v>43851</v>
-      </c>
-      <c r="CC3" s="2">
-        <v>45459</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>135</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>234</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>236</v>
-      </c>
-      <c r="CI3">
-        <v>23728283</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>238</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>332</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>267</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>273</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>269</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>276</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>281</v>
-      </c>
-      <c r="CQ3" t="s">
-        <v>286</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>291</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>297</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>302</v>
-      </c>
-      <c r="CU3" t="s">
-        <v>307</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>311</v>
-      </c>
-      <c r="CW3" t="s">
-        <v>324</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>321</v>
-      </c>
-      <c r="CY3" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="CZ3" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>315</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>319</v>
-      </c>
-      <c r="DC3" t="s">
-        <v>317</v>
-      </c>
-      <c r="DD3" t="s">
-        <v>344</v>
-      </c>
-      <c r="DE3" t="s">
-        <v>341</v>
-      </c>
-      <c r="DF3">
-        <v>10</v>
-      </c>
-      <c r="DG3">
-        <v>45</v>
-      </c>
-      <c r="DH3" t="s">
+      <c r="DM3" s="6">
+        <v>44875</v>
+      </c>
+      <c r="DN3" t="s">
         <v>363</v>
       </c>
-      <c r="DI3">
-        <v>987654321098</v>
-      </c>
-      <c r="DJ3" t="s">
-        <v>364</v>
-      </c>
-      <c r="DK3">
-        <v>380002002</v>
-      </c>
-      <c r="DL3" t="s">
-        <v>365</v>
-      </c>
-      <c r="DM3" t="s">
-        <v>366</v>
-      </c>
-      <c r="DN3">
+      <c r="DO3">
         <v>1</v>
       </c>
-      <c r="DO3" s="6">
-        <v>44875</v>
-      </c>
-      <c r="DP3" t="s">
-        <v>367</v>
-      </c>
-      <c r="DQ3">
+      <c r="DP3" s="6">
+        <v>33005</v>
+      </c>
+      <c r="DQ3" t="s">
+        <v>389</v>
+      </c>
+      <c r="DR3" t="s">
+        <v>390</v>
+      </c>
+      <c r="DS3">
+        <v>9876543210</v>
+      </c>
+      <c r="DT3">
+        <v>2240001234</v>
+      </c>
+      <c r="DU3">
+        <v>2240005678</v>
+      </c>
+      <c r="DV3" t="s">
+        <v>391</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>229</v>
+      </c>
+      <c r="DX3">
         <v>1</v>
       </c>
-      <c r="DR3" s="6">
-        <v>33005</v>
-      </c>
-      <c r="DS3" t="s">
+      <c r="DY3">
+        <v>3</v>
+      </c>
+      <c r="DZ3" t="s">
+        <v>392</v>
+      </c>
+      <c r="EA3" t="s">
         <v>393</v>
       </c>
-      <c r="DT3" t="s">
-        <v>394</v>
-      </c>
-      <c r="DU3">
-        <v>9876543210</v>
-      </c>
-      <c r="DV3">
-        <v>2240001234</v>
-      </c>
-      <c r="DW3">
-        <v>2240005678</v>
-      </c>
-      <c r="DX3" t="s">
-        <v>395</v>
-      </c>
-      <c r="DY3" t="s">
-        <v>233</v>
-      </c>
-      <c r="DZ3">
-        <v>1</v>
-      </c>
-      <c r="EA3">
-        <v>3</v>
-      </c>
-      <c r="EB3" t="s">
-        <v>396</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>397</v>
-      </c>
-      <c r="ED3">
+      <c r="EB3">
         <v>450000</v>
       </c>
-      <c r="EE3">
+      <c r="EC3">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:135" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" t="s">
         <v>103</v>
       </c>
-      <c r="G4" t="s">
-        <v>107</v>
-      </c>
       <c r="I4" s="2">
-        <v>33271</v>
+        <v>37317</v>
       </c>
       <c r="J4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" t="s">
         <v>108</v>
       </c>
-      <c r="K4" t="s">
-        <v>109</v>
-      </c>
-      <c r="L4" t="s">
-        <v>112</v>
-      </c>
       <c r="M4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="N4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="P4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Q4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R4" s="2">
         <v>38373</v>
       </c>
       <c r="S4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="T4" s="2">
         <v>44039</v>
@@ -3081,396 +3067,396 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="W4">
         <v>123456789012</v>
       </c>
       <c r="X4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="Y4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Z4" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="2">
         <v>45987</v>
       </c>
-      <c r="AD4">
+      <c r="AB4">
         <v>3</v>
       </c>
-      <c r="AE4" t="b">
+      <c r="AC4" t="b">
         <v>1</v>
       </c>
+      <c r="AD4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>151</v>
+      </c>
       <c r="AF4" t="s">
-        <v>150</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>155</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI4" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG4" s="2">
         <v>43119</v>
       </c>
-      <c r="AJ4" t="b">
+      <c r="AH4" t="b">
         <v>1</v>
       </c>
-      <c r="AK4" t="b">
+      <c r="AI4" t="b">
         <v>1</v>
       </c>
+      <c r="AJ4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>164</v>
+      </c>
       <c r="AL4" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="AM4">
+        <v>3</v>
       </c>
       <c r="AN4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO4">
-        <v>3</v>
-      </c>
-      <c r="AP4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP4" s="2">
+        <v>43871</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>43491</v>
+      </c>
+      <c r="AR4" t="s">
         <v>176</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AS4" t="s">
         <v>179</v>
       </c>
-      <c r="AR4" s="2">
-        <v>43871</v>
-      </c>
-      <c r="AS4" s="2">
-        <v>43491</v>
-      </c>
       <c r="AT4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>195</v>
+      </c>
+      <c r="AX4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>201</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>206</v>
+      </c>
+      <c r="BE4" s="2">
+        <v>45886</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>412</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>216</v>
+      </c>
+      <c r="BI4" s="2">
+        <v>44950</v>
+      </c>
+      <c r="BJ4" s="2">
+        <v>43396</v>
+      </c>
+      <c r="BK4" s="2">
+        <v>45305</v>
+      </c>
+      <c r="BL4" s="2">
+        <v>44060</v>
+      </c>
+      <c r="BM4" s="2">
+        <v>44862</v>
+      </c>
+      <c r="BN4" s="2">
+        <v>44002</v>
+      </c>
+      <c r="BO4" s="2">
+        <v>41544</v>
+      </c>
+      <c r="BP4" s="2">
+        <v>43972</v>
+      </c>
+      <c r="BQ4" s="2">
+        <v>43361</v>
+      </c>
+      <c r="BR4" s="2">
+        <v>45226</v>
+      </c>
+      <c r="BS4" s="2">
+        <v>44399</v>
+      </c>
+      <c r="BT4" s="2">
+        <v>43312</v>
+      </c>
+      <c r="BU4" s="2">
+        <v>43442</v>
+      </c>
+      <c r="BV4" s="2">
+        <v>44269</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>45805</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>221</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>413</v>
+      </c>
+      <c r="BZ4" s="2">
+        <v>43525</v>
+      </c>
+      <c r="CA4" s="2">
+        <v>45427</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>229</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>230</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG4">
+        <v>23728283</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>234</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>329</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>263</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>270</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>266</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>273</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>278</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>283</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>288</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>294</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>299</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>304</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>308</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>321</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>318</v>
+      </c>
+      <c r="CW4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="CX4" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>311</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>314</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>313</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>341</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>336</v>
+      </c>
+      <c r="DD4">
+        <v>59</v>
+      </c>
+      <c r="DE4">
+        <v>23</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>359</v>
+      </c>
+      <c r="DG4">
+        <v>987654321098</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>360</v>
+      </c>
+      <c r="DI4">
+        <v>380002002</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>361</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>362</v>
+      </c>
+      <c r="DL4">
+        <v>1</v>
+      </c>
+      <c r="DM4" s="6">
+        <v>44875</v>
+      </c>
+      <c r="DN4" t="s">
+        <v>363</v>
+      </c>
+      <c r="DO4">
+        <v>1</v>
+      </c>
+      <c r="DP4" s="6">
+        <v>31313</v>
+      </c>
+      <c r="DQ4" t="s">
+        <v>394</v>
+      </c>
+      <c r="DR4" t="s">
+        <v>395</v>
+      </c>
+      <c r="DS4">
+        <v>9898989898</v>
+      </c>
+      <c r="DT4">
+        <v>7930001234</v>
+      </c>
+      <c r="DU4">
+        <v>7930005678</v>
+      </c>
+      <c r="DV4" t="s">
+        <v>396</v>
+      </c>
+      <c r="DW4" t="s">
+        <v>397</v>
+      </c>
+      <c r="DX4">
+        <v>2</v>
+      </c>
+      <c r="DY4">
+        <v>4</v>
+      </c>
+      <c r="DZ4" t="s">
+        <v>398</v>
+      </c>
+      <c r="EA4" t="s">
+        <v>399</v>
+      </c>
+      <c r="EB4">
+        <v>850000</v>
+      </c>
+      <c r="EC4">
         <v>180</v>
       </c>
-      <c r="AU4" t="s">
-        <v>183</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>188</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>193</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>199</v>
-      </c>
-      <c r="AZ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>423</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>205</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG4" s="2">
-        <v>45886</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>215</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>220</v>
-      </c>
-      <c r="BK4" s="2">
-        <v>44950</v>
-      </c>
-      <c r="BL4" s="2">
-        <v>43396</v>
-      </c>
-      <c r="BM4" s="2">
-        <v>45305</v>
-      </c>
-      <c r="BN4" s="2">
-        <v>44060</v>
-      </c>
-      <c r="BO4" s="2">
-        <v>44862</v>
-      </c>
-      <c r="BP4" s="2">
-        <v>44002</v>
-      </c>
-      <c r="BQ4" s="2">
-        <v>41544</v>
-      </c>
-      <c r="BR4" s="2">
-        <v>43972</v>
-      </c>
-      <c r="BS4" s="2">
-        <v>43361</v>
-      </c>
-      <c r="BT4" s="2">
-        <v>45226</v>
-      </c>
-      <c r="BU4" s="2">
-        <v>44399</v>
-      </c>
-      <c r="BV4" s="2">
-        <v>43312</v>
-      </c>
-      <c r="BW4" s="2">
-        <v>43442</v>
-      </c>
-      <c r="BX4" s="2">
-        <v>44269</v>
-      </c>
-      <c r="BY4" s="2">
-        <v>45805</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>225</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>422</v>
-      </c>
-      <c r="CB4" s="2">
-        <v>43525</v>
-      </c>
-      <c r="CC4" s="2">
-        <v>45427</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>135</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>233</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>234</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>236</v>
-      </c>
-      <c r="CI4">
-        <v>23728283</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>238</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>333</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>267</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>274</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>270</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>277</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>282</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>287</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>292</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>298</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>303</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>308</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>312</v>
-      </c>
-      <c r="CW4" t="s">
-        <v>325</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>322</v>
-      </c>
-      <c r="CY4" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="CZ4" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>315</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>318</v>
-      </c>
-      <c r="DC4" t="s">
-        <v>317</v>
-      </c>
-      <c r="DD4" t="s">
-        <v>345</v>
-      </c>
-      <c r="DE4" t="s">
-        <v>340</v>
-      </c>
-      <c r="DF4">
-        <v>59</v>
-      </c>
-      <c r="DG4">
-        <v>23</v>
-      </c>
-      <c r="DH4" t="s">
-        <v>363</v>
-      </c>
-      <c r="DI4">
-        <v>987654321098</v>
-      </c>
-      <c r="DJ4" t="s">
-        <v>364</v>
-      </c>
-      <c r="DK4">
-        <v>380002002</v>
-      </c>
-      <c r="DL4" t="s">
-        <v>365</v>
-      </c>
-      <c r="DM4" t="s">
-        <v>366</v>
-      </c>
-      <c r="DN4">
-        <v>1</v>
-      </c>
-      <c r="DO4" s="6">
-        <v>44875</v>
-      </c>
-      <c r="DP4" t="s">
-        <v>367</v>
-      </c>
-      <c r="DQ4">
-        <v>1</v>
-      </c>
-      <c r="DR4" s="6">
-        <v>31313</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>398</v>
-      </c>
-      <c r="DT4" t="s">
-        <v>399</v>
-      </c>
-      <c r="DU4">
-        <v>9898989898</v>
-      </c>
-      <c r="DV4">
-        <v>7930001234</v>
-      </c>
-      <c r="DW4">
-        <v>7930005678</v>
-      </c>
-      <c r="DX4" t="s">
-        <v>400</v>
-      </c>
-      <c r="DY4" t="s">
-        <v>401</v>
-      </c>
-      <c r="DZ4">
-        <v>2</v>
-      </c>
-      <c r="EA4">
-        <v>4</v>
-      </c>
-      <c r="EB4" t="s">
-        <v>402</v>
-      </c>
-      <c r="EC4" t="s">
-        <v>403</v>
-      </c>
-      <c r="ED4">
-        <v>850000</v>
-      </c>
-      <c r="EE4">
-        <v>180</v>
-      </c>
     </row>
-    <row r="5" spans="1:135" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" s="2">
+        <v>37318</v>
+      </c>
+      <c r="J5" t="s">
         <v>104</v>
       </c>
-      <c r="G5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I5" s="2">
-        <v>33272</v>
-      </c>
-      <c r="J5" t="s">
-        <v>108</v>
-      </c>
       <c r="K5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" t="s">
         <v>109</v>
       </c>
-      <c r="L5" t="s">
-        <v>113</v>
-      </c>
       <c r="M5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="P5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="Q5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R5" s="2">
         <v>43084</v>
       </c>
       <c r="S5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="T5" s="2">
         <v>45895</v>
@@ -3479,396 +3465,396 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="W5">
         <v>123456789012</v>
       </c>
       <c r="X5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Y5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="Z5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AA5" s="2">
         <v>45987</v>
       </c>
-      <c r="AD5">
+      <c r="AB5">
         <v>4</v>
       </c>
-      <c r="AE5" t="b">
+      <c r="AC5" t="b">
         <v>1</v>
       </c>
+      <c r="AD5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>152</v>
+      </c>
       <c r="AF5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI5" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG5" s="2">
         <v>43446</v>
       </c>
-      <c r="AJ5" t="b">
+      <c r="AH5" t="b">
         <v>0</v>
       </c>
-      <c r="AK5" t="b">
+      <c r="AI5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>164</v>
+      </c>
       <c r="AL5" t="s">
-        <v>166</v>
-      </c>
-      <c r="AM5" t="s">
         <v>168</v>
       </c>
+      <c r="AM5">
+        <v>4</v>
+      </c>
       <c r="AN5" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO5">
-        <v>4</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR5" s="2">
+        <v>173</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP5" s="2">
         <v>42312</v>
       </c>
-      <c r="AS5" s="2">
+      <c r="AQ5" s="2">
         <v>41829</v>
       </c>
+      <c r="AR5" t="s">
+        <v>176</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>180</v>
+      </c>
       <c r="AT5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AU5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="AV5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AW5" t="s">
-        <v>194</v>
-      </c>
-      <c r="AX5" t="s">
         <v>196</v>
       </c>
+      <c r="AX5" t="b">
+        <v>0</v>
+      </c>
       <c r="AY5" t="s">
-        <v>200</v>
-      </c>
-      <c r="AZ5" t="b">
+        <v>414</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="b">
         <v>0</v>
       </c>
-      <c r="BA5" t="s">
-        <v>423</v>
-      </c>
-      <c r="BB5" t="s">
+      <c r="BC5" t="s">
         <v>202</v>
       </c>
-      <c r="BC5" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>206</v>
+      <c r="BD5" t="s">
+        <v>207</v>
+      </c>
+      <c r="BE5" s="2">
+        <v>45439</v>
       </c>
       <c r="BF5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG5" s="2">
-        <v>45439</v>
+        <v>412</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>212</v>
       </c>
       <c r="BH5" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>216</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>45091</v>
+      </c>
+      <c r="BJ5" s="2">
+        <v>45345</v>
       </c>
       <c r="BK5" s="2">
-        <v>45091</v>
+        <v>43185</v>
       </c>
       <c r="BL5" s="2">
-        <v>45345</v>
+        <v>44929</v>
       </c>
       <c r="BM5" s="2">
-        <v>43185</v>
+        <v>43749</v>
       </c>
       <c r="BN5" s="2">
-        <v>44929</v>
+        <v>44530</v>
       </c>
       <c r="BO5" s="2">
-        <v>43749</v>
+        <v>43080</v>
       </c>
       <c r="BP5" s="2">
-        <v>44530</v>
+        <v>43193</v>
       </c>
       <c r="BQ5" s="2">
-        <v>43080</v>
+        <v>43485</v>
       </c>
       <c r="BR5" s="2">
-        <v>43193</v>
+        <v>43354</v>
       </c>
       <c r="BS5" s="2">
-        <v>43485</v>
+        <v>45524</v>
       </c>
       <c r="BT5" s="2">
-        <v>43354</v>
+        <v>44177</v>
       </c>
       <c r="BU5" s="2">
-        <v>45524</v>
+        <v>43545</v>
       </c>
       <c r="BV5" s="2">
-        <v>44177</v>
+        <v>44525</v>
       </c>
       <c r="BW5" s="2">
-        <v>43545</v>
-      </c>
-      <c r="BX5" s="2">
-        <v>44525</v>
-      </c>
-      <c r="BY5" s="2">
         <v>45800</v>
       </c>
-      <c r="BZ5" t="s">
-        <v>226</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>422</v>
-      </c>
-      <c r="CB5" s="2">
+      <c r="BX5" t="s">
+        <v>222</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>413</v>
+      </c>
+      <c r="BZ5" s="2">
         <v>43885</v>
       </c>
-      <c r="CC5" s="2">
+      <c r="CA5" s="2">
         <v>45563</v>
       </c>
+      <c r="CB5" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>229</v>
+      </c>
       <c r="CD5" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="CE5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="CF5" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG5">
+        <v>23728283</v>
+      </c>
+      <c r="CH5" t="s">
         <v>234</v>
       </c>
-      <c r="CG5" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>236</v>
-      </c>
-      <c r="CI5">
-        <v>23728283</v>
+      <c r="CI5" t="s">
+        <v>330</v>
       </c>
       <c r="CJ5" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="CK5" t="s">
-        <v>334</v>
+        <v>268</v>
       </c>
       <c r="CL5" t="s">
         <v>267</v>
       </c>
       <c r="CM5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="CN5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="CO5" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="CP5" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="CQ5" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="CR5" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="CS5" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="CT5" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="CU5" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="CV5" t="s">
+        <v>316</v>
+      </c>
+      <c r="CW5" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="CX5" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>311</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>315</v>
+      </c>
+      <c r="DA5" t="s">
         <v>313</v>
       </c>
-      <c r="CW5" t="s">
-        <v>323</v>
-      </c>
-      <c r="CX5" t="s">
-        <v>320</v>
-      </c>
-      <c r="CY5" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="CZ5" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="DA5" t="s">
-        <v>315</v>
-      </c>
       <c r="DB5" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="DC5" t="s">
-        <v>317</v>
-      </c>
-      <c r="DD5" t="s">
-        <v>346</v>
-      </c>
-      <c r="DE5" t="s">
-        <v>340</v>
-      </c>
-      <c r="DF5">
+        <v>336</v>
+      </c>
+      <c r="DD5">
         <v>45</v>
       </c>
+      <c r="DE5">
+        <v>67</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>364</v>
+      </c>
       <c r="DG5">
-        <v>67</v>
+        <v>456789123456</v>
       </c>
       <c r="DH5" t="s">
+        <v>365</v>
+      </c>
+      <c r="DI5">
+        <v>110002003</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>366</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>367</v>
+      </c>
+      <c r="DL5">
+        <v>1</v>
+      </c>
+      <c r="DM5" s="6">
+        <v>44352</v>
+      </c>
+      <c r="DN5" t="s">
         <v>368</v>
       </c>
-      <c r="DI5">
-        <v>456789123456</v>
-      </c>
-      <c r="DJ5" t="s">
-        <v>369</v>
-      </c>
-      <c r="DK5">
-        <v>110002003</v>
-      </c>
-      <c r="DL5" t="s">
-        <v>370</v>
-      </c>
-      <c r="DM5" t="s">
-        <v>371</v>
-      </c>
-      <c r="DN5">
+      <c r="DO5">
         <v>1</v>
       </c>
-      <c r="DO5" s="6">
-        <v>44352</v>
-      </c>
-      <c r="DP5" t="s">
-        <v>372</v>
-      </c>
-      <c r="DQ5">
+      <c r="DP5" s="6">
+        <v>33644</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>400</v>
+      </c>
+      <c r="DR5" t="s">
+        <v>401</v>
+      </c>
+      <c r="DS5">
+        <v>9123456789</v>
+      </c>
+      <c r="DT5">
+        <v>1145001234</v>
+      </c>
+      <c r="DU5">
+        <v>1145007890</v>
+      </c>
+      <c r="DV5" t="s">
+        <v>402</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>403</v>
+      </c>
+      <c r="DX5">
         <v>1</v>
       </c>
-      <c r="DR5" s="6">
-        <v>33644</v>
-      </c>
-      <c r="DS5" t="s">
+      <c r="DY5">
+        <v>3</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>392</v>
+      </c>
+      <c r="EA5" t="s">
         <v>404</v>
       </c>
-      <c r="DT5" t="s">
-        <v>405</v>
-      </c>
-      <c r="DU5">
-        <v>9123456789</v>
-      </c>
-      <c r="DV5">
-        <v>1145001234</v>
-      </c>
-      <c r="DW5">
-        <v>1145007890</v>
-      </c>
-      <c r="DX5" t="s">
-        <v>406</v>
-      </c>
-      <c r="DY5" t="s">
-        <v>407</v>
-      </c>
-      <c r="DZ5">
-        <v>1</v>
-      </c>
-      <c r="EA5">
-        <v>3</v>
-      </c>
-      <c r="EB5" t="s">
-        <v>396</v>
-      </c>
-      <c r="EC5" t="s">
-        <v>408</v>
-      </c>
-      <c r="ED5">
+      <c r="EB5">
         <v>520000</v>
       </c>
-      <c r="EE5">
+      <c r="EC5">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:135" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="2">
+        <v>37319</v>
+      </c>
+      <c r="J6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" t="s">
         <v>105</v>
       </c>
-      <c r="G6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" s="2">
-        <v>33273</v>
-      </c>
-      <c r="J6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K6" t="s">
-        <v>109</v>
-      </c>
       <c r="L6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="P6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Q6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="R6" s="2">
         <v>40686</v>
       </c>
       <c r="S6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T6" s="2">
         <v>43867</v>
@@ -3877,339 +3863,339 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="W6">
         <v>123456789012</v>
       </c>
       <c r="X6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Y6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Z6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AA6" s="2">
         <v>45987</v>
       </c>
-      <c r="AD6">
+      <c r="AB6">
         <v>5</v>
       </c>
-      <c r="AE6" t="b">
+      <c r="AC6" t="b">
         <v>1</v>
       </c>
+      <c r="AD6" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>153</v>
+      </c>
       <c r="AF6" t="s">
-        <v>152</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>157</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AI6" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG6" s="2">
         <v>45627</v>
       </c>
-      <c r="AJ6" t="b">
+      <c r="AH6" t="b">
         <v>0</v>
       </c>
-      <c r="AK6" t="b">
+      <c r="AI6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="s">
+        <v>163</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>164</v>
+      </c>
       <c r="AL6" t="s">
-        <v>167</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="AM6">
+        <v>5</v>
       </c>
       <c r="AN6" t="s">
-        <v>173</v>
-      </c>
-      <c r="AO6">
+        <v>174</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>175</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>45774</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>44158</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>181</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>191</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>192</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AX6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>414</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>203</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>208</v>
+      </c>
+      <c r="BE6" s="2">
+        <v>44259</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>412</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>213</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>218</v>
+      </c>
+      <c r="BI6" s="2">
+        <v>44204</v>
+      </c>
+      <c r="BJ6" s="2">
+        <v>44545</v>
+      </c>
+      <c r="BK6" s="2">
+        <v>44869</v>
+      </c>
+      <c r="BL6" s="2">
+        <v>45896</v>
+      </c>
+      <c r="BM6" s="2">
+        <v>45418</v>
+      </c>
+      <c r="BN6" s="2">
+        <v>44048</v>
+      </c>
+      <c r="BO6" s="2">
+        <v>43172</v>
+      </c>
+      <c r="BP6" s="2">
+        <v>45787</v>
+      </c>
+      <c r="BQ6" s="2">
+        <v>45476</v>
+      </c>
+      <c r="BR6" s="2">
+        <v>44155</v>
+      </c>
+      <c r="BS6" s="2">
+        <v>45643</v>
+      </c>
+      <c r="BT6" s="2">
+        <v>43862</v>
+      </c>
+      <c r="BU6" s="2">
+        <v>44370</v>
+      </c>
+      <c r="BV6" s="2">
+        <v>45077</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>45419</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>223</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>413</v>
+      </c>
+      <c r="BZ6" s="2">
+        <v>44033</v>
+      </c>
+      <c r="CA6" s="2">
+        <v>45710</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>131</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>229</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG6">
+        <v>23728283</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>234</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>331</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>263</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>269</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>264</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>275</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>280</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>285</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>290</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>296</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>301</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>306</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>309</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>320</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>317</v>
+      </c>
+      <c r="CW6" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="CX6" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>311</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>315</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>312</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>343</v>
+      </c>
+      <c r="DC6" t="s">
+        <v>344</v>
+      </c>
+      <c r="DD6">
+        <v>36</v>
+      </c>
+      <c r="DE6">
+        <v>32</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>369</v>
+      </c>
+      <c r="DG6">
+        <v>321654987654</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>370</v>
+      </c>
+      <c r="DI6">
+        <v>500001004</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>371</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>372</v>
+      </c>
+      <c r="DL6">
+        <v>2</v>
+      </c>
+      <c r="DM6" s="6">
+        <v>43910</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>373</v>
+      </c>
+      <c r="DO6">
+        <v>2</v>
+      </c>
+      <c r="DP6" s="6">
+        <v>32342</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>405</v>
+      </c>
+      <c r="DR6" t="s">
+        <v>406</v>
+      </c>
+      <c r="DS6">
+        <v>9988776655</v>
+      </c>
+      <c r="DT6">
+        <v>4060001234</v>
+      </c>
+      <c r="DU6">
+        <v>4060004321</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>407</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>408</v>
+      </c>
+      <c r="DX6">
+        <v>2</v>
+      </c>
+      <c r="DY6">
         <v>5</v>
       </c>
-      <c r="AP6" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>179</v>
-      </c>
-      <c r="AR6" s="2">
-        <v>45774</v>
-      </c>
-      <c r="AS6" s="2">
-        <v>44158</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>180</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>185</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>190</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>195</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>196</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AZ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>423</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>202</v>
-      </c>
-      <c r="BC6" t="b">
-        <v>1</v>
-      </c>
-      <c r="BD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>207</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>212</v>
-      </c>
-      <c r="BG6" s="2">
-        <v>44259</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>421</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>217</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>222</v>
-      </c>
-      <c r="BK6" s="2">
-        <v>44204</v>
-      </c>
-      <c r="BL6" s="2">
-        <v>44545</v>
-      </c>
-      <c r="BM6" s="2">
-        <v>44869</v>
-      </c>
-      <c r="BN6" s="2">
-        <v>45896</v>
-      </c>
-      <c r="BO6" s="2">
-        <v>45418</v>
-      </c>
-      <c r="BP6" s="2">
-        <v>44048</v>
-      </c>
-      <c r="BQ6" s="2">
-        <v>43172</v>
-      </c>
-      <c r="BR6" s="2">
-        <v>45787</v>
-      </c>
-      <c r="BS6" s="2">
-        <v>45476</v>
-      </c>
-      <c r="BT6" s="2">
-        <v>44155</v>
-      </c>
-      <c r="BU6" s="2">
-        <v>45643</v>
-      </c>
-      <c r="BV6" s="2">
-        <v>43862</v>
-      </c>
-      <c r="BW6" s="2">
-        <v>44370</v>
-      </c>
-      <c r="BX6" s="2">
-        <v>45077</v>
-      </c>
-      <c r="BY6" s="2">
-        <v>45419</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>227</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>422</v>
-      </c>
-      <c r="CB6" s="2">
-        <v>44033</v>
-      </c>
-      <c r="CC6" s="2">
-        <v>45710</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>135</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>233</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>234</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>235</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>236</v>
-      </c>
-      <c r="CI6">
-        <v>23728283</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>238</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>335</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>267</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>273</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>268</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>279</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>284</v>
-      </c>
-      <c r="CQ6" t="s">
-        <v>289</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>294</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>300</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>305</v>
-      </c>
-      <c r="CU6" t="s">
-        <v>310</v>
-      </c>
-      <c r="CV6" t="s">
-        <v>313</v>
-      </c>
-      <c r="CW6" t="s">
-        <v>324</v>
-      </c>
-      <c r="CX6" t="s">
-        <v>321</v>
-      </c>
-      <c r="CY6" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="CZ6" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>315</v>
-      </c>
-      <c r="DB6" t="s">
-        <v>319</v>
-      </c>
-      <c r="DC6" t="s">
-        <v>316</v>
-      </c>
-      <c r="DD6" t="s">
-        <v>347</v>
-      </c>
-      <c r="DE6" t="s">
-        <v>348</v>
-      </c>
-      <c r="DF6">
-        <v>36</v>
-      </c>
-      <c r="DG6">
-        <v>32</v>
-      </c>
-      <c r="DH6" t="s">
-        <v>373</v>
-      </c>
-      <c r="DI6">
-        <v>321654987654</v>
-      </c>
-      <c r="DJ6" t="s">
-        <v>374</v>
-      </c>
-      <c r="DK6">
-        <v>500001004</v>
-      </c>
-      <c r="DL6" t="s">
-        <v>375</v>
-      </c>
-      <c r="DM6" t="s">
-        <v>376</v>
-      </c>
-      <c r="DN6">
-        <v>2</v>
-      </c>
-      <c r="DO6" s="6">
-        <v>43910</v>
-      </c>
-      <c r="DP6" t="s">
-        <v>377</v>
-      </c>
-      <c r="DQ6">
-        <v>2</v>
-      </c>
-      <c r="DR6" s="6">
-        <v>32342</v>
-      </c>
-      <c r="DS6" t="s">
+      <c r="DZ6" t="s">
         <v>409</v>
       </c>
-      <c r="DT6" t="s">
+      <c r="EA6" t="s">
         <v>410</v>
       </c>
-      <c r="DU6">
-        <v>9988776655</v>
-      </c>
-      <c r="DV6">
-        <v>4060001234</v>
-      </c>
-      <c r="DW6">
-        <v>4060004321</v>
-      </c>
-      <c r="DX6" t="s">
-        <v>411</v>
-      </c>
-      <c r="DY6" t="s">
-        <v>412</v>
-      </c>
-      <c r="DZ6">
-        <v>2</v>
-      </c>
-      <c r="EA6">
-        <v>5</v>
-      </c>
-      <c r="EB6" t="s">
-        <v>413</v>
-      </c>
-      <c r="EC6" t="s">
-        <v>414</v>
-      </c>
-      <c r="ED6">
+      <c r="EB6">
         <v>1200000</v>
       </c>
-      <c r="EE6">
+      <c r="EC6">
         <v>156</v>
       </c>
     </row>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="423">
   <si>
     <t>AgentCode</t>
   </si>
@@ -837,33 +837,12 @@
     <t>Agency</t>
   </si>
   <si>
-    <t>Direct Sales</t>
-  </si>
-  <si>
-    <t>Banca Assurance</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
     <t>Broker</t>
   </si>
   <si>
-    <t>Field Agent</t>
-  </si>
-  <si>
     <t>Unit Manager</t>
   </si>
   <si>
-    <t>Digital Partner</t>
-  </si>
-  <si>
-    <t>Tele-Sales</t>
-  </si>
-  <si>
-    <t>Bank Partner Tier A</t>
-  </si>
-  <si>
     <t>Salaried Employee</t>
   </si>
   <si>
@@ -978,15 +957,6 @@
     <t>Tokyo</t>
   </si>
   <si>
-    <t>Senior Manager</t>
-  </si>
-  <si>
-    <t>Software Engineer</t>
-  </si>
-  <si>
-    <t>Data Analyst</t>
-  </si>
-  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -1285,6 +1255,39 @@
   </si>
   <si>
     <t>AadhaarNumber</t>
+  </si>
+  <si>
+    <t>Bancassurance</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Retail Agency</t>
+  </si>
+  <si>
+    <t>Private Banks</t>
+  </si>
+  <si>
+    <t>Digital Sales</t>
+  </si>
+  <si>
+    <t>Group Employee</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>Corporate Account Manager</t>
+  </si>
+  <si>
+    <t>Zonal Manager</t>
+  </si>
+  <si>
+    <t>Area Head</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -1876,7 +1879,7 @@
         <v>19</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
@@ -2062,7 +2065,7 @@
         <v>227</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>228</v>
@@ -2125,93 +2128,93 @@
         <v>262</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="DE1" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="DF1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="DF1" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="DG1" s="3" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="DJ1" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="DK1" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="DL1" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="DM1" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="DN1" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="DO1" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="DP1" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="DQ1" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="DR1" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="DS1" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="DT1" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="DU1" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="DV1" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="DW1" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="DX1" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="DY1" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="DL1" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="DM1" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="DN1" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="DO1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="DP1" s="3" t="s">
+      <c r="DZ1" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="DQ1" s="3" t="s">
+      <c r="EA1" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="DR1" s="3" t="s">
+      <c r="EB1" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="DS1" s="3" t="s">
+      <c r="EC1" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="DT1" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="DU1" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="DV1" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="DW1" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="DX1" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="DY1" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="DZ1" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="EA1" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="EB1" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="EC1" s="3" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
@@ -2358,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AZ2" t="s">
         <v>198</v>
@@ -2379,7 +2382,7 @@
         <v>42203</v>
       </c>
       <c r="BF2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BG2" t="s">
         <v>209</v>
@@ -2436,7 +2439,7 @@
         <v>219</v>
       </c>
       <c r="BY2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="BZ2" s="2">
         <v>44001</v>
@@ -2466,7 +2469,7 @@
         <v>234</v>
       </c>
       <c r="CI2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="CJ2" t="s">
         <v>263</v>
@@ -2481,52 +2484,52 @@
         <v>271</v>
       </c>
       <c r="CN2" t="s">
-        <v>276</v>
+        <v>415</v>
       </c>
       <c r="CO2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="CP2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="CQ2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="CR2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="CS2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="CT2" t="s">
         <v>233</v>
       </c>
       <c r="CU2" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="CV2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="CW2" s="5" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="CX2" s="5" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="CY2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="CZ2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="DA2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="DB2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="DC2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="DD2">
         <v>100</v>
@@ -2535,22 +2538,22 @@
         <v>12</v>
       </c>
       <c r="DF2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="DG2">
         <v>123456789012</v>
       </c>
       <c r="DH2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="DI2">
         <v>400240001</v>
       </c>
       <c r="DJ2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="DK2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="DL2">
         <v>1</v>
@@ -2559,7 +2562,7 @@
         <v>44941</v>
       </c>
       <c r="DN2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="DO2">
         <v>1</v>
@@ -2568,10 +2571,10 @@
         <v>33005</v>
       </c>
       <c r="DQ2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="DR2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="DS2">
         <v>9876543210</v>
@@ -2583,7 +2586,7 @@
         <v>2240005678</v>
       </c>
       <c r="DV2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="DW2" t="s">
         <v>229</v>
@@ -2595,10 +2598,10 @@
         <v>3</v>
       </c>
       <c r="DZ2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="EA2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="EB2">
         <v>450000</v>
@@ -2609,7 +2612,7 @@
     </row>
     <row r="3" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
@@ -2756,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AZ3" t="s">
         <v>198</v>
@@ -2777,7 +2780,7 @@
         <v>43907</v>
       </c>
       <c r="BF3" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BG3" t="s">
         <v>210</v>
@@ -2834,7 +2837,7 @@
         <v>220</v>
       </c>
       <c r="BY3" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="BZ3" s="2">
         <v>43851</v>
@@ -2864,7 +2867,7 @@
         <v>234</v>
       </c>
       <c r="CI3" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="CJ3" t="s">
         <v>263</v>
@@ -2876,55 +2879,55 @@
         <v>265</v>
       </c>
       <c r="CM3" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="CN3" t="s">
-        <v>277</v>
+        <v>416</v>
       </c>
       <c r="CO3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="CP3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="CQ3" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="CR3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="CS3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="CT3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="CU3" t="s">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="CV3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="CW3" s="5" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="CX3" s="5" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="CY3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="CZ3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="DA3" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="DB3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="DC3" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="DD3">
         <v>10</v>
@@ -2933,22 +2936,22 @@
         <v>45</v>
       </c>
       <c r="DF3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="DG3">
         <v>987654321098</v>
       </c>
       <c r="DH3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="DI3">
         <v>380002002</v>
       </c>
       <c r="DJ3" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="DK3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="DL3">
         <v>1</v>
@@ -2957,7 +2960,7 @@
         <v>44875</v>
       </c>
       <c r="DN3" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="DO3">
         <v>1</v>
@@ -2966,10 +2969,10 @@
         <v>33005</v>
       </c>
       <c r="DQ3" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="DR3" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="DS3">
         <v>9876543210</v>
@@ -2981,7 +2984,7 @@
         <v>2240005678</v>
       </c>
       <c r="DV3" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="DW3" t="s">
         <v>229</v>
@@ -2993,10 +2996,10 @@
         <v>3</v>
       </c>
       <c r="DZ3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="EA3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="EB3">
         <v>450000</v>
@@ -3007,7 +3010,7 @@
     </row>
     <row r="4" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
@@ -3154,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AZ4" t="s">
         <v>198</v>
@@ -3175,7 +3178,7 @@
         <v>45886</v>
       </c>
       <c r="BF4" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BG4" t="s">
         <v>211</v>
@@ -3232,7 +3235,7 @@
         <v>221</v>
       </c>
       <c r="BY4" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="BZ4" s="2">
         <v>43525</v>
@@ -3262,7 +3265,7 @@
         <v>234</v>
       </c>
       <c r="CI4" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="CJ4" t="s">
         <v>263</v>
@@ -3274,55 +3277,55 @@
         <v>266</v>
       </c>
       <c r="CM4" t="s">
-        <v>273</v>
+        <v>413</v>
       </c>
       <c r="CN4" t="s">
-        <v>278</v>
+        <v>417</v>
       </c>
       <c r="CO4" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="CP4" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="CQ4" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="CR4" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="CS4" t="s">
+        <v>297</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>301</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>421</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>311</v>
+      </c>
+      <c r="CW4" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="CX4" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CY4" t="s">
         <v>304</v>
       </c>
-      <c r="CT4" t="s">
-        <v>308</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>321</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>318</v>
-      </c>
-      <c r="CW4" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="CX4" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="CY4" t="s">
-        <v>311</v>
-      </c>
       <c r="CZ4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="DA4" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="DB4" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="DC4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="DD4">
         <v>59</v>
@@ -3331,22 +3334,22 @@
         <v>23</v>
       </c>
       <c r="DF4" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="DG4">
         <v>987654321098</v>
       </c>
       <c r="DH4" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="DI4">
         <v>380002002</v>
       </c>
       <c r="DJ4" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="DK4" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="DL4">
         <v>1</v>
@@ -3355,7 +3358,7 @@
         <v>44875</v>
       </c>
       <c r="DN4" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="DO4">
         <v>1</v>
@@ -3364,10 +3367,10 @@
         <v>31313</v>
       </c>
       <c r="DQ4" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="DR4" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="DS4">
         <v>9898989898</v>
@@ -3379,10 +3382,10 @@
         <v>7930005678</v>
       </c>
       <c r="DV4" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="DW4" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="DX4">
         <v>2</v>
@@ -3391,10 +3394,10 @@
         <v>4</v>
       </c>
       <c r="DZ4" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="EA4" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="EB4">
         <v>850000</v>
@@ -3405,7 +3408,7 @@
     </row>
     <row r="5" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B5" t="s">
         <v>80</v>
@@ -3552,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AZ5" t="s">
         <v>198</v>
@@ -3573,7 +3576,7 @@
         <v>45439</v>
       </c>
       <c r="BF5" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BG5" t="s">
         <v>212</v>
@@ -3630,7 +3633,7 @@
         <v>222</v>
       </c>
       <c r="BY5" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="BZ5" s="2">
         <v>43885</v>
@@ -3660,7 +3663,7 @@
         <v>234</v>
       </c>
       <c r="CI5" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="CJ5" t="s">
         <v>263</v>
@@ -3672,55 +3675,55 @@
         <v>267</v>
       </c>
       <c r="CM5" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="CN5" t="s">
-        <v>279</v>
+        <v>418</v>
       </c>
       <c r="CO5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="CP5" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="CQ5" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="CR5" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="CS5" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="CT5" t="s">
+        <v>302</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>422</v>
+      </c>
+      <c r="CV5" t="s">
         <v>309</v>
       </c>
-      <c r="CU5" t="s">
-        <v>319</v>
-      </c>
-      <c r="CV5" t="s">
-        <v>316</v>
-      </c>
       <c r="CW5" s="5" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="CX5" s="5" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="CY5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="CZ5" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="DA5" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="DB5" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="DC5" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="DD5">
         <v>45</v>
@@ -3729,22 +3732,22 @@
         <v>67</v>
       </c>
       <c r="DF5" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="DG5">
         <v>456789123456</v>
       </c>
       <c r="DH5" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="DI5">
         <v>110002003</v>
       </c>
       <c r="DJ5" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="DK5" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="DL5">
         <v>1</v>
@@ -3753,7 +3756,7 @@
         <v>44352</v>
       </c>
       <c r="DN5" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="DO5">
         <v>1</v>
@@ -3762,10 +3765,10 @@
         <v>33644</v>
       </c>
       <c r="DQ5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="DR5" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="DS5">
         <v>9123456789</v>
@@ -3777,10 +3780,10 @@
         <v>1145007890</v>
       </c>
       <c r="DV5" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="DW5" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="DX5">
         <v>1</v>
@@ -3789,10 +3792,10 @@
         <v>3</v>
       </c>
       <c r="DZ5" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="EA5" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="EB5">
         <v>520000</v>
@@ -3803,7 +3806,7 @@
     </row>
     <row r="6" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B6" t="s">
         <v>81</v>
@@ -3950,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AZ6" t="s">
         <v>198</v>
@@ -3971,7 +3974,7 @@
         <v>44259</v>
       </c>
       <c r="BF6" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="BG6" t="s">
         <v>213</v>
@@ -4028,7 +4031,7 @@
         <v>223</v>
       </c>
       <c r="BY6" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="BZ6" s="2">
         <v>44033</v>
@@ -4058,7 +4061,7 @@
         <v>234</v>
       </c>
       <c r="CI6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="CJ6" t="s">
         <v>263</v>
@@ -4070,55 +4073,55 @@
         <v>264</v>
       </c>
       <c r="CM6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="CN6" t="s">
-        <v>280</v>
+        <v>419</v>
       </c>
       <c r="CO6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="CP6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="CQ6" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="CR6" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="CS6" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="CT6" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="CU6" t="s">
-        <v>320</v>
+        <v>389</v>
       </c>
       <c r="CV6" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="CW6" s="5" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="CX6" s="5" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="CY6" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="CZ6" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="DA6" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="DB6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="DC6" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="DD6">
         <v>36</v>
@@ -4127,22 +4130,22 @@
         <v>32</v>
       </c>
       <c r="DF6" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="DG6">
         <v>321654987654</v>
       </c>
       <c r="DH6" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="DI6">
         <v>500001004</v>
       </c>
       <c r="DJ6" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="DK6" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="DL6">
         <v>2</v>
@@ -4151,7 +4154,7 @@
         <v>43910</v>
       </c>
       <c r="DN6" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="DO6">
         <v>2</v>
@@ -4160,10 +4163,10 @@
         <v>32342</v>
       </c>
       <c r="DQ6" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="DR6" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="DS6">
         <v>9988776655</v>
@@ -4175,10 +4178,10 @@
         <v>4060004321</v>
       </c>
       <c r="DV6" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="DW6" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="DX6">
         <v>2</v>
@@ -4187,10 +4190,10 @@
         <v>5</v>
       </c>
       <c r="DZ6" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="EA6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="EB6">
         <v>1200000</v>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="698">
   <si>
     <t>AgentCode</t>
   </si>
@@ -534,9 +534,6 @@
     <t>Sales Executive</t>
   </si>
   <si>
-    <t>Branch Manager</t>
-  </si>
-  <si>
     <t>PQRST3456U</t>
   </si>
   <si>
@@ -1716,9 +1713,6 @@
     <t>AM25</t>
   </si>
   <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>LIC006</t>
   </si>
   <si>
@@ -2089,6 +2083,36 @@
   </si>
   <si>
     <t>NPSTrngCompletionDate</t>
+  </si>
+  <si>
+    <t>Unit Manager</t>
+  </si>
+  <si>
+    <t>Area Head</t>
+  </si>
+  <si>
+    <t>National Head</t>
+  </si>
+  <si>
+    <t>Zonal Head</t>
+  </si>
+  <si>
+    <t>Region Head</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Katraj unit Office</t>
+  </si>
+  <si>
+    <t>Unit Office</t>
+  </si>
+  <si>
+    <t>Health</t>
   </si>
 </sst>
 </file>
@@ -2492,7 +2516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:EC22"/>
+  <dimension ref="A1:ED22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -2626,7 +2650,7 @@
     <col min="133" max="133" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2652,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -2694,7 +2718,7 @@
         <v>19</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
@@ -2808,7 +2832,7 @@
         <v>56</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>57</v>
@@ -2817,7 +2841,7 @@
         <v>58</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>59</v>
@@ -2835,10 +2859,10 @@
         <v>63</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="BT1" s="1" t="s">
         <v>64</v>
@@ -2880,7 +2904,7 @@
         <v>94</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>95</v>
@@ -3026,26 +3050,29 @@
       <c r="EC1" s="3" t="s">
         <v>168</v>
       </c>
+      <c r="ED1" s="3" t="s">
+        <v>694</v>
+      </c>
     </row>
-    <row r="2" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
         <v>181</v>
-      </c>
-      <c r="B2" t="s">
-        <v>182</v>
       </c>
       <c r="C2" t="str">
         <f>TRIM(B2)</f>
         <v>Bell Murphy</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G2" t="s">
         <v>74</v>
@@ -3066,7 +3093,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O2" t="s">
         <v>80</v>
@@ -3087,16 +3114,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W2" s="9">
         <v>291830217845</v>
       </c>
       <c r="X2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Z2" t="s">
         <v>82</v>
@@ -3108,13 +3135,13 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AE2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AF2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG2" s="2">
         <v>44082</v>
@@ -3135,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AO2" t="s">
         <v>85</v>
@@ -3153,25 +3180,25 @@
         <v>8129055432</v>
       </c>
       <c r="AT2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AU2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AV2" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AW2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AX2" t="b">
         <v>0</v>
       </c>
       <c r="AY2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BA2" t="b">
         <v>1</v>
@@ -3180,16 +3207,16 @@
         <v>0</v>
       </c>
       <c r="BC2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BD2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="BE2" s="2">
         <v>45671</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG2" t="s">
         <v>87</v>
@@ -3243,10 +3270,10 @@
         <v>45420</v>
       </c>
       <c r="BX2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="BY2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ2" s="2">
         <v>45377</v>
@@ -3258,16 +3285,16 @@
         <v>81</v>
       </c>
       <c r="CC2" t="s">
+        <v>586</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>587</v>
+      </c>
+      <c r="CE2" t="s">
         <v>588</v>
       </c>
-      <c r="CD2" t="s">
-        <v>589</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>590</v>
-      </c>
       <c r="CF2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG2">
         <v>400050</v>
@@ -3276,7 +3303,7 @@
         <v>98</v>
       </c>
       <c r="CI2" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ2" t="s">
         <v>121</v>
@@ -3291,7 +3318,7 @@
         <v>124</v>
       </c>
       <c r="CN2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO2" t="s">
         <v>125</v>
@@ -3312,10 +3339,10 @@
         <v>97</v>
       </c>
       <c r="CU2" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV2" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW2" s="5" t="s">
         <v>133</v>
@@ -3333,7 +3360,7 @@
         <v>131</v>
       </c>
       <c r="DB2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="DC2" t="s">
         <v>141</v>
@@ -3345,13 +3372,13 @@
         <v>32</v>
       </c>
       <c r="DF2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="DG2">
         <v>829104573612</v>
       </c>
       <c r="DH2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="DI2">
         <v>500001004</v>
@@ -3378,10 +3405,10 @@
         <v>32343</v>
       </c>
       <c r="DQ2" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR2" t="s">
         <v>172</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>173</v>
       </c>
       <c r="DS2">
         <v>9988776657</v>
@@ -3393,7 +3420,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW2" t="s">
         <v>96</v>
@@ -3416,25 +3443,28 @@
       <c r="EC2">
         <v>156</v>
       </c>
+      <c r="ED2" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="3" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G3" t="s">
         <v>74</v>
@@ -3455,7 +3485,7 @@
         <v>78</v>
       </c>
       <c r="N3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O3" t="s">
         <v>80</v>
@@ -3476,16 +3506,16 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="W3" s="9">
         <v>810344529012</v>
       </c>
       <c r="X3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Y3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Z3" t="s">
         <v>82</v>
@@ -3497,13 +3527,13 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AE3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AF3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG3" s="2">
         <v>45028</v>
@@ -3524,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="AN3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AO3" t="s">
         <v>85</v>
@@ -3542,25 +3572,25 @@
         <v>9847012345</v>
       </c>
       <c r="AT3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AU3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AV3" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AW3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AX3" t="b">
         <v>0</v>
       </c>
       <c r="AY3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BA3" t="b">
         <v>1</v>
@@ -3569,16 +3599,16 @@
         <v>0</v>
       </c>
       <c r="BC3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="BD3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="BE3" s="2">
         <v>45716</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG3" t="s">
         <v>87</v>
@@ -3632,10 +3662,10 @@
         <v>45421</v>
       </c>
       <c r="BX3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="BY3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ3" s="2">
         <v>45860</v>
@@ -3647,16 +3677,16 @@
         <v>81</v>
       </c>
       <c r="CC3" t="s">
+        <v>589</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>590</v>
+      </c>
+      <c r="CE3" t="s">
         <v>591</v>
       </c>
-      <c r="CD3" t="s">
-        <v>592</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>593</v>
-      </c>
       <c r="CF3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG3">
         <v>400053</v>
@@ -3665,7 +3695,7 @@
         <v>98</v>
       </c>
       <c r="CI3" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ3" t="s">
         <v>121</v>
@@ -3680,7 +3710,7 @@
         <v>124</v>
       </c>
       <c r="CN3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO3" t="s">
         <v>125</v>
@@ -3701,10 +3731,10 @@
         <v>97</v>
       </c>
       <c r="CU3" t="s">
-        <v>171</v>
+        <v>689</v>
       </c>
       <c r="CV3" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW3" s="5" t="s">
         <v>133</v>
@@ -3722,7 +3752,7 @@
         <v>131</v>
       </c>
       <c r="DB3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="DC3" t="s">
         <v>140</v>
@@ -3734,13 +3764,13 @@
         <v>32</v>
       </c>
       <c r="DF3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="DG3" s="9">
         <v>473910284756</v>
       </c>
       <c r="DH3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="DI3">
         <v>500001004</v>
@@ -3767,10 +3797,10 @@
         <v>32344</v>
       </c>
       <c r="DQ3" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR3" t="s">
         <v>172</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>173</v>
       </c>
       <c r="DS3">
         <v>9988776655</v>
@@ -3782,7 +3812,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW3" t="s">
         <v>96</v>
@@ -3805,25 +3835,28 @@
       <c r="EC3">
         <v>156</v>
       </c>
+      <c r="ED3" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="4" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G4" t="s">
         <v>74</v>
@@ -3844,7 +3877,7 @@
         <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O4" t="s">
         <v>80</v>
@@ -3865,16 +3898,16 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="W4" s="9">
         <v>456712348901</v>
       </c>
       <c r="X4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Y4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z4" t="s">
         <v>82</v>
@@ -3886,13 +3919,13 @@
         <v>1</v>
       </c>
       <c r="AD4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AE4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AF4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG4" s="2">
         <v>45678</v>
@@ -3904,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AK4" s="8" t="s">
         <v>83</v>
@@ -3916,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="AN4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AO4" t="s">
         <v>85</v>
@@ -3934,25 +3967,25 @@
         <v>7736088990</v>
       </c>
       <c r="AT4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AU4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AW4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AX4" t="b">
         <v>0</v>
       </c>
       <c r="AY4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BA4" t="b">
         <v>1</v>
@@ -3961,16 +3994,16 @@
         <v>0</v>
       </c>
       <c r="BC4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BD4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BE4" s="2">
         <v>45731</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG4" t="s">
         <v>87</v>
@@ -4024,10 +4057,10 @@
         <v>45422</v>
       </c>
       <c r="BX4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="BY4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ4" s="2">
         <v>45423</v>
@@ -4039,16 +4072,16 @@
         <v>81</v>
       </c>
       <c r="CC4" t="s">
+        <v>592</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>593</v>
+      </c>
+      <c r="CE4" t="s">
         <v>594</v>
       </c>
-      <c r="CD4" t="s">
-        <v>595</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>596</v>
-      </c>
       <c r="CF4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG4">
         <v>400089</v>
@@ -4057,7 +4090,7 @@
         <v>98</v>
       </c>
       <c r="CI4" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ4" t="s">
         <v>121</v>
@@ -4072,7 +4105,7 @@
         <v>124</v>
       </c>
       <c r="CN4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO4" t="s">
         <v>125</v>
@@ -4093,10 +4126,10 @@
         <v>97</v>
       </c>
       <c r="CU4" t="s">
-        <v>171</v>
+        <v>690</v>
       </c>
       <c r="CV4" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW4" s="5" t="s">
         <v>133</v>
@@ -4114,7 +4147,7 @@
         <v>131</v>
       </c>
       <c r="DB4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="DC4" t="s">
         <v>139</v>
@@ -4126,13 +4159,13 @@
         <v>32</v>
       </c>
       <c r="DF4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DG4">
         <v>109283746501</v>
       </c>
       <c r="DH4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="DI4">
         <v>500001004</v>
@@ -4159,10 +4192,10 @@
         <v>32345</v>
       </c>
       <c r="DQ4" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR4" t="s">
         <v>172</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>173</v>
       </c>
       <c r="DS4">
         <v>9988776655</v>
@@ -4174,7 +4207,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW4" t="s">
         <v>96</v>
@@ -4197,25 +4230,28 @@
       <c r="EC4">
         <v>156</v>
       </c>
+      <c r="ED4" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="5" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -4236,7 +4272,7 @@
         <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O5" t="s">
         <v>80</v>
@@ -4257,16 +4293,16 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="W5" s="9">
         <v>773200193345</v>
       </c>
       <c r="X5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Y5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Z5" t="s">
         <v>82</v>
@@ -4278,13 +4314,13 @@
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AE5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AF5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG5" s="2">
         <v>44530</v>
@@ -4305,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="AN5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO5" t="s">
         <v>85</v>
@@ -4323,25 +4359,25 @@
         <v>6235109876</v>
       </c>
       <c r="AT5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AU5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AV5" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AW5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AX5" t="b">
         <v>0</v>
       </c>
       <c r="AY5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="BA5" t="b">
         <v>1</v>
@@ -4350,16 +4386,16 @@
         <v>0</v>
       </c>
       <c r="BC5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BD5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BE5" s="2">
         <v>45750</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG5" t="s">
         <v>87</v>
@@ -4413,10 +4449,10 @@
         <v>45423</v>
       </c>
       <c r="BX5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="BY5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ5" s="2">
         <v>45663</v>
@@ -4428,16 +4464,16 @@
         <v>81</v>
       </c>
       <c r="CC5" t="s">
+        <v>595</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>596</v>
+      </c>
+      <c r="CE5" t="s">
         <v>597</v>
       </c>
-      <c r="CD5" t="s">
-        <v>598</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>599</v>
-      </c>
       <c r="CF5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG5">
         <v>400028</v>
@@ -4446,7 +4482,7 @@
         <v>98</v>
       </c>
       <c r="CI5" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ5" t="s">
         <v>121</v>
@@ -4461,7 +4497,7 @@
         <v>124</v>
       </c>
       <c r="CN5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO5" t="s">
         <v>125</v>
@@ -4482,10 +4518,10 @@
         <v>97</v>
       </c>
       <c r="CU5" t="s">
-        <v>171</v>
+        <v>691</v>
       </c>
       <c r="CV5" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW5" s="5" t="s">
         <v>133</v>
@@ -4503,7 +4539,7 @@
         <v>131</v>
       </c>
       <c r="DB5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="DC5" t="s">
         <v>139</v>
@@ -4515,13 +4551,13 @@
         <v>32</v>
       </c>
       <c r="DF5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DG5">
         <v>556473829102</v>
       </c>
       <c r="DH5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="DI5">
         <v>500001004</v>
@@ -4548,10 +4584,10 @@
         <v>32346</v>
       </c>
       <c r="DQ5" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR5" t="s">
         <v>172</v>
-      </c>
-      <c r="DR5" t="s">
-        <v>173</v>
       </c>
       <c r="DS5">
         <v>9988776655</v>
@@ -4563,7 +4599,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW5" t="s">
         <v>96</v>
@@ -4586,25 +4622,28 @@
       <c r="EC5">
         <v>156</v>
       </c>
+      <c r="ED5" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="6" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -4625,7 +4664,7 @@
         <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O6" t="s">
         <v>80</v>
@@ -4646,16 +4685,16 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="W6" s="9">
         <v>109855672210</v>
       </c>
       <c r="X6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Z6" t="s">
         <v>82</v>
@@ -4667,13 +4706,13 @@
         <v>1</v>
       </c>
       <c r="AD6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AE6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AF6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG6" s="2">
         <v>45488</v>
@@ -4694,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="AN6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO6" t="s">
         <v>85</v>
@@ -4712,25 +4751,25 @@
         <v>9447056789</v>
       </c>
       <c r="AT6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AU6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AV6" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AW6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AX6" t="b">
         <v>0</v>
       </c>
       <c r="AY6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BA6" t="b">
         <v>1</v>
@@ -4739,16 +4778,16 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BD6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="BE6" s="2">
         <v>45769</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG6" t="s">
         <v>87</v>
@@ -4802,10 +4841,10 @@
         <v>45424</v>
       </c>
       <c r="BX6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="BY6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ6" s="2">
         <v>45501</v>
@@ -4817,16 +4856,16 @@
         <v>81</v>
       </c>
       <c r="CC6" t="s">
+        <v>598</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>599</v>
+      </c>
+      <c r="CE6" t="s">
         <v>600</v>
       </c>
-      <c r="CD6" t="s">
-        <v>601</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>602</v>
-      </c>
       <c r="CF6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG6">
         <v>400030</v>
@@ -4835,7 +4874,7 @@
         <v>98</v>
       </c>
       <c r="CI6" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ6" t="s">
         <v>121</v>
@@ -4850,7 +4889,7 @@
         <v>124</v>
       </c>
       <c r="CN6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO6" t="s">
         <v>125</v>
@@ -4871,10 +4910,10 @@
         <v>97</v>
       </c>
       <c r="CU6" t="s">
-        <v>171</v>
+        <v>692</v>
       </c>
       <c r="CV6" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW6" s="5" t="s">
         <v>133</v>
@@ -4892,7 +4931,7 @@
         <v>131</v>
       </c>
       <c r="DB6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="DC6" t="s">
         <v>142</v>
@@ -4904,13 +4943,13 @@
         <v>32</v>
       </c>
       <c r="DF6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="DG6">
         <v>901827364519</v>
       </c>
       <c r="DH6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="DI6">
         <v>500001004</v>
@@ -4937,10 +4976,10 @@
         <v>32347</v>
       </c>
       <c r="DQ6" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR6" t="s">
         <v>172</v>
-      </c>
-      <c r="DR6" t="s">
-        <v>173</v>
       </c>
       <c r="DS6">
         <v>9988776655</v>
@@ -4952,7 +4991,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW6" t="s">
         <v>96</v>
@@ -4975,25 +5014,28 @@
       <c r="EC6">
         <v>156</v>
       </c>
+      <c r="ED6" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="7" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G7" t="s">
         <v>74</v>
@@ -5014,7 +5056,7 @@
         <v>78</v>
       </c>
       <c r="N7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O7" t="s">
         <v>80</v>
@@ -5035,16 +5077,16 @@
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="W7" s="9">
         <v>654399871123</v>
       </c>
       <c r="X7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Y7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Z7" t="s">
         <v>82</v>
@@ -5056,13 +5098,13 @@
         <v>1</v>
       </c>
       <c r="AD7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AE7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AF7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG7" s="2">
         <v>46297</v>
@@ -5083,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="AN7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AO7" t="s">
         <v>85</v>
@@ -5101,25 +5143,25 @@
         <v>8547123456</v>
       </c>
       <c r="AT7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AV7" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AW7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AX7" t="b">
         <v>0</v>
       </c>
       <c r="AY7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="BA7" t="b">
         <v>1</v>
@@ -5128,16 +5170,16 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="BD7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BE7" s="2">
         <v>45787</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG7" t="s">
         <v>87</v>
@@ -5191,10 +5233,10 @@
         <v>45425</v>
       </c>
       <c r="BX7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="BY7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ7" s="2">
         <v>45826</v>
@@ -5206,16 +5248,16 @@
         <v>81</v>
       </c>
       <c r="CC7" t="s">
+        <v>601</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>602</v>
+      </c>
+      <c r="CE7" t="s">
         <v>603</v>
       </c>
-      <c r="CD7" t="s">
-        <v>604</v>
-      </c>
-      <c r="CE7" t="s">
-        <v>605</v>
-      </c>
       <c r="CF7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG7">
         <v>400030</v>
@@ -5224,7 +5266,7 @@
         <v>98</v>
       </c>
       <c r="CI7" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ7" t="s">
         <v>121</v>
@@ -5239,7 +5281,7 @@
         <v>124</v>
       </c>
       <c r="CN7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO7" t="s">
         <v>125</v>
@@ -5260,10 +5302,10 @@
         <v>97</v>
       </c>
       <c r="CU7" t="s">
-        <v>171</v>
+        <v>693</v>
       </c>
       <c r="CV7" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW7" s="5" t="s">
         <v>133</v>
@@ -5281,7 +5323,7 @@
         <v>131</v>
       </c>
       <c r="DB7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="DC7" t="s">
         <v>141</v>
@@ -5293,13 +5335,13 @@
         <v>32</v>
       </c>
       <c r="DF7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="DG7">
         <v>234567890123</v>
       </c>
       <c r="DH7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="DI7">
         <v>500001004</v>
@@ -5326,10 +5368,10 @@
         <v>32348</v>
       </c>
       <c r="DQ7" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR7" t="s">
         <v>172</v>
-      </c>
-      <c r="DR7" t="s">
-        <v>173</v>
       </c>
       <c r="DS7">
         <v>9988776655</v>
@@ -5341,7 +5383,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW7" t="s">
         <v>96</v>
@@ -5364,25 +5406,28 @@
       <c r="EC7">
         <v>156</v>
       </c>
+      <c r="ED7" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="8" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
         <v>73</v>
@@ -5403,7 +5448,7 @@
         <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O8" t="s">
         <v>80</v>
@@ -5424,16 +5469,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W8" s="9">
         <v>334566784456</v>
       </c>
       <c r="X8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Y8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Z8" t="s">
         <v>82</v>
@@ -5445,13 +5490,13 @@
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AE8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AF8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG8" s="2">
         <v>43912</v>
@@ -5472,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="AN8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO8" t="s">
         <v>85</v>
@@ -5490,25 +5535,25 @@
         <v>7025034567</v>
       </c>
       <c r="AT8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AU8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AW8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AX8" t="b">
         <v>0</v>
       </c>
       <c r="AY8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BA8" t="b">
         <v>1</v>
@@ -5517,16 +5562,16 @@
         <v>0</v>
       </c>
       <c r="BC8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="BD8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BE8" s="2">
         <v>45815</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG8" t="s">
         <v>87</v>
@@ -5580,10 +5625,10 @@
         <v>45426</v>
       </c>
       <c r="BX8" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="BY8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ8" s="2">
         <v>45907</v>
@@ -5595,13 +5640,13 @@
         <v>81</v>
       </c>
       <c r="CC8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="CE8" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="CF8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG8">
         <v>400077</v>
@@ -5610,7 +5655,7 @@
         <v>98</v>
       </c>
       <c r="CI8" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ8" t="s">
         <v>121</v>
@@ -5625,7 +5670,7 @@
         <v>124</v>
       </c>
       <c r="CN8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO8" t="s">
         <v>125</v>
@@ -5646,10 +5691,10 @@
         <v>97</v>
       </c>
       <c r="CU8" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV8" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW8" s="5" t="s">
         <v>133</v>
@@ -5667,7 +5712,7 @@
         <v>131</v>
       </c>
       <c r="DB8" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="DC8" t="s">
         <v>140</v>
@@ -5679,13 +5724,13 @@
         <v>32</v>
       </c>
       <c r="DF8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="DG8">
         <v>678901234567</v>
       </c>
       <c r="DH8" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="DI8">
         <v>500001004</v>
@@ -5712,10 +5757,10 @@
         <v>32349</v>
       </c>
       <c r="DQ8" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR8" t="s">
         <v>172</v>
-      </c>
-      <c r="DR8" t="s">
-        <v>173</v>
       </c>
       <c r="DS8">
         <v>9988776655</v>
@@ -5727,7 +5772,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW8" t="s">
         <v>96</v>
@@ -5750,25 +5795,28 @@
       <c r="EC8">
         <v>156</v>
       </c>
+      <c r="ED8" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="9" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
         <v>74</v>
@@ -5789,7 +5837,7 @@
         <v>78</v>
       </c>
       <c r="N9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O9" t="s">
         <v>80</v>
@@ -5810,16 +5858,16 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="W9" s="9">
         <v>901233456789</v>
       </c>
       <c r="X9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Y9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Z9" t="s">
         <v>82</v>
@@ -5831,13 +5879,13 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AE9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG9" s="2">
         <v>44792</v>
@@ -5858,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="AN9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AO9" t="s">
         <v>85</v>
@@ -5876,25 +5924,25 @@
         <v>6365045678</v>
       </c>
       <c r="AT9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AU9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AV9" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AW9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AX9" t="b">
         <v>0</v>
       </c>
       <c r="AY9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BA9" t="b">
         <v>1</v>
@@ -5903,16 +5951,16 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BD9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="BE9" s="2">
         <v>45833</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG9" t="s">
         <v>87</v>
@@ -5966,10 +6014,10 @@
         <v>45427</v>
       </c>
       <c r="BX9" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="BY9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ9" s="2">
         <v>45476</v>
@@ -5981,16 +6029,16 @@
         <v>81</v>
       </c>
       <c r="CC9" t="s">
+        <v>606</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>607</v>
+      </c>
+      <c r="CE9" t="s">
         <v>608</v>
       </c>
-      <c r="CD9" t="s">
-        <v>609</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>610</v>
-      </c>
       <c r="CF9" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG9">
         <v>400049</v>
@@ -5999,7 +6047,7 @@
         <v>98</v>
       </c>
       <c r="CI9" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ9" t="s">
         <v>121</v>
@@ -6014,7 +6062,7 @@
         <v>124</v>
       </c>
       <c r="CN9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO9" t="s">
         <v>125</v>
@@ -6035,10 +6083,10 @@
         <v>97</v>
       </c>
       <c r="CU9" t="s">
-        <v>171</v>
+        <v>689</v>
       </c>
       <c r="CV9" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW9" s="5" t="s">
         <v>133</v>
@@ -6056,7 +6104,7 @@
         <v>131</v>
       </c>
       <c r="DB9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="DC9" t="s">
         <v>139</v>
@@ -6068,13 +6116,13 @@
         <v>32</v>
       </c>
       <c r="DF9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="DG9">
         <v>345678901234</v>
       </c>
       <c r="DH9" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="DI9">
         <v>500001004</v>
@@ -6101,10 +6149,10 @@
         <v>32350</v>
       </c>
       <c r="DQ9" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR9" t="s">
         <v>172</v>
-      </c>
-      <c r="DR9" t="s">
-        <v>173</v>
       </c>
       <c r="DS9">
         <v>9988776655</v>
@@ -6116,7 +6164,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW9" t="s">
         <v>96</v>
@@ -6139,25 +6187,28 @@
       <c r="EC9">
         <v>156</v>
       </c>
+      <c r="ED9" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="10" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G10" t="s">
         <v>74</v>
@@ -6178,7 +6229,7 @@
         <v>78</v>
       </c>
       <c r="N10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O10" t="s">
         <v>80</v>
@@ -6199,16 +6250,16 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="W10" s="9">
         <v>556788901123</v>
       </c>
       <c r="X10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Y10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Z10" t="s">
         <v>82</v>
@@ -6220,13 +6271,13 @@
         <v>1</v>
       </c>
       <c r="AD10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AE10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AF10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG10" s="2">
         <v>45996</v>
@@ -6247,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO10" t="s">
         <v>85</v>
@@ -6265,25 +6316,25 @@
         <v>9946067890</v>
       </c>
       <c r="AT10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AU10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AV10" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AW10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AX10" t="b">
         <v>0</v>
       </c>
       <c r="AY10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BA10" t="b">
         <v>1</v>
@@ -6292,16 +6343,16 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BD10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BE10" s="2">
         <v>45857</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG10" t="s">
         <v>88</v>
@@ -6352,10 +6403,10 @@
         <v>45428</v>
       </c>
       <c r="BX10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="BY10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ10" s="2">
         <v>45833</v>
@@ -6367,16 +6418,16 @@
         <v>81</v>
       </c>
       <c r="CC10" t="s">
+        <v>609</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>610</v>
+      </c>
+      <c r="CE10" t="s">
         <v>611</v>
       </c>
-      <c r="CD10" t="s">
-        <v>612</v>
-      </c>
-      <c r="CE10" t="s">
-        <v>613</v>
-      </c>
       <c r="CF10" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG10">
         <v>400049</v>
@@ -6385,7 +6436,7 @@
         <v>98</v>
       </c>
       <c r="CI10" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ10" t="s">
         <v>121</v>
@@ -6400,7 +6451,7 @@
         <v>124</v>
       </c>
       <c r="CN10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO10" t="s">
         <v>125</v>
@@ -6421,10 +6472,10 @@
         <v>97</v>
       </c>
       <c r="CU10" t="s">
-        <v>171</v>
+        <v>690</v>
       </c>
       <c r="CV10" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW10" s="5" t="s">
         <v>133</v>
@@ -6442,7 +6493,7 @@
         <v>131</v>
       </c>
       <c r="DB10" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="DC10" t="s">
         <v>139</v>
@@ -6454,13 +6505,13 @@
         <v>32</v>
       </c>
       <c r="DF10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="DG10">
         <v>890123456789</v>
       </c>
       <c r="DH10" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="DI10">
         <v>500001004</v>
@@ -6487,10 +6538,10 @@
         <v>32351</v>
       </c>
       <c r="DQ10" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR10" t="s">
         <v>172</v>
-      </c>
-      <c r="DR10" t="s">
-        <v>173</v>
       </c>
       <c r="DS10">
         <v>9988776655</v>
@@ -6502,7 +6553,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW10" t="s">
         <v>96</v>
@@ -6525,25 +6576,28 @@
       <c r="EC10">
         <v>156</v>
       </c>
+      <c r="ED10" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="11" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G11" t="s">
         <v>74</v>
@@ -6564,7 +6618,7 @@
         <v>78</v>
       </c>
       <c r="N11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O11" t="s">
         <v>80</v>
@@ -6585,16 +6639,16 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="W11" s="9">
         <v>223455678890</v>
       </c>
       <c r="X11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Y11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Z11" t="s">
         <v>82</v>
@@ -6606,13 +6660,13 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AE11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AF11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG11" s="2">
         <v>45105</v>
@@ -6633,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="AN11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AO11" t="s">
         <v>85</v>
@@ -6651,25 +6705,25 @@
         <v>8891078901</v>
       </c>
       <c r="AT11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AU11" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AW11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AX11" t="b">
         <v>0</v>
       </c>
       <c r="AY11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="BA11" t="b">
         <v>1</v>
@@ -6678,16 +6732,16 @@
         <v>0</v>
       </c>
       <c r="BC11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="BD11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BE11" s="2">
         <v>45870</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG11" t="s">
         <v>88</v>
@@ -6738,10 +6792,10 @@
         <v>45429</v>
       </c>
       <c r="BX11" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BY11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ11" s="2">
         <v>45394</v>
@@ -6753,16 +6807,16 @@
         <v>81</v>
       </c>
       <c r="CC11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="CD11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="CE11" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="CF11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG11">
         <v>400049</v>
@@ -6771,7 +6825,7 @@
         <v>98</v>
       </c>
       <c r="CI11" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ11" t="s">
         <v>121</v>
@@ -6786,7 +6840,7 @@
         <v>124</v>
       </c>
       <c r="CN11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO11" t="s">
         <v>125</v>
@@ -6807,10 +6861,10 @@
         <v>97</v>
       </c>
       <c r="CU11" t="s">
-        <v>171</v>
+        <v>691</v>
       </c>
       <c r="CV11" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW11" s="5" t="s">
         <v>133</v>
@@ -6828,7 +6882,7 @@
         <v>131</v>
       </c>
       <c r="DB11" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="DC11" t="s">
         <v>142</v>
@@ -6840,13 +6894,13 @@
         <v>32</v>
       </c>
       <c r="DF11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DG11">
         <v>123456789012</v>
       </c>
       <c r="DH11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="DI11">
         <v>500001004</v>
@@ -6873,10 +6927,10 @@
         <v>32352</v>
       </c>
       <c r="DQ11" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR11" t="s">
         <v>172</v>
-      </c>
-      <c r="DR11" t="s">
-        <v>173</v>
       </c>
       <c r="DS11">
         <v>9988776655</v>
@@ -6888,7 +6942,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW11" t="s">
         <v>96</v>
@@ -6911,25 +6965,28 @@
       <c r="EC11">
         <v>156</v>
       </c>
+      <c r="ED11" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="12" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" t="s">
         <v>74</v>
@@ -6950,7 +7007,7 @@
         <v>79</v>
       </c>
       <c r="N12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O12" t="s">
         <v>80</v>
@@ -6971,16 +7028,16 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="W12" s="9">
         <v>889011234456</v>
       </c>
       <c r="X12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Z12" t="s">
         <v>82</v>
@@ -6992,13 +7049,13 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AE12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AF12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG12" s="2">
         <v>45336</v>
@@ -7019,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AO12" t="s">
         <v>85</v>
@@ -7037,25 +7094,25 @@
         <v>7558089012</v>
       </c>
       <c r="AT12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AU12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AV12" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AW12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AX12" t="b">
         <v>0</v>
       </c>
       <c r="AY12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BA12" t="b">
         <v>1</v>
@@ -7064,16 +7121,16 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BD12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BE12" s="2">
         <v>45886</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG12" t="s">
         <v>88</v>
@@ -7124,10 +7181,10 @@
         <v>45430</v>
       </c>
       <c r="BX12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="BY12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ12" s="2">
         <v>45700</v>
@@ -7139,16 +7196,16 @@
         <v>81</v>
       </c>
       <c r="CC12" t="s">
+        <v>614</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>615</v>
+      </c>
+      <c r="CE12" t="s">
         <v>616</v>
       </c>
-      <c r="CD12" t="s">
-        <v>617</v>
-      </c>
-      <c r="CE12" t="s">
-        <v>618</v>
-      </c>
       <c r="CF12" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG12">
         <v>400020</v>
@@ -7157,7 +7214,7 @@
         <v>98</v>
       </c>
       <c r="CI12" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ12" t="s">
         <v>121</v>
@@ -7172,7 +7229,7 @@
         <v>124</v>
       </c>
       <c r="CN12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO12" t="s">
         <v>125</v>
@@ -7193,10 +7250,10 @@
         <v>97</v>
       </c>
       <c r="CU12" t="s">
-        <v>171</v>
+        <v>692</v>
       </c>
       <c r="CV12" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW12" s="5" t="s">
         <v>133</v>
@@ -7214,7 +7271,7 @@
         <v>131</v>
       </c>
       <c r="DB12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="DC12" t="s">
         <v>141</v>
@@ -7226,13 +7283,13 @@
         <v>32</v>
       </c>
       <c r="DF12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="DG12">
         <v>778899001122</v>
       </c>
       <c r="DH12" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="DI12">
         <v>500001004</v>
@@ -7259,10 +7316,10 @@
         <v>32353</v>
       </c>
       <c r="DQ12" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR12" t="s">
         <v>172</v>
-      </c>
-      <c r="DR12" t="s">
-        <v>173</v>
       </c>
       <c r="DS12">
         <v>9988776655</v>
@@ -7274,7 +7331,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW12" t="s">
         <v>96</v>
@@ -7297,25 +7354,28 @@
       <c r="EC12">
         <v>156</v>
       </c>
+      <c r="ED12" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="13" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -7336,7 +7396,7 @@
         <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O13" t="s">
         <v>80</v>
@@ -7357,16 +7417,16 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="W13" s="9">
         <v>667899012234</v>
       </c>
       <c r="X13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Y13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Z13" t="s">
         <v>82</v>
@@ -7378,13 +7438,13 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AF13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG13" s="2">
         <v>44325</v>
@@ -7405,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="AN13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO13" t="s">
         <v>85</v>
@@ -7423,25 +7483,25 @@
         <v>6005090123</v>
       </c>
       <c r="AT13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AU13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AV13" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AW13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AX13" t="b">
         <v>0</v>
       </c>
       <c r="AY13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="BA13" t="b">
         <v>1</v>
@@ -7450,16 +7510,16 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BD13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="BE13" s="2">
         <v>45912</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG13" t="s">
         <v>88</v>
@@ -7510,10 +7570,10 @@
         <v>45431</v>
       </c>
       <c r="BX13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="BY13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ13" s="2">
         <v>45521</v>
@@ -7525,16 +7585,16 @@
         <v>81</v>
       </c>
       <c r="CC13" t="s">
+        <v>617</v>
+      </c>
+      <c r="CD13" t="s">
+        <v>618</v>
+      </c>
+      <c r="CE13" t="s">
         <v>619</v>
       </c>
-      <c r="CD13" t="s">
-        <v>620</v>
-      </c>
-      <c r="CE13" t="s">
-        <v>621</v>
-      </c>
       <c r="CF13" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG13">
         <v>400026</v>
@@ -7543,7 +7603,7 @@
         <v>98</v>
       </c>
       <c r="CI13" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ13" t="s">
         <v>121</v>
@@ -7558,7 +7618,7 @@
         <v>124</v>
       </c>
       <c r="CN13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO13" t="s">
         <v>125</v>
@@ -7579,10 +7639,10 @@
         <v>97</v>
       </c>
       <c r="CU13" t="s">
-        <v>171</v>
+        <v>693</v>
       </c>
       <c r="CV13" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW13" s="5" t="s">
         <v>133</v>
@@ -7600,7 +7660,7 @@
         <v>131</v>
       </c>
       <c r="DB13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="DC13" t="s">
         <v>140</v>
@@ -7612,13 +7672,13 @@
         <v>32</v>
       </c>
       <c r="DF13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="DG13">
         <v>445566778899</v>
       </c>
       <c r="DH13" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="DI13">
         <v>500001004</v>
@@ -7645,10 +7705,10 @@
         <v>32354</v>
       </c>
       <c r="DQ13" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR13" t="s">
         <v>172</v>
-      </c>
-      <c r="DR13" t="s">
-        <v>173</v>
       </c>
       <c r="DS13">
         <v>9988776655</v>
@@ -7660,7 +7720,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW13" t="s">
         <v>96</v>
@@ -7683,25 +7743,28 @@
       <c r="EC13">
         <v>156</v>
       </c>
+      <c r="ED13" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="14" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" t="s">
         <v>74</v>
@@ -7722,7 +7785,7 @@
         <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O14" t="s">
         <v>80</v>
@@ -7743,16 +7806,16 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="W14" s="9">
         <v>112344567789</v>
       </c>
       <c r="X14" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z14" t="s">
         <v>82</v>
@@ -7764,13 +7827,13 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AF14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG14" s="2">
         <v>46142</v>
@@ -7791,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="AN14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AO14" t="s">
         <v>85</v>
@@ -7809,25 +7872,25 @@
         <v>9037001234</v>
       </c>
       <c r="AT14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AU14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AV14" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AW14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AX14" t="b">
         <v>0</v>
       </c>
       <c r="AY14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="BA14" t="b">
         <v>1</v>
@@ -7836,16 +7899,16 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BD14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="BE14" s="2">
         <v>45930</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG14" t="s">
         <v>88</v>
@@ -7896,10 +7959,10 @@
         <v>45432</v>
       </c>
       <c r="BX14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="BY14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ14" s="2">
         <v>45837</v>
@@ -7911,16 +7974,16 @@
         <v>81</v>
       </c>
       <c r="CC14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="CD14" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="CE14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="CF14" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG14">
         <v>400053</v>
@@ -7929,7 +7992,7 @@
         <v>98</v>
       </c>
       <c r="CI14" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ14" t="s">
         <v>121</v>
@@ -7944,7 +8007,7 @@
         <v>124</v>
       </c>
       <c r="CN14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO14" t="s">
         <v>125</v>
@@ -7965,10 +8028,10 @@
         <v>97</v>
       </c>
       <c r="CU14" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV14" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW14" s="5" t="s">
         <v>133</v>
@@ -7986,7 +8049,7 @@
         <v>131</v>
       </c>
       <c r="DB14" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="DC14" t="s">
         <v>139</v>
@@ -7998,13 +8061,13 @@
         <v>32</v>
       </c>
       <c r="DF14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DG14">
         <v>990011223344</v>
       </c>
       <c r="DH14" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="DI14">
         <v>500001004</v>
@@ -8031,10 +8094,10 @@
         <v>32355</v>
       </c>
       <c r="DQ14" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR14" t="s">
         <v>172</v>
-      </c>
-      <c r="DR14" t="s">
-        <v>173</v>
       </c>
       <c r="DS14">
         <v>9988776655</v>
@@ -8046,7 +8109,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW14" t="s">
         <v>96</v>
@@ -8069,25 +8132,28 @@
       <c r="EC14">
         <v>156</v>
       </c>
+      <c r="ED14" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="15" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
         <v>74</v>
@@ -8108,7 +8174,7 @@
         <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O15" t="s">
         <v>80</v>
@@ -8129,16 +8195,16 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W15" s="9">
         <v>445677890012</v>
       </c>
       <c r="X15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Y15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z15" t="s">
         <v>82</v>
@@ -8150,13 +8216,13 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AE15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AF15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG15" s="2">
         <v>44176</v>
@@ -8177,7 +8243,7 @@
         <v>1</v>
       </c>
       <c r="AN15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO15" t="s">
         <v>85</v>
@@ -8195,25 +8261,25 @@
         <v>8301011223</v>
       </c>
       <c r="AT15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AU15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AV15" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AW15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AX15" t="b">
         <v>0</v>
       </c>
       <c r="AY15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="BA15" t="b">
         <v>1</v>
@@ -8222,16 +8288,16 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="BD15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="BE15" s="2">
         <v>45935</v>
       </c>
       <c r="BF15" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG15" t="s">
         <v>88</v>
@@ -8282,10 +8348,10 @@
         <v>45433</v>
       </c>
       <c r="BX15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="BY15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ15" s="2">
         <v>45656</v>
@@ -8297,13 +8363,13 @@
         <v>81</v>
       </c>
       <c r="CC15" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="CE15" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="CF15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG15">
         <v>400063</v>
@@ -8312,7 +8378,7 @@
         <v>98</v>
       </c>
       <c r="CI15" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ15" t="s">
         <v>121</v>
@@ -8327,7 +8393,7 @@
         <v>124</v>
       </c>
       <c r="CN15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO15" t="s">
         <v>125</v>
@@ -8348,10 +8414,10 @@
         <v>97</v>
       </c>
       <c r="CU15" t="s">
-        <v>171</v>
+        <v>689</v>
       </c>
       <c r="CV15" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW15" s="5" t="s">
         <v>133</v>
@@ -8369,7 +8435,7 @@
         <v>131</v>
       </c>
       <c r="DB15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="DC15" t="s">
         <v>139</v>
@@ -8381,13 +8447,13 @@
         <v>32</v>
       </c>
       <c r="DF15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="DG15">
         <v>223344556677</v>
       </c>
       <c r="DH15" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="DI15">
         <v>500001004</v>
@@ -8414,10 +8480,10 @@
         <v>32356</v>
       </c>
       <c r="DQ15" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR15" t="s">
         <v>172</v>
-      </c>
-      <c r="DR15" t="s">
-        <v>173</v>
       </c>
       <c r="DS15">
         <v>9988776655</v>
@@ -8429,7 +8495,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW15" t="s">
         <v>96</v>
@@ -8452,25 +8518,28 @@
       <c r="EC15">
         <v>156</v>
       </c>
+      <c r="ED15" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="16" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
@@ -8491,7 +8560,7 @@
         <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O16" t="s">
         <v>80</v>
@@ -8512,16 +8581,16 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="W16" s="9">
         <v>990122345567</v>
       </c>
       <c r="X16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z16" t="s">
         <v>82</v>
@@ -8533,13 +8602,13 @@
         <v>1</v>
       </c>
       <c r="AD16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AE16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AF16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG16" s="2">
         <v>44859</v>
@@ -8560,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="AN16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO16" t="s">
         <v>85</v>
@@ -8578,25 +8647,25 @@
         <v>7205022334</v>
       </c>
       <c r="AT16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AU16" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AV16" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AW16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AX16" t="b">
         <v>0</v>
       </c>
       <c r="AY16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="BA16" t="b">
         <v>1</v>
@@ -8605,16 +8674,16 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="BD16" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="BE16" s="2">
         <v>45951</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG16" t="s">
         <v>88</v>
@@ -8665,10 +8734,10 @@
         <v>45434</v>
       </c>
       <c r="BX16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="BY16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ16" s="2">
         <v>45819</v>
@@ -8680,16 +8749,16 @@
         <v>81</v>
       </c>
       <c r="CC16" t="s">
+        <v>624</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>625</v>
+      </c>
+      <c r="CE16" t="s">
         <v>626</v>
       </c>
-      <c r="CD16" t="s">
-        <v>627</v>
-      </c>
-      <c r="CE16" t="s">
-        <v>628</v>
-      </c>
       <c r="CF16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG16">
         <v>400070</v>
@@ -8698,7 +8767,7 @@
         <v>98</v>
       </c>
       <c r="CI16" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ16" t="s">
         <v>121</v>
@@ -8713,7 +8782,7 @@
         <v>124</v>
       </c>
       <c r="CN16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO16" t="s">
         <v>125</v>
@@ -8734,10 +8803,10 @@
         <v>97</v>
       </c>
       <c r="CU16" t="s">
-        <v>171</v>
+        <v>690</v>
       </c>
       <c r="CV16" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW16" s="5" t="s">
         <v>133</v>
@@ -8755,7 +8824,7 @@
         <v>131</v>
       </c>
       <c r="DB16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="DC16" t="s">
         <v>142</v>
@@ -8767,13 +8836,13 @@
         <v>32</v>
       </c>
       <c r="DF16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="DG16">
         <v>550066117722</v>
       </c>
       <c r="DH16" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="DI16">
         <v>500001004</v>
@@ -8800,10 +8869,10 @@
         <v>32357</v>
       </c>
       <c r="DQ16" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR16" t="s">
         <v>172</v>
-      </c>
-      <c r="DR16" t="s">
-        <v>173</v>
       </c>
       <c r="DS16">
         <v>9988776655</v>
@@ -8815,7 +8884,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW16" t="s">
         <v>96</v>
@@ -8838,25 +8907,28 @@
       <c r="EC16">
         <v>156</v>
       </c>
+      <c r="ED16" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -8877,7 +8949,7 @@
         <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O17" t="s">
         <v>80</v>
@@ -8898,16 +8970,16 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W17" s="9">
         <v>334566789901</v>
       </c>
       <c r="X17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Y17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Z17" t="s">
         <v>82</v>
@@ -8919,13 +8991,13 @@
         <v>1</v>
       </c>
       <c r="AD17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AF17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG17" s="2">
         <v>45845</v>
@@ -8946,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="AN17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AO17" t="s">
         <v>85</v>
@@ -8964,25 +9036,25 @@
         <v>6145033445</v>
       </c>
       <c r="AT17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AU17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AV17" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AW17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AX17" t="b">
         <v>0</v>
       </c>
       <c r="AY17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="BA17" t="b">
         <v>1</v>
@@ -8991,16 +9063,16 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="BD17" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="BE17" s="2">
         <v>45969</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG17" t="s">
         <v>89</v>
@@ -9051,10 +9123,10 @@
         <v>45435</v>
       </c>
       <c r="BX17" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="BY17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ17" s="2">
         <v>45306</v>
@@ -9066,13 +9138,13 @@
         <v>81</v>
       </c>
       <c r="CC17" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="CE17" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="CF17" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG17">
         <v>400077</v>
@@ -9081,7 +9153,7 @@
         <v>98</v>
       </c>
       <c r="CI17" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ17" t="s">
         <v>121</v>
@@ -9096,7 +9168,7 @@
         <v>124</v>
       </c>
       <c r="CN17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO17" t="s">
         <v>125</v>
@@ -9117,10 +9189,10 @@
         <v>97</v>
       </c>
       <c r="CU17" t="s">
-        <v>171</v>
+        <v>691</v>
       </c>
       <c r="CV17" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW17" s="5" t="s">
         <v>133</v>
@@ -9138,7 +9210,7 @@
         <v>131</v>
       </c>
       <c r="DB17" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="DC17" t="s">
         <v>141</v>
@@ -9150,13 +9222,13 @@
         <v>32</v>
       </c>
       <c r="DF17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="DG17">
         <v>883399440055</v>
       </c>
       <c r="DH17" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="DI17">
         <v>500001004</v>
@@ -9183,10 +9255,10 @@
         <v>32358</v>
       </c>
       <c r="DQ17" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR17" t="s">
         <v>172</v>
-      </c>
-      <c r="DR17" t="s">
-        <v>173</v>
       </c>
       <c r="DS17">
         <v>9988776655</v>
@@ -9198,7 +9270,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW17" t="s">
         <v>96</v>
@@ -9221,25 +9293,28 @@
       <c r="EC17">
         <v>156</v>
       </c>
+      <c r="ED17" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="18" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G18" t="s">
         <v>74</v>
@@ -9260,7 +9335,7 @@
         <v>79</v>
       </c>
       <c r="N18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O18" t="s">
         <v>80</v>
@@ -9281,16 +9356,16 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W18" s="9">
         <v>778900123345</v>
       </c>
       <c r="X18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Z18" t="s">
         <v>82</v>
@@ -9302,13 +9377,13 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AE18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AF18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG18" s="2">
         <v>45186</v>
@@ -9329,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="AN18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO18" t="s">
         <v>85</v>
@@ -9347,25 +9422,25 @@
         <v>9176044556</v>
       </c>
       <c r="AT18" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AU18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AW18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AX18" t="b">
         <v>0</v>
       </c>
       <c r="AY18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BA18" t="b">
         <v>1</v>
@@ -9374,16 +9449,16 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BD18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BE18" s="2">
         <v>45990</v>
       </c>
       <c r="BF18" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG18" t="s">
         <v>89</v>
@@ -9434,10 +9509,10 @@
         <v>45436</v>
       </c>
       <c r="BX18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="BY18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ18" s="2">
         <v>45726</v>
@@ -9449,16 +9524,16 @@
         <v>81</v>
       </c>
       <c r="CC18" t="s">
+        <v>629</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>630</v>
+      </c>
+      <c r="CE18" t="s">
         <v>631</v>
       </c>
-      <c r="CD18" t="s">
-        <v>632</v>
-      </c>
-      <c r="CE18" t="s">
-        <v>633</v>
-      </c>
       <c r="CF18" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG18">
         <v>400022</v>
@@ -9467,7 +9542,7 @@
         <v>98</v>
       </c>
       <c r="CI18" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ18" t="s">
         <v>121</v>
@@ -9482,7 +9557,7 @@
         <v>124</v>
       </c>
       <c r="CN18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO18" t="s">
         <v>125</v>
@@ -9503,10 +9578,10 @@
         <v>97</v>
       </c>
       <c r="CU18" t="s">
-        <v>171</v>
+        <v>692</v>
       </c>
       <c r="CV18" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW18" s="5" t="s">
         <v>133</v>
@@ -9524,7 +9599,7 @@
         <v>131</v>
       </c>
       <c r="DB18" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="DC18" t="s">
         <v>140</v>
@@ -9536,13 +9611,13 @@
         <v>32</v>
       </c>
       <c r="DF18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="DG18">
         <v>116622773388</v>
       </c>
       <c r="DH18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="DI18">
         <v>500001004</v>
@@ -9569,10 +9644,10 @@
         <v>32359</v>
       </c>
       <c r="DQ18" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR18" t="s">
         <v>172</v>
-      </c>
-      <c r="DR18" t="s">
-        <v>173</v>
       </c>
       <c r="DS18">
         <v>9988776655</v>
@@ -9584,7 +9659,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW18" t="s">
         <v>96</v>
@@ -9607,25 +9682,28 @@
       <c r="EC18">
         <v>156</v>
       </c>
+      <c r="ED18" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="19" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G19" t="s">
         <v>74</v>
@@ -9646,7 +9724,7 @@
         <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O19" t="s">
         <v>80</v>
@@ -9667,16 +9745,16 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W19" s="9">
         <v>1233456678</v>
       </c>
       <c r="X19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z19" t="s">
         <v>82</v>
@@ -9688,13 +9766,13 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AE19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AF19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG19" s="2">
         <v>45616</v>
@@ -9715,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="AN19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO19" t="s">
         <v>85</v>
@@ -9733,25 +9811,25 @@
         <v>8606055667</v>
       </c>
       <c r="AT19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AU19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AV19" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AW19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AX19" t="b">
         <v>0</v>
       </c>
       <c r="AY19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="BA19" t="b">
         <v>1</v>
@@ -9760,16 +9838,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BD19" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="BE19" s="2">
         <v>45995</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG19" t="s">
         <v>89</v>
@@ -9820,10 +9898,10 @@
         <v>45437</v>
       </c>
       <c r="BX19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="BY19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ19" s="2">
         <v>45556</v>
@@ -9835,16 +9913,16 @@
         <v>81</v>
       </c>
       <c r="CC19" t="s">
+        <v>632</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>633</v>
+      </c>
+      <c r="CE19" t="s">
         <v>634</v>
       </c>
-      <c r="CD19" t="s">
-        <v>635</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>636</v>
-      </c>
       <c r="CF19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG19">
         <v>400005</v>
@@ -9853,7 +9931,7 @@
         <v>98</v>
       </c>
       <c r="CI19" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ19" t="s">
         <v>121</v>
@@ -9868,7 +9946,7 @@
         <v>124</v>
       </c>
       <c r="CN19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO19" t="s">
         <v>125</v>
@@ -9889,10 +9967,10 @@
         <v>97</v>
       </c>
       <c r="CU19" t="s">
-        <v>171</v>
+        <v>693</v>
       </c>
       <c r="CV19" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW19" s="5" t="s">
         <v>133</v>
@@ -9910,7 +9988,7 @@
         <v>131</v>
       </c>
       <c r="DB19" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="DC19" t="s">
         <v>139</v>
@@ -9922,13 +10000,13 @@
         <v>32</v>
       </c>
       <c r="DF19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="DG19">
         <v>661177228833</v>
       </c>
       <c r="DH19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="DI19">
         <v>500001004</v>
@@ -9955,10 +10033,10 @@
         <v>32360</v>
       </c>
       <c r="DQ19" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR19" t="s">
         <v>172</v>
-      </c>
-      <c r="DR19" t="s">
-        <v>173</v>
       </c>
       <c r="DS19">
         <v>9988776655</v>
@@ -9970,7 +10048,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW19" t="s">
         <v>96</v>
@@ -9993,25 +10071,28 @@
       <c r="EC19">
         <v>156</v>
       </c>
+      <c r="ED19" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="20" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
         <v>74</v>
@@ -10032,7 +10113,7 @@
         <v>79</v>
       </c>
       <c r="N20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O20" t="s">
         <v>80</v>
@@ -10053,16 +10134,16 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W20" s="9">
         <v>556788901123</v>
       </c>
       <c r="X20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z20" t="s">
         <v>82</v>
@@ -10074,13 +10155,13 @@
         <v>1</v>
       </c>
       <c r="AD20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AE20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AF20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG20" s="2">
         <v>44200</v>
@@ -10101,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="AN20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO20" t="s">
         <v>85</v>
@@ -10119,25 +10200,25 @@
         <v>7845066778</v>
       </c>
       <c r="AT20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AU20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AV20" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AW20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AX20" t="b">
         <v>0</v>
       </c>
       <c r="AY20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BA20" t="b">
         <v>1</v>
@@ -10146,16 +10227,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="BD20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BE20" s="2">
         <v>46007</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG20" t="s">
         <v>89</v>
@@ -10206,10 +10287,10 @@
         <v>45438</v>
       </c>
       <c r="BX20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BY20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ20" s="2">
         <v>45965</v>
@@ -10221,13 +10302,13 @@
         <v>81</v>
       </c>
       <c r="CC20" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="CD20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="CF20" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG20">
         <v>400006</v>
@@ -10236,7 +10317,7 @@
         <v>98</v>
       </c>
       <c r="CI20" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ20" t="s">
         <v>121</v>
@@ -10251,7 +10332,7 @@
         <v>124</v>
       </c>
       <c r="CN20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO20" t="s">
         <v>125</v>
@@ -10272,10 +10353,10 @@
         <v>97</v>
       </c>
       <c r="CU20" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV20" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW20" s="5" t="s">
         <v>133</v>
@@ -10293,7 +10374,7 @@
         <v>131</v>
       </c>
       <c r="DB20" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="DC20" t="s">
         <v>139</v>
@@ -10305,13 +10386,13 @@
         <v>32</v>
       </c>
       <c r="DF20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="DG20">
         <v>338844995500</v>
       </c>
       <c r="DH20" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="DI20">
         <v>500001004</v>
@@ -10338,10 +10419,10 @@
         <v>32361</v>
       </c>
       <c r="DQ20" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR20" t="s">
         <v>172</v>
-      </c>
-      <c r="DR20" t="s">
-        <v>173</v>
       </c>
       <c r="DS20">
         <v>9988776655</v>
@@ -10353,7 +10434,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW20" t="s">
         <v>96</v>
@@ -10376,25 +10457,28 @@
       <c r="EC20">
         <v>156</v>
       </c>
+      <c r="ED20" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="21" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G21" t="s">
         <v>74</v>
@@ -10415,7 +10499,7 @@
         <v>79</v>
       </c>
       <c r="N21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O21" t="s">
         <v>80</v>
@@ -10436,16 +10520,16 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="W21" s="9">
         <v>889011234456</v>
       </c>
       <c r="X21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Z21" t="s">
         <v>82</v>
@@ -10457,13 +10541,13 @@
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AE21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AF21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG21" s="2">
         <v>46235</v>
@@ -10484,7 +10568,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AO21" t="s">
         <v>85</v>
@@ -10502,25 +10586,25 @@
         <v>6282077889</v>
       </c>
       <c r="AT21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AU21" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AV21" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AW21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AX21" t="b">
         <v>0</v>
       </c>
       <c r="AY21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="BA21" t="b">
         <v>1</v>
@@ -10529,16 +10613,16 @@
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="BD21" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="BE21" s="2">
         <v>46022</v>
       </c>
       <c r="BF21" s="2" t="s">
-        <v>565</v>
+        <v>697</v>
       </c>
       <c r="BG21" t="s">
         <v>89</v>
@@ -10589,10 +10673,10 @@
         <v>45439</v>
       </c>
       <c r="BX21" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="BY21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ21" s="2">
         <v>45596</v>
@@ -10604,22 +10688,22 @@
         <v>81</v>
       </c>
       <c r="CC21" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="CE21" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="CF21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="CH21" t="s">
         <v>98</v>
       </c>
       <c r="CI21" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ21" t="s">
         <v>121</v>
@@ -10634,7 +10718,7 @@
         <v>124</v>
       </c>
       <c r="CN21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO21" t="s">
         <v>125</v>
@@ -10655,10 +10739,10 @@
         <v>97</v>
       </c>
       <c r="CU21" t="s">
-        <v>171</v>
+        <v>689</v>
       </c>
       <c r="CV21" t="s">
-        <v>96</v>
+        <v>696</v>
       </c>
       <c r="CW21" s="5" t="s">
         <v>133</v>
@@ -10676,7 +10760,7 @@
         <v>131</v>
       </c>
       <c r="DB21" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="DC21" t="s">
         <v>142</v>
@@ -10688,13 +10772,13 @@
         <v>32</v>
       </c>
       <c r="DF21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="DG21">
         <v>994400551166</v>
       </c>
       <c r="DH21" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="DI21">
         <v>500001004</v>
@@ -10721,10 +10805,10 @@
         <v>32362</v>
       </c>
       <c r="DQ21" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR21" t="s">
         <v>172</v>
-      </c>
-      <c r="DR21" t="s">
-        <v>173</v>
       </c>
       <c r="DS21">
         <v>9988776655</v>
@@ -10736,7 +10820,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW21" t="s">
         <v>96</v>
@@ -10759,8 +10843,11 @@
       <c r="EC21">
         <v>156</v>
       </c>
+      <c r="ED21" t="s">
+        <v>695</v>
+      </c>
     </row>
-    <row r="22" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:134" x14ac:dyDescent="0.35">
       <c r="DD22">
         <v>70</v>
       </c>
@@ -10768,13 +10855,13 @@
         <v>32</v>
       </c>
       <c r="DF22" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="DG22">
         <v>338844925500</v>
       </c>
       <c r="DH22" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="DI22">
         <v>500001004</v>
@@ -10801,10 +10888,10 @@
         <v>32363</v>
       </c>
       <c r="DQ22" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR22" t="s">
         <v>172</v>
-      </c>
-      <c r="DR22" t="s">
-        <v>173</v>
       </c>
       <c r="DS22">
         <v>9988776655</v>
@@ -10816,7 +10903,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW22" t="s">
         <v>96</v>
@@ -10838,6 +10925,9 @@
       </c>
       <c r="EC22">
         <v>156</v>
+      </c>
+      <c r="ED22" t="s">
+        <v>695</v>
       </c>
     </row>
   </sheetData>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -2103,9 +2103,6 @@
     <t>Agent</t>
   </si>
   <si>
-    <t>Branch</t>
-  </si>
-  <si>
     <t>Katraj unit Office</t>
   </si>
   <si>
@@ -2113,6 +2110,9 @@
   </si>
   <si>
     <t>Health</t>
+  </si>
+  <si>
+    <t>BranchDesc</t>
   </si>
 </sst>
 </file>
@@ -2648,6 +2648,7 @@
     <col min="131" max="131" width="19" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="14" bestFit="1" customWidth="1"/>
     <col min="133" max="133" width="16" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:134" x14ac:dyDescent="0.35">
@@ -3051,7 +3052,7 @@
         <v>168</v>
       </c>
       <c r="ED1" s="3" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
     </row>
     <row r="2" spans="1:134" x14ac:dyDescent="0.35">
@@ -3216,7 +3217,7 @@
         <v>45671</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG2" t="s">
         <v>87</v>
@@ -3342,7 +3343,7 @@
         <v>688</v>
       </c>
       <c r="CV2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW2" s="5" t="s">
         <v>133</v>
@@ -3444,7 +3445,7 @@
         <v>156</v>
       </c>
       <c r="ED2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3" spans="1:134" x14ac:dyDescent="0.35">
@@ -3608,7 +3609,7 @@
         <v>45716</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG3" t="s">
         <v>87</v>
@@ -3734,7 +3735,7 @@
         <v>689</v>
       </c>
       <c r="CV3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW3" s="5" t="s">
         <v>133</v>
@@ -3836,7 +3837,7 @@
         <v>156</v>
       </c>
       <c r="ED3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:134" x14ac:dyDescent="0.35">
@@ -4003,7 +4004,7 @@
         <v>45731</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG4" t="s">
         <v>87</v>
@@ -4129,7 +4130,7 @@
         <v>690</v>
       </c>
       <c r="CV4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW4" s="5" t="s">
         <v>133</v>
@@ -4231,7 +4232,7 @@
         <v>156</v>
       </c>
       <c r="ED4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:134" x14ac:dyDescent="0.35">
@@ -4395,7 +4396,7 @@
         <v>45750</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG5" t="s">
         <v>87</v>
@@ -4521,7 +4522,7 @@
         <v>691</v>
       </c>
       <c r="CV5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW5" s="5" t="s">
         <v>133</v>
@@ -4623,7 +4624,7 @@
         <v>156</v>
       </c>
       <c r="ED5" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:134" x14ac:dyDescent="0.35">
@@ -4787,7 +4788,7 @@
         <v>45769</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG6" t="s">
         <v>87</v>
@@ -4913,7 +4914,7 @@
         <v>692</v>
       </c>
       <c r="CV6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW6" s="5" t="s">
         <v>133</v>
@@ -5015,7 +5016,7 @@
         <v>156</v>
       </c>
       <c r="ED6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:134" x14ac:dyDescent="0.35">
@@ -5179,7 +5180,7 @@
         <v>45787</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG7" t="s">
         <v>87</v>
@@ -5305,7 +5306,7 @@
         <v>693</v>
       </c>
       <c r="CV7" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW7" s="5" t="s">
         <v>133</v>
@@ -5407,7 +5408,7 @@
         <v>156</v>
       </c>
       <c r="ED7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="8" spans="1:134" x14ac:dyDescent="0.35">
@@ -5571,7 +5572,7 @@
         <v>45815</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG8" t="s">
         <v>87</v>
@@ -5694,7 +5695,7 @@
         <v>688</v>
       </c>
       <c r="CV8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW8" s="5" t="s">
         <v>133</v>
@@ -5796,7 +5797,7 @@
         <v>156</v>
       </c>
       <c r="ED8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:134" x14ac:dyDescent="0.35">
@@ -5960,7 +5961,7 @@
         <v>45833</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG9" t="s">
         <v>87</v>
@@ -6086,7 +6087,7 @@
         <v>689</v>
       </c>
       <c r="CV9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW9" s="5" t="s">
         <v>133</v>
@@ -6188,7 +6189,7 @@
         <v>156</v>
       </c>
       <c r="ED9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:134" x14ac:dyDescent="0.35">
@@ -6352,7 +6353,7 @@
         <v>45857</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG10" t="s">
         <v>88</v>
@@ -6475,7 +6476,7 @@
         <v>690</v>
       </c>
       <c r="CV10" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW10" s="5" t="s">
         <v>133</v>
@@ -6577,7 +6578,7 @@
         <v>156</v>
       </c>
       <c r="ED10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="11" spans="1:134" x14ac:dyDescent="0.35">
@@ -6741,7 +6742,7 @@
         <v>45870</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG11" t="s">
         <v>88</v>
@@ -6864,7 +6865,7 @@
         <v>691</v>
       </c>
       <c r="CV11" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW11" s="5" t="s">
         <v>133</v>
@@ -6966,7 +6967,7 @@
         <v>156</v>
       </c>
       <c r="ED11" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" spans="1:134" x14ac:dyDescent="0.35">
@@ -7130,7 +7131,7 @@
         <v>45886</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG12" t="s">
         <v>88</v>
@@ -7253,7 +7254,7 @@
         <v>692</v>
       </c>
       <c r="CV12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW12" s="5" t="s">
         <v>133</v>
@@ -7355,7 +7356,7 @@
         <v>156</v>
       </c>
       <c r="ED12" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="13" spans="1:134" x14ac:dyDescent="0.35">
@@ -7519,7 +7520,7 @@
         <v>45912</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG13" t="s">
         <v>88</v>
@@ -7642,7 +7643,7 @@
         <v>693</v>
       </c>
       <c r="CV13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW13" s="5" t="s">
         <v>133</v>
@@ -7744,7 +7745,7 @@
         <v>156</v>
       </c>
       <c r="ED13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" spans="1:134" x14ac:dyDescent="0.35">
@@ -7908,7 +7909,7 @@
         <v>45930</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG14" t="s">
         <v>88</v>
@@ -8031,7 +8032,7 @@
         <v>688</v>
       </c>
       <c r="CV14" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW14" s="5" t="s">
         <v>133</v>
@@ -8133,7 +8134,7 @@
         <v>156</v>
       </c>
       <c r="ED14" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="15" spans="1:134" x14ac:dyDescent="0.35">
@@ -8297,7 +8298,7 @@
         <v>45935</v>
       </c>
       <c r="BF15" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG15" t="s">
         <v>88</v>
@@ -8417,7 +8418,7 @@
         <v>689</v>
       </c>
       <c r="CV15" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW15" s="5" t="s">
         <v>133</v>
@@ -8519,7 +8520,7 @@
         <v>156</v>
       </c>
       <c r="ED15" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="16" spans="1:134" x14ac:dyDescent="0.35">
@@ -8683,7 +8684,7 @@
         <v>45951</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG16" t="s">
         <v>88</v>
@@ -8806,7 +8807,7 @@
         <v>690</v>
       </c>
       <c r="CV16" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW16" s="5" t="s">
         <v>133</v>
@@ -8908,7 +8909,7 @@
         <v>156</v>
       </c>
       <c r="ED16" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" spans="1:134" x14ac:dyDescent="0.35">
@@ -9072,7 +9073,7 @@
         <v>45969</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG17" t="s">
         <v>89</v>
@@ -9192,7 +9193,7 @@
         <v>691</v>
       </c>
       <c r="CV17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW17" s="5" t="s">
         <v>133</v>
@@ -9294,7 +9295,7 @@
         <v>156</v>
       </c>
       <c r="ED17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="18" spans="1:134" x14ac:dyDescent="0.35">
@@ -9458,7 +9459,7 @@
         <v>45990</v>
       </c>
       <c r="BF18" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG18" t="s">
         <v>89</v>
@@ -9581,7 +9582,7 @@
         <v>692</v>
       </c>
       <c r="CV18" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW18" s="5" t="s">
         <v>133</v>
@@ -9683,7 +9684,7 @@
         <v>156</v>
       </c>
       <c r="ED18" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="19" spans="1:134" x14ac:dyDescent="0.35">
@@ -9847,7 +9848,7 @@
         <v>45995</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG19" t="s">
         <v>89</v>
@@ -9970,7 +9971,7 @@
         <v>693</v>
       </c>
       <c r="CV19" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW19" s="5" t="s">
         <v>133</v>
@@ -10072,7 +10073,7 @@
         <v>156</v>
       </c>
       <c r="ED19" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="20" spans="1:134" x14ac:dyDescent="0.35">
@@ -10236,7 +10237,7 @@
         <v>46007</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG20" t="s">
         <v>89</v>
@@ -10356,7 +10357,7 @@
         <v>688</v>
       </c>
       <c r="CV20" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW20" s="5" t="s">
         <v>133</v>
@@ -10458,7 +10459,7 @@
         <v>156</v>
       </c>
       <c r="ED20" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="1:134" x14ac:dyDescent="0.35">
@@ -10622,7 +10623,7 @@
         <v>46022</v>
       </c>
       <c r="BF21" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="BG21" t="s">
         <v>89</v>
@@ -10742,7 +10743,7 @@
         <v>689</v>
       </c>
       <c r="CV21" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="CW21" s="5" t="s">
         <v>133</v>
@@ -10844,7 +10845,7 @@
         <v>156</v>
       </c>
       <c r="ED21" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:134" x14ac:dyDescent="0.35">
@@ -10927,7 +10928,7 @@
         <v>156</v>
       </c>
       <c r="ED22" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="690">
   <si>
     <t>AgentCode</t>
   </si>
@@ -534,6 +534,9 @@
     <t>Sales Executive</t>
   </si>
   <si>
+    <t>Branch Manager</t>
+  </si>
+  <si>
     <t>PQRST3456U</t>
   </si>
   <si>
@@ -1713,6 +1716,9 @@
     <t>AM25</t>
   </si>
   <si>
+    <t>Insurance</t>
+  </si>
+  <si>
     <t>LIC006</t>
   </si>
   <si>
@@ -2083,36 +2089,6 @@
   </si>
   <si>
     <t>NPSTrngCompletionDate</t>
-  </si>
-  <si>
-    <t>Unit Manager</t>
-  </si>
-  <si>
-    <t>Area Head</t>
-  </si>
-  <si>
-    <t>National Head</t>
-  </si>
-  <si>
-    <t>Zonal Head</t>
-  </si>
-  <si>
-    <t>Region Head</t>
-  </si>
-  <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>Katraj unit Office</t>
-  </si>
-  <si>
-    <t>Unit Office</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>BranchDesc</t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:ED22"/>
+  <dimension ref="A1:EC22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -2648,10 +2624,9 @@
     <col min="131" max="131" width="19" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="14" bestFit="1" customWidth="1"/>
     <col min="133" max="133" width="16" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2677,7 +2652,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -2719,7 +2694,7 @@
         <v>19</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
@@ -2833,7 +2808,7 @@
         <v>56</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>57</v>
@@ -2842,7 +2817,7 @@
         <v>58</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>59</v>
@@ -2860,10 +2835,10 @@
         <v>63</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="BT1" s="1" t="s">
         <v>64</v>
@@ -2905,7 +2880,7 @@
         <v>94</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>95</v>
@@ -3051,29 +3026,26 @@
       <c r="EC1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="ED1" s="3" t="s">
-        <v>697</v>
-      </c>
     </row>
-    <row r="2" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C2" t="str">
         <f>TRIM(B2)</f>
         <v>Bell Murphy</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G2" t="s">
         <v>74</v>
@@ -3094,7 +3066,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O2" t="s">
         <v>80</v>
@@ -3115,16 +3087,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="W2" s="9">
         <v>291830217845</v>
       </c>
       <c r="X2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Y2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z2" t="s">
         <v>82</v>
@@ -3136,13 +3108,13 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AE2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AF2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG2" s="2">
         <v>44082</v>
@@ -3163,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO2" t="s">
         <v>85</v>
@@ -3181,25 +3153,25 @@
         <v>8129055432</v>
       </c>
       <c r="AT2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AU2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AV2" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AW2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AX2" t="b">
         <v>0</v>
       </c>
       <c r="AY2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="BA2" t="b">
         <v>1</v>
@@ -3208,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="BC2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="BD2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="BE2" s="2">
         <v>45671</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG2" t="s">
         <v>87</v>
@@ -3271,10 +3243,10 @@
         <v>45420</v>
       </c>
       <c r="BX2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="BY2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ2" s="2">
         <v>45377</v>
@@ -3286,16 +3258,16 @@
         <v>81</v>
       </c>
       <c r="CC2" t="s">
+        <v>588</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>589</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>590</v>
+      </c>
+      <c r="CF2" t="s">
         <v>586</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>587</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>588</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>584</v>
       </c>
       <c r="CG2">
         <v>400050</v>
@@ -3304,7 +3276,7 @@
         <v>98</v>
       </c>
       <c r="CI2" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="CJ2" t="s">
         <v>121</v>
@@ -3319,7 +3291,7 @@
         <v>124</v>
       </c>
       <c r="CN2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO2" t="s">
         <v>125</v>
@@ -3340,10 +3312,10 @@
         <v>97</v>
       </c>
       <c r="CU2" t="s">
-        <v>688</v>
+        <v>171</v>
       </c>
       <c r="CV2" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW2" s="5" t="s">
         <v>133</v>
@@ -3361,7 +3333,7 @@
         <v>131</v>
       </c>
       <c r="DB2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="DC2" t="s">
         <v>141</v>
@@ -3373,13 +3345,13 @@
         <v>32</v>
       </c>
       <c r="DF2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="DG2">
         <v>829104573612</v>
       </c>
       <c r="DH2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="DI2">
         <v>500001004</v>
@@ -3406,10 +3378,10 @@
         <v>32343</v>
       </c>
       <c r="DQ2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS2">
         <v>9988776657</v>
@@ -3421,7 +3393,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW2" t="s">
         <v>96</v>
@@ -3444,28 +3416,25 @@
       <c r="EC2">
         <v>156</v>
       </c>
-      <c r="ED2" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G3" t="s">
         <v>74</v>
@@ -3486,7 +3455,7 @@
         <v>78</v>
       </c>
       <c r="N3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O3" t="s">
         <v>80</v>
@@ -3507,16 +3476,16 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="W3" s="9">
         <v>810344529012</v>
       </c>
       <c r="X3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Y3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z3" t="s">
         <v>82</v>
@@ -3528,13 +3497,13 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AE3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG3" s="2">
         <v>45028</v>
@@ -3555,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="AN3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO3" t="s">
         <v>85</v>
@@ -3573,25 +3542,25 @@
         <v>9847012345</v>
       </c>
       <c r="AT3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AU3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AV3" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AW3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AX3" t="b">
         <v>0</v>
       </c>
       <c r="AY3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="BA3" t="b">
         <v>1</v>
@@ -3600,16 +3569,16 @@
         <v>0</v>
       </c>
       <c r="BC3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="BD3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="BE3" s="2">
         <v>45716</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG3" t="s">
         <v>87</v>
@@ -3663,10 +3632,10 @@
         <v>45421</v>
       </c>
       <c r="BX3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="BY3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ3" s="2">
         <v>45860</v>
@@ -3678,16 +3647,16 @@
         <v>81</v>
       </c>
       <c r="CC3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="CD3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="CE3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CF3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG3">
         <v>400053</v>
@@ -3696,7 +3665,7 @@
         <v>98</v>
       </c>
       <c r="CI3" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="CJ3" t="s">
         <v>121</v>
@@ -3711,7 +3680,7 @@
         <v>124</v>
       </c>
       <c r="CN3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO3" t="s">
         <v>125</v>
@@ -3732,10 +3701,10 @@
         <v>97</v>
       </c>
       <c r="CU3" t="s">
-        <v>689</v>
+        <v>171</v>
       </c>
       <c r="CV3" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW3" s="5" t="s">
         <v>133</v>
@@ -3753,7 +3722,7 @@
         <v>131</v>
       </c>
       <c r="DB3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="DC3" t="s">
         <v>140</v>
@@ -3765,13 +3734,13 @@
         <v>32</v>
       </c>
       <c r="DF3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="DG3" s="9">
         <v>473910284756</v>
       </c>
       <c r="DH3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="DI3">
         <v>500001004</v>
@@ -3798,10 +3767,10 @@
         <v>32344</v>
       </c>
       <c r="DQ3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS3">
         <v>9988776655</v>
@@ -3813,7 +3782,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW3" t="s">
         <v>96</v>
@@ -3836,28 +3805,25 @@
       <c r="EC3">
         <v>156</v>
       </c>
-      <c r="ED3" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G4" t="s">
         <v>74</v>
@@ -3878,7 +3844,7 @@
         <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O4" t="s">
         <v>80</v>
@@ -3899,16 +3865,16 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="W4" s="9">
         <v>456712348901</v>
       </c>
       <c r="X4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Y4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z4" t="s">
         <v>82</v>
@@ -3920,13 +3886,13 @@
         <v>1</v>
       </c>
       <c r="AD4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AE4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AF4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG4" s="2">
         <v>45678</v>
@@ -3938,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AK4" s="8" t="s">
         <v>83</v>
@@ -3950,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="AN4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO4" t="s">
         <v>85</v>
@@ -3968,25 +3934,25 @@
         <v>7736088990</v>
       </c>
       <c r="AT4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AU4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AW4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AX4" t="b">
         <v>0</v>
       </c>
       <c r="AY4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="BA4" t="b">
         <v>1</v>
@@ -3995,16 +3961,16 @@
         <v>0</v>
       </c>
       <c r="BC4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="BD4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="BE4" s="2">
         <v>45731</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG4" t="s">
         <v>87</v>
@@ -4058,10 +4024,10 @@
         <v>45422</v>
       </c>
       <c r="BX4" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="BY4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ4" s="2">
         <v>45423</v>
@@ -4073,16 +4039,16 @@
         <v>81</v>
       </c>
       <c r="CC4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="CD4" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="CE4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="CF4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG4">
         <v>400089</v>
@@ -4091,7 +4057,7 @@
         <v>98</v>
       </c>
       <c r="CI4" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="CJ4" t="s">
         <v>121</v>
@@ -4106,7 +4072,7 @@
         <v>124</v>
       </c>
       <c r="CN4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO4" t="s">
         <v>125</v>
@@ -4127,10 +4093,10 @@
         <v>97</v>
       </c>
       <c r="CU4" t="s">
-        <v>690</v>
+        <v>171</v>
       </c>
       <c r="CV4" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW4" s="5" t="s">
         <v>133</v>
@@ -4148,7 +4114,7 @@
         <v>131</v>
       </c>
       <c r="DB4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="DC4" t="s">
         <v>139</v>
@@ -4160,13 +4126,13 @@
         <v>32</v>
       </c>
       <c r="DF4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="DG4">
         <v>109283746501</v>
       </c>
       <c r="DH4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="DI4">
         <v>500001004</v>
@@ -4193,10 +4159,10 @@
         <v>32345</v>
       </c>
       <c r="DQ4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS4">
         <v>9988776655</v>
@@ -4208,7 +4174,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW4" t="s">
         <v>96</v>
@@ -4231,28 +4197,25 @@
       <c r="EC4">
         <v>156</v>
       </c>
-      <c r="ED4" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -4273,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O5" t="s">
         <v>80</v>
@@ -4294,16 +4257,16 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="W5" s="9">
         <v>773200193345</v>
       </c>
       <c r="X5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z5" t="s">
         <v>82</v>
@@ -4315,13 +4278,13 @@
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AE5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG5" s="2">
         <v>44530</v>
@@ -4342,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="AN5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO5" t="s">
         <v>85</v>
@@ -4360,25 +4323,25 @@
         <v>6235109876</v>
       </c>
       <c r="AT5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AU5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AV5" s="8" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AW5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AX5" t="b">
         <v>0</v>
       </c>
       <c r="AY5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="BA5" t="b">
         <v>1</v>
@@ -4387,16 +4350,16 @@
         <v>0</v>
       </c>
       <c r="BC5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="BD5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="BE5" s="2">
         <v>45750</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG5" t="s">
         <v>87</v>
@@ -4450,10 +4413,10 @@
         <v>45423</v>
       </c>
       <c r="BX5" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="BY5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ5" s="2">
         <v>45663</v>
@@ -4465,16 +4428,16 @@
         <v>81</v>
       </c>
       <c r="CC5" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CD5" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="CE5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="CF5" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG5">
         <v>400028</v>
@@ -4483,7 +4446,7 @@
         <v>98</v>
       </c>
       <c r="CI5" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="CJ5" t="s">
         <v>121</v>
@@ -4498,7 +4461,7 @@
         <v>124</v>
       </c>
       <c r="CN5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO5" t="s">
         <v>125</v>
@@ -4519,10 +4482,10 @@
         <v>97</v>
       </c>
       <c r="CU5" t="s">
-        <v>691</v>
+        <v>171</v>
       </c>
       <c r="CV5" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW5" s="5" t="s">
         <v>133</v>
@@ -4540,7 +4503,7 @@
         <v>131</v>
       </c>
       <c r="DB5" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="DC5" t="s">
         <v>139</v>
@@ -4552,13 +4515,13 @@
         <v>32</v>
       </c>
       <c r="DF5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="DG5">
         <v>556473829102</v>
       </c>
       <c r="DH5" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="DI5">
         <v>500001004</v>
@@ -4585,10 +4548,10 @@
         <v>32346</v>
       </c>
       <c r="DQ5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS5">
         <v>9988776655</v>
@@ -4600,7 +4563,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW5" t="s">
         <v>96</v>
@@ -4623,28 +4586,25 @@
       <c r="EC5">
         <v>156</v>
       </c>
-      <c r="ED5" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -4665,7 +4625,7 @@
         <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O6" t="s">
         <v>80</v>
@@ -4686,16 +4646,16 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="W6" s="9">
         <v>109855672210</v>
       </c>
       <c r="X6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z6" t="s">
         <v>82</v>
@@ -4707,13 +4667,13 @@
         <v>1</v>
       </c>
       <c r="AD6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AE6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG6" s="2">
         <v>45488</v>
@@ -4734,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="AN6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO6" t="s">
         <v>85</v>
@@ -4752,25 +4712,25 @@
         <v>9447056789</v>
       </c>
       <c r="AT6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AU6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AV6" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AW6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AX6" t="b">
         <v>0</v>
       </c>
       <c r="AY6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="BA6" t="b">
         <v>1</v>
@@ -4779,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="BD6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="BE6" s="2">
         <v>45769</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG6" t="s">
         <v>87</v>
@@ -4842,10 +4802,10 @@
         <v>45424</v>
       </c>
       <c r="BX6" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="BY6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ6" s="2">
         <v>45501</v>
@@ -4857,16 +4817,16 @@
         <v>81</v>
       </c>
       <c r="CC6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="CD6" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="CE6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="CF6" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG6">
         <v>400030</v>
@@ -4875,7 +4835,7 @@
         <v>98</v>
       </c>
       <c r="CI6" s="8" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="CJ6" t="s">
         <v>121</v>
@@ -4890,7 +4850,7 @@
         <v>124</v>
       </c>
       <c r="CN6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO6" t="s">
         <v>125</v>
@@ -4911,10 +4871,10 @@
         <v>97</v>
       </c>
       <c r="CU6" t="s">
-        <v>692</v>
+        <v>171</v>
       </c>
       <c r="CV6" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW6" s="5" t="s">
         <v>133</v>
@@ -4932,7 +4892,7 @@
         <v>131</v>
       </c>
       <c r="DB6" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="DC6" t="s">
         <v>142</v>
@@ -4944,13 +4904,13 @@
         <v>32</v>
       </c>
       <c r="DF6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="DG6">
         <v>901827364519</v>
       </c>
       <c r="DH6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="DI6">
         <v>500001004</v>
@@ -4977,10 +4937,10 @@
         <v>32347</v>
       </c>
       <c r="DQ6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS6">
         <v>9988776655</v>
@@ -4992,7 +4952,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW6" t="s">
         <v>96</v>
@@ -5015,28 +4975,25 @@
       <c r="EC6">
         <v>156</v>
       </c>
-      <c r="ED6" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G7" t="s">
         <v>74</v>
@@ -5057,7 +5014,7 @@
         <v>78</v>
       </c>
       <c r="N7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O7" t="s">
         <v>80</v>
@@ -5078,16 +5035,16 @@
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="W7" s="9">
         <v>654399871123</v>
       </c>
       <c r="X7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Y7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z7" t="s">
         <v>82</v>
@@ -5099,13 +5056,13 @@
         <v>1</v>
       </c>
       <c r="AD7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AE7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AF7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG7" s="2">
         <v>46297</v>
@@ -5126,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="AN7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO7" t="s">
         <v>85</v>
@@ -5144,25 +5101,25 @@
         <v>8547123456</v>
       </c>
       <c r="AT7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AU7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AV7" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AW7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AX7" t="b">
         <v>0</v>
       </c>
       <c r="AY7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="BA7" t="b">
         <v>1</v>
@@ -5171,16 +5128,16 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="BD7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="BE7" s="2">
         <v>45787</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG7" t="s">
         <v>87</v>
@@ -5234,10 +5191,10 @@
         <v>45425</v>
       </c>
       <c r="BX7" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="BY7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ7" s="2">
         <v>45826</v>
@@ -5249,16 +5206,16 @@
         <v>81</v>
       </c>
       <c r="CC7" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="CD7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="CE7" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="CF7" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG7">
         <v>400030</v>
@@ -5267,7 +5224,7 @@
         <v>98</v>
       </c>
       <c r="CI7" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ7" t="s">
         <v>121</v>
@@ -5282,7 +5239,7 @@
         <v>124</v>
       </c>
       <c r="CN7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO7" t="s">
         <v>125</v>
@@ -5303,10 +5260,10 @@
         <v>97</v>
       </c>
       <c r="CU7" t="s">
-        <v>693</v>
+        <v>171</v>
       </c>
       <c r="CV7" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW7" s="5" t="s">
         <v>133</v>
@@ -5324,7 +5281,7 @@
         <v>131</v>
       </c>
       <c r="DB7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="DC7" t="s">
         <v>141</v>
@@ -5336,13 +5293,13 @@
         <v>32</v>
       </c>
       <c r="DF7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="DG7">
         <v>234567890123</v>
       </c>
       <c r="DH7" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="DI7">
         <v>500001004</v>
@@ -5369,10 +5326,10 @@
         <v>32348</v>
       </c>
       <c r="DQ7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS7">
         <v>9988776655</v>
@@ -5384,7 +5341,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW7" t="s">
         <v>96</v>
@@ -5407,28 +5364,25 @@
       <c r="EC7">
         <v>156</v>
       </c>
-      <c r="ED7" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="8" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G8" t="s">
         <v>73</v>
@@ -5449,7 +5403,7 @@
         <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O8" t="s">
         <v>80</v>
@@ -5470,16 +5424,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="W8" s="9">
         <v>334566784456</v>
       </c>
       <c r="X8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Y8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z8" t="s">
         <v>82</v>
@@ -5491,13 +5445,13 @@
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AE8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF8" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG8" s="2">
         <v>43912</v>
@@ -5518,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="AN8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO8" t="s">
         <v>85</v>
@@ -5536,25 +5490,25 @@
         <v>7025034567</v>
       </c>
       <c r="AT8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AU8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AW8" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AX8" t="b">
         <v>0</v>
       </c>
       <c r="AY8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ8" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="BA8" t="b">
         <v>1</v>
@@ -5563,16 +5517,16 @@
         <v>0</v>
       </c>
       <c r="BC8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="BD8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="BE8" s="2">
         <v>45815</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG8" t="s">
         <v>87</v>
@@ -5626,10 +5580,10 @@
         <v>45426</v>
       </c>
       <c r="BX8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="BY8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ8" s="2">
         <v>45907</v>
@@ -5641,13 +5595,13 @@
         <v>81</v>
       </c>
       <c r="CC8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="CE8" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="CF8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG8">
         <v>400077</v>
@@ -5656,7 +5610,7 @@
         <v>98</v>
       </c>
       <c r="CI8" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ8" t="s">
         <v>121</v>
@@ -5671,7 +5625,7 @@
         <v>124</v>
       </c>
       <c r="CN8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO8" t="s">
         <v>125</v>
@@ -5692,10 +5646,10 @@
         <v>97</v>
       </c>
       <c r="CU8" t="s">
-        <v>688</v>
+        <v>171</v>
       </c>
       <c r="CV8" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW8" s="5" t="s">
         <v>133</v>
@@ -5713,7 +5667,7 @@
         <v>131</v>
       </c>
       <c r="DB8" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="DC8" t="s">
         <v>140</v>
@@ -5725,13 +5679,13 @@
         <v>32</v>
       </c>
       <c r="DF8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="DG8">
         <v>678901234567</v>
       </c>
       <c r="DH8" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="DI8">
         <v>500001004</v>
@@ -5758,10 +5712,10 @@
         <v>32349</v>
       </c>
       <c r="DQ8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS8">
         <v>9988776655</v>
@@ -5773,7 +5727,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW8" t="s">
         <v>96</v>
@@ -5796,28 +5750,25 @@
       <c r="EC8">
         <v>156</v>
       </c>
-      <c r="ED8" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="9" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G9" t="s">
         <v>74</v>
@@ -5838,7 +5789,7 @@
         <v>78</v>
       </c>
       <c r="N9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O9" t="s">
         <v>80</v>
@@ -5859,16 +5810,16 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="W9" s="9">
         <v>901233456789</v>
       </c>
       <c r="X9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Z9" t="s">
         <v>82</v>
@@ -5880,13 +5831,13 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AE9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG9" s="2">
         <v>44792</v>
@@ -5907,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="AN9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO9" t="s">
         <v>85</v>
@@ -5925,25 +5876,25 @@
         <v>6365045678</v>
       </c>
       <c r="AT9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AU9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AV9" s="8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AW9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AX9" t="b">
         <v>0</v>
       </c>
       <c r="AY9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="BA9" t="b">
         <v>1</v>
@@ -5952,16 +5903,16 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="BD9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="BE9" s="2">
         <v>45833</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG9" t="s">
         <v>87</v>
@@ -6015,10 +5966,10 @@
         <v>45427</v>
       </c>
       <c r="BX9" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="BY9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ9" s="2">
         <v>45476</v>
@@ -6030,16 +5981,16 @@
         <v>81</v>
       </c>
       <c r="CC9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CD9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="CE9" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="CF9" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG9">
         <v>400049</v>
@@ -6048,7 +5999,7 @@
         <v>98</v>
       </c>
       <c r="CI9" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ9" t="s">
         <v>121</v>
@@ -6063,7 +6014,7 @@
         <v>124</v>
       </c>
       <c r="CN9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO9" t="s">
         <v>125</v>
@@ -6084,10 +6035,10 @@
         <v>97</v>
       </c>
       <c r="CU9" t="s">
-        <v>689</v>
+        <v>171</v>
       </c>
       <c r="CV9" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW9" s="5" t="s">
         <v>133</v>
@@ -6105,7 +6056,7 @@
         <v>131</v>
       </c>
       <c r="DB9" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="DC9" t="s">
         <v>139</v>
@@ -6117,13 +6068,13 @@
         <v>32</v>
       </c>
       <c r="DF9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="DG9">
         <v>345678901234</v>
       </c>
       <c r="DH9" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="DI9">
         <v>500001004</v>
@@ -6150,10 +6101,10 @@
         <v>32350</v>
       </c>
       <c r="DQ9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS9">
         <v>9988776655</v>
@@ -6165,7 +6116,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW9" t="s">
         <v>96</v>
@@ -6188,28 +6139,25 @@
       <c r="EC9">
         <v>156</v>
       </c>
-      <c r="ED9" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="10" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G10" t="s">
         <v>74</v>
@@ -6230,7 +6178,7 @@
         <v>78</v>
       </c>
       <c r="N10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O10" t="s">
         <v>80</v>
@@ -6251,16 +6199,16 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="W10" s="9">
         <v>556788901123</v>
       </c>
       <c r="X10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Y10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z10" t="s">
         <v>82</v>
@@ -6272,13 +6220,13 @@
         <v>1</v>
       </c>
       <c r="AD10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AE10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AF10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG10" s="2">
         <v>45996</v>
@@ -6299,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO10" t="s">
         <v>85</v>
@@ -6317,25 +6265,25 @@
         <v>9946067890</v>
       </c>
       <c r="AT10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AU10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AV10" s="8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AW10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AX10" t="b">
         <v>0</v>
       </c>
       <c r="AY10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BA10" t="b">
         <v>1</v>
@@ -6344,16 +6292,16 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="BD10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="BE10" s="2">
         <v>45857</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG10" t="s">
         <v>88</v>
@@ -6404,10 +6352,10 @@
         <v>45428</v>
       </c>
       <c r="BX10" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="BY10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ10" s="2">
         <v>45833</v>
@@ -6419,16 +6367,16 @@
         <v>81</v>
       </c>
       <c r="CC10" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="CD10" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="CE10" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="CF10" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG10">
         <v>400049</v>
@@ -6437,7 +6385,7 @@
         <v>98</v>
       </c>
       <c r="CI10" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ10" t="s">
         <v>121</v>
@@ -6452,7 +6400,7 @@
         <v>124</v>
       </c>
       <c r="CN10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO10" t="s">
         <v>125</v>
@@ -6473,10 +6421,10 @@
         <v>97</v>
       </c>
       <c r="CU10" t="s">
-        <v>690</v>
+        <v>171</v>
       </c>
       <c r="CV10" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW10" s="5" t="s">
         <v>133</v>
@@ -6494,7 +6442,7 @@
         <v>131</v>
       </c>
       <c r="DB10" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="DC10" t="s">
         <v>139</v>
@@ -6506,13 +6454,13 @@
         <v>32</v>
       </c>
       <c r="DF10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="DG10">
         <v>890123456789</v>
       </c>
       <c r="DH10" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="DI10">
         <v>500001004</v>
@@ -6539,10 +6487,10 @@
         <v>32351</v>
       </c>
       <c r="DQ10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS10">
         <v>9988776655</v>
@@ -6554,7 +6502,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW10" t="s">
         <v>96</v>
@@ -6577,28 +6525,25 @@
       <c r="EC10">
         <v>156</v>
       </c>
-      <c r="ED10" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="11" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G11" t="s">
         <v>74</v>
@@ -6619,7 +6564,7 @@
         <v>78</v>
       </c>
       <c r="N11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O11" t="s">
         <v>80</v>
@@ -6640,16 +6585,16 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="W11" s="9">
         <v>223455678890</v>
       </c>
       <c r="X11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Y11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z11" t="s">
         <v>82</v>
@@ -6661,13 +6606,13 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AE11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AF11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG11" s="2">
         <v>45105</v>
@@ -6688,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="AN11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO11" t="s">
         <v>85</v>
@@ -6706,25 +6651,25 @@
         <v>8891078901</v>
       </c>
       <c r="AT11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AU11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AW11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AX11" t="b">
         <v>0</v>
       </c>
       <c r="AY11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="BA11" t="b">
         <v>1</v>
@@ -6733,16 +6678,16 @@
         <v>0</v>
       </c>
       <c r="BC11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="BD11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="BE11" s="2">
         <v>45870</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG11" t="s">
         <v>88</v>
@@ -6793,10 +6738,10 @@
         <v>45429</v>
       </c>
       <c r="BX11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="BY11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ11" s="2">
         <v>45394</v>
@@ -6808,16 +6753,16 @@
         <v>81</v>
       </c>
       <c r="CC11" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="CD11" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="CE11" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="CF11" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG11">
         <v>400049</v>
@@ -6826,7 +6771,7 @@
         <v>98</v>
       </c>
       <c r="CI11" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ11" t="s">
         <v>121</v>
@@ -6841,7 +6786,7 @@
         <v>124</v>
       </c>
       <c r="CN11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO11" t="s">
         <v>125</v>
@@ -6862,10 +6807,10 @@
         <v>97</v>
       </c>
       <c r="CU11" t="s">
-        <v>691</v>
+        <v>171</v>
       </c>
       <c r="CV11" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW11" s="5" t="s">
         <v>133</v>
@@ -6883,7 +6828,7 @@
         <v>131</v>
       </c>
       <c r="DB11" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="DC11" t="s">
         <v>142</v>
@@ -6895,13 +6840,13 @@
         <v>32</v>
       </c>
       <c r="DF11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="DG11">
         <v>123456789012</v>
       </c>
       <c r="DH11" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="DI11">
         <v>500001004</v>
@@ -6928,10 +6873,10 @@
         <v>32352</v>
       </c>
       <c r="DQ11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS11">
         <v>9988776655</v>
@@ -6943,7 +6888,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW11" t="s">
         <v>96</v>
@@ -6966,28 +6911,25 @@
       <c r="EC11">
         <v>156</v>
       </c>
-      <c r="ED11" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="12" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G12" t="s">
         <v>74</v>
@@ -7008,7 +6950,7 @@
         <v>79</v>
       </c>
       <c r="N12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O12" t="s">
         <v>80</v>
@@ -7029,16 +6971,16 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="W12" s="9">
         <v>889011234456</v>
       </c>
       <c r="X12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Y12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z12" t="s">
         <v>82</v>
@@ -7050,13 +6992,13 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AE12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG12" s="2">
         <v>45336</v>
@@ -7077,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO12" t="s">
         <v>85</v>
@@ -7095,25 +7037,25 @@
         <v>7558089012</v>
       </c>
       <c r="AT12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AU12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AV12" s="8" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AW12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AX12" t="b">
         <v>0</v>
       </c>
       <c r="AY12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="BA12" t="b">
         <v>1</v>
@@ -7122,16 +7064,16 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="BD12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="BE12" s="2">
         <v>45886</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG12" t="s">
         <v>88</v>
@@ -7182,10 +7124,10 @@
         <v>45430</v>
       </c>
       <c r="BX12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="BY12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ12" s="2">
         <v>45700</v>
@@ -7197,16 +7139,16 @@
         <v>81</v>
       </c>
       <c r="CC12" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="CD12" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="CE12" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="CF12" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG12">
         <v>400020</v>
@@ -7215,7 +7157,7 @@
         <v>98</v>
       </c>
       <c r="CI12" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ12" t="s">
         <v>121</v>
@@ -7230,7 +7172,7 @@
         <v>124</v>
       </c>
       <c r="CN12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO12" t="s">
         <v>125</v>
@@ -7251,10 +7193,10 @@
         <v>97</v>
       </c>
       <c r="CU12" t="s">
-        <v>692</v>
+        <v>171</v>
       </c>
       <c r="CV12" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW12" s="5" t="s">
         <v>133</v>
@@ -7272,7 +7214,7 @@
         <v>131</v>
       </c>
       <c r="DB12" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="DC12" t="s">
         <v>141</v>
@@ -7284,13 +7226,13 @@
         <v>32</v>
       </c>
       <c r="DF12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="DG12">
         <v>778899001122</v>
       </c>
       <c r="DH12" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="DI12">
         <v>500001004</v>
@@ -7317,10 +7259,10 @@
         <v>32353</v>
       </c>
       <c r="DQ12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS12">
         <v>9988776655</v>
@@ -7332,7 +7274,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW12" t="s">
         <v>96</v>
@@ -7355,28 +7297,25 @@
       <c r="EC12">
         <v>156</v>
       </c>
-      <c r="ED12" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="13" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -7397,7 +7336,7 @@
         <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O13" t="s">
         <v>80</v>
@@ -7418,16 +7357,16 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="W13" s="9">
         <v>667899012234</v>
       </c>
       <c r="X13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z13" t="s">
         <v>82</v>
@@ -7439,13 +7378,13 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AE13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG13" s="2">
         <v>44325</v>
@@ -7466,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="AN13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO13" t="s">
         <v>85</v>
@@ -7484,25 +7423,25 @@
         <v>6005090123</v>
       </c>
       <c r="AT13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AU13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AV13" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AW13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AX13" t="b">
         <v>0</v>
       </c>
       <c r="AY13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="BA13" t="b">
         <v>1</v>
@@ -7511,16 +7450,16 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="BD13" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="BE13" s="2">
         <v>45912</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG13" t="s">
         <v>88</v>
@@ -7571,10 +7510,10 @@
         <v>45431</v>
       </c>
       <c r="BX13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="BY13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ13" s="2">
         <v>45521</v>
@@ -7586,16 +7525,16 @@
         <v>81</v>
       </c>
       <c r="CC13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="CD13" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="CE13" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="CF13" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG13">
         <v>400026</v>
@@ -7604,7 +7543,7 @@
         <v>98</v>
       </c>
       <c r="CI13" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ13" t="s">
         <v>121</v>
@@ -7619,7 +7558,7 @@
         <v>124</v>
       </c>
       <c r="CN13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO13" t="s">
         <v>125</v>
@@ -7640,10 +7579,10 @@
         <v>97</v>
       </c>
       <c r="CU13" t="s">
-        <v>693</v>
+        <v>171</v>
       </c>
       <c r="CV13" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW13" s="5" t="s">
         <v>133</v>
@@ -7661,7 +7600,7 @@
         <v>131</v>
       </c>
       <c r="DB13" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="DC13" t="s">
         <v>140</v>
@@ -7673,13 +7612,13 @@
         <v>32</v>
       </c>
       <c r="DF13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="DG13">
         <v>445566778899</v>
       </c>
       <c r="DH13" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="DI13">
         <v>500001004</v>
@@ -7706,10 +7645,10 @@
         <v>32354</v>
       </c>
       <c r="DQ13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS13">
         <v>9988776655</v>
@@ -7721,7 +7660,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW13" t="s">
         <v>96</v>
@@ -7744,28 +7683,25 @@
       <c r="EC13">
         <v>156</v>
       </c>
-      <c r="ED13" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="14" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G14" t="s">
         <v>74</v>
@@ -7786,7 +7722,7 @@
         <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O14" t="s">
         <v>80</v>
@@ -7807,16 +7743,16 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="W14" s="9">
         <v>112344567789</v>
       </c>
       <c r="X14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Y14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z14" t="s">
         <v>82</v>
@@ -7828,13 +7764,13 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AE14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG14" s="2">
         <v>46142</v>
@@ -7855,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="AN14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO14" t="s">
         <v>85</v>
@@ -7873,25 +7809,25 @@
         <v>9037001234</v>
       </c>
       <c r="AT14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AU14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AV14" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AW14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AX14" t="b">
         <v>0</v>
       </c>
       <c r="AY14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ14" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="BA14" t="b">
         <v>1</v>
@@ -7900,16 +7836,16 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="BD14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="BE14" s="2">
         <v>45930</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG14" t="s">
         <v>88</v>
@@ -7960,10 +7896,10 @@
         <v>45432</v>
       </c>
       <c r="BX14" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="BY14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ14" s="2">
         <v>45837</v>
@@ -7975,16 +7911,16 @@
         <v>81</v>
       </c>
       <c r="CC14" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="CD14" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="CE14" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CF14" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG14">
         <v>400053</v>
@@ -7993,7 +7929,7 @@
         <v>98</v>
       </c>
       <c r="CI14" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ14" t="s">
         <v>121</v>
@@ -8008,7 +7944,7 @@
         <v>124</v>
       </c>
       <c r="CN14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO14" t="s">
         <v>125</v>
@@ -8029,10 +7965,10 @@
         <v>97</v>
       </c>
       <c r="CU14" t="s">
-        <v>688</v>
+        <v>171</v>
       </c>
       <c r="CV14" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW14" s="5" t="s">
         <v>133</v>
@@ -8050,7 +7986,7 @@
         <v>131</v>
       </c>
       <c r="DB14" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="DC14" t="s">
         <v>139</v>
@@ -8062,13 +7998,13 @@
         <v>32</v>
       </c>
       <c r="DF14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="DG14">
         <v>990011223344</v>
       </c>
       <c r="DH14" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="DI14">
         <v>500001004</v>
@@ -8095,10 +8031,10 @@
         <v>32355</v>
       </c>
       <c r="DQ14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS14">
         <v>9988776655</v>
@@ -8110,7 +8046,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW14" t="s">
         <v>96</v>
@@ -8133,28 +8069,25 @@
       <c r="EC14">
         <v>156</v>
       </c>
-      <c r="ED14" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="15" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G15" t="s">
         <v>74</v>
@@ -8175,7 +8108,7 @@
         <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O15" t="s">
         <v>80</v>
@@ -8196,16 +8129,16 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="W15" s="9">
         <v>445677890012</v>
       </c>
       <c r="X15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Y15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z15" t="s">
         <v>82</v>
@@ -8217,13 +8150,13 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AE15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AF15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG15" s="2">
         <v>44176</v>
@@ -8244,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="AN15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO15" t="s">
         <v>85</v>
@@ -8262,25 +8195,25 @@
         <v>8301011223</v>
       </c>
       <c r="AT15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AU15" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AV15" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AW15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AX15" t="b">
         <v>0</v>
       </c>
       <c r="AY15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BA15" t="b">
         <v>1</v>
@@ -8289,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="BD15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="BE15" s="2">
         <v>45935</v>
       </c>
       <c r="BF15" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG15" t="s">
         <v>88</v>
@@ -8349,10 +8282,10 @@
         <v>45433</v>
       </c>
       <c r="BX15" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="BY15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ15" s="2">
         <v>45656</v>
@@ -8364,13 +8297,13 @@
         <v>81</v>
       </c>
       <c r="CC15" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="CE15" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="CF15" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG15">
         <v>400063</v>
@@ -8379,7 +8312,7 @@
         <v>98</v>
       </c>
       <c r="CI15" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ15" t="s">
         <v>121</v>
@@ -8394,7 +8327,7 @@
         <v>124</v>
       </c>
       <c r="CN15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO15" t="s">
         <v>125</v>
@@ -8415,10 +8348,10 @@
         <v>97</v>
       </c>
       <c r="CU15" t="s">
-        <v>689</v>
+        <v>171</v>
       </c>
       <c r="CV15" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW15" s="5" t="s">
         <v>133</v>
@@ -8436,7 +8369,7 @@
         <v>131</v>
       </c>
       <c r="DB15" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="DC15" t="s">
         <v>139</v>
@@ -8448,13 +8381,13 @@
         <v>32</v>
       </c>
       <c r="DF15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="DG15">
         <v>223344556677</v>
       </c>
       <c r="DH15" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="DI15">
         <v>500001004</v>
@@ -8481,10 +8414,10 @@
         <v>32356</v>
       </c>
       <c r="DQ15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS15">
         <v>9988776655</v>
@@ -8496,7 +8429,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW15" t="s">
         <v>96</v>
@@ -8519,28 +8452,25 @@
       <c r="EC15">
         <v>156</v>
       </c>
-      <c r="ED15" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="16" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
@@ -8561,7 +8491,7 @@
         <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O16" t="s">
         <v>80</v>
@@ -8582,16 +8512,16 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="W16" s="9">
         <v>990122345567</v>
       </c>
       <c r="X16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Y16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z16" t="s">
         <v>82</v>
@@ -8603,13 +8533,13 @@
         <v>1</v>
       </c>
       <c r="AD16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AE16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AF16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG16" s="2">
         <v>44859</v>
@@ -8630,7 +8560,7 @@
         <v>1</v>
       </c>
       <c r="AN16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO16" t="s">
         <v>85</v>
@@ -8648,25 +8578,25 @@
         <v>7205022334</v>
       </c>
       <c r="AT16" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AU16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AV16" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AW16" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AX16" t="b">
         <v>0</v>
       </c>
       <c r="AY16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ16" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="BA16" t="b">
         <v>1</v>
@@ -8675,16 +8605,16 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="BD16" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="BE16" s="2">
         <v>45951</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG16" t="s">
         <v>88</v>
@@ -8735,10 +8665,10 @@
         <v>45434</v>
       </c>
       <c r="BX16" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="BY16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ16" s="2">
         <v>45819</v>
@@ -8750,16 +8680,16 @@
         <v>81</v>
       </c>
       <c r="CC16" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="CD16" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="CE16" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="CF16" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG16">
         <v>400070</v>
@@ -8768,7 +8698,7 @@
         <v>98</v>
       </c>
       <c r="CI16" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ16" t="s">
         <v>121</v>
@@ -8783,7 +8713,7 @@
         <v>124</v>
       </c>
       <c r="CN16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO16" t="s">
         <v>125</v>
@@ -8804,10 +8734,10 @@
         <v>97</v>
       </c>
       <c r="CU16" t="s">
-        <v>690</v>
+        <v>171</v>
       </c>
       <c r="CV16" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW16" s="5" t="s">
         <v>133</v>
@@ -8825,7 +8755,7 @@
         <v>131</v>
       </c>
       <c r="DB16" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="DC16" t="s">
         <v>142</v>
@@ -8837,13 +8767,13 @@
         <v>32</v>
       </c>
       <c r="DF16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="DG16">
         <v>550066117722</v>
       </c>
       <c r="DH16" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="DI16">
         <v>500001004</v>
@@ -8870,10 +8800,10 @@
         <v>32357</v>
       </c>
       <c r="DQ16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS16">
         <v>9988776655</v>
@@ -8885,7 +8815,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW16" t="s">
         <v>96</v>
@@ -8908,28 +8838,25 @@
       <c r="EC16">
         <v>156</v>
       </c>
-      <c r="ED16" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="17" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -8950,7 +8877,7 @@
         <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O17" t="s">
         <v>80</v>
@@ -8971,16 +8898,16 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="W17" s="9">
         <v>334566789901</v>
       </c>
       <c r="X17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Y17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z17" t="s">
         <v>82</v>
@@ -8992,13 +8919,13 @@
         <v>1</v>
       </c>
       <c r="AD17" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AE17" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AF17" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG17" s="2">
         <v>45845</v>
@@ -9019,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="AN17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO17" t="s">
         <v>85</v>
@@ -9037,25 +8964,25 @@
         <v>6145033445</v>
       </c>
       <c r="AT17" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AU17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AV17" s="8" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AW17" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AX17" t="b">
         <v>0</v>
       </c>
       <c r="AY17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ17" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="BA17" t="b">
         <v>1</v>
@@ -9064,16 +8991,16 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="BD17" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="BE17" s="2">
         <v>45969</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG17" t="s">
         <v>89</v>
@@ -9124,10 +9051,10 @@
         <v>45435</v>
       </c>
       <c r="BX17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="BY17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ17" s="2">
         <v>45306</v>
@@ -9139,13 +9066,13 @@
         <v>81</v>
       </c>
       <c r="CC17" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="CE17" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="CF17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG17">
         <v>400077</v>
@@ -9154,7 +9081,7 @@
         <v>98</v>
       </c>
       <c r="CI17" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ17" t="s">
         <v>121</v>
@@ -9169,7 +9096,7 @@
         <v>124</v>
       </c>
       <c r="CN17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO17" t="s">
         <v>125</v>
@@ -9190,10 +9117,10 @@
         <v>97</v>
       </c>
       <c r="CU17" t="s">
-        <v>691</v>
+        <v>171</v>
       </c>
       <c r="CV17" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW17" s="5" t="s">
         <v>133</v>
@@ -9211,7 +9138,7 @@
         <v>131</v>
       </c>
       <c r="DB17" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="DC17" t="s">
         <v>141</v>
@@ -9223,13 +9150,13 @@
         <v>32</v>
       </c>
       <c r="DF17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="DG17">
         <v>883399440055</v>
       </c>
       <c r="DH17" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="DI17">
         <v>500001004</v>
@@ -9256,10 +9183,10 @@
         <v>32358</v>
       </c>
       <c r="DQ17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS17">
         <v>9988776655</v>
@@ -9271,7 +9198,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW17" t="s">
         <v>96</v>
@@ -9294,28 +9221,25 @@
       <c r="EC17">
         <v>156</v>
       </c>
-      <c r="ED17" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="18" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G18" t="s">
         <v>74</v>
@@ -9336,7 +9260,7 @@
         <v>79</v>
       </c>
       <c r="N18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O18" t="s">
         <v>80</v>
@@ -9357,16 +9281,16 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="W18" s="9">
         <v>778900123345</v>
       </c>
       <c r="X18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z18" t="s">
         <v>82</v>
@@ -9378,13 +9302,13 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AE18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AF18" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG18" s="2">
         <v>45186</v>
@@ -9405,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="AN18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO18" t="s">
         <v>85</v>
@@ -9423,25 +9347,25 @@
         <v>9176044556</v>
       </c>
       <c r="AT18" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AU18" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AW18" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AX18" t="b">
         <v>0</v>
       </c>
       <c r="AY18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="BA18" t="b">
         <v>1</v>
@@ -9450,16 +9374,16 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="BD18" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="BE18" s="2">
         <v>45990</v>
       </c>
       <c r="BF18" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG18" t="s">
         <v>89</v>
@@ -9510,10 +9434,10 @@
         <v>45436</v>
       </c>
       <c r="BX18" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="BY18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ18" s="2">
         <v>45726</v>
@@ -9525,16 +9449,16 @@
         <v>81</v>
       </c>
       <c r="CC18" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="CD18" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="CE18" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="CF18" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG18">
         <v>400022</v>
@@ -9543,7 +9467,7 @@
         <v>98</v>
       </c>
       <c r="CI18" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ18" t="s">
         <v>121</v>
@@ -9558,7 +9482,7 @@
         <v>124</v>
       </c>
       <c r="CN18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO18" t="s">
         <v>125</v>
@@ -9579,10 +9503,10 @@
         <v>97</v>
       </c>
       <c r="CU18" t="s">
-        <v>692</v>
+        <v>171</v>
       </c>
       <c r="CV18" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW18" s="5" t="s">
         <v>133</v>
@@ -9600,7 +9524,7 @@
         <v>131</v>
       </c>
       <c r="DB18" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="DC18" t="s">
         <v>140</v>
@@ -9612,13 +9536,13 @@
         <v>32</v>
       </c>
       <c r="DF18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="DG18">
         <v>116622773388</v>
       </c>
       <c r="DH18" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="DI18">
         <v>500001004</v>
@@ -9645,10 +9569,10 @@
         <v>32359</v>
       </c>
       <c r="DQ18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS18">
         <v>9988776655</v>
@@ -9660,7 +9584,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW18" t="s">
         <v>96</v>
@@ -9683,28 +9607,25 @@
       <c r="EC18">
         <v>156</v>
       </c>
-      <c r="ED18" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="19" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G19" t="s">
         <v>74</v>
@@ -9725,7 +9646,7 @@
         <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O19" t="s">
         <v>80</v>
@@ -9746,16 +9667,16 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="W19" s="9">
         <v>1233456678</v>
       </c>
       <c r="X19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z19" t="s">
         <v>82</v>
@@ -9767,13 +9688,13 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AE19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AF19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG19" s="2">
         <v>45616</v>
@@ -9794,7 +9715,7 @@
         <v>1</v>
       </c>
       <c r="AN19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO19" t="s">
         <v>85</v>
@@ -9812,25 +9733,25 @@
         <v>8606055667</v>
       </c>
       <c r="AT19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AU19" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AV19" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AW19" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AX19" t="b">
         <v>0</v>
       </c>
       <c r="AY19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ19" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="BA19" t="b">
         <v>1</v>
@@ -9839,16 +9760,16 @@
         <v>0</v>
       </c>
       <c r="BC19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="BD19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="BE19" s="2">
         <v>45995</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG19" t="s">
         <v>89</v>
@@ -9899,10 +9820,10 @@
         <v>45437</v>
       </c>
       <c r="BX19" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="BY19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ19" s="2">
         <v>45556</v>
@@ -9914,16 +9835,16 @@
         <v>81</v>
       </c>
       <c r="CC19" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="CD19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="CE19" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="CF19" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG19">
         <v>400005</v>
@@ -9932,7 +9853,7 @@
         <v>98</v>
       </c>
       <c r="CI19" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ19" t="s">
         <v>121</v>
@@ -9947,7 +9868,7 @@
         <v>124</v>
       </c>
       <c r="CN19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO19" t="s">
         <v>125</v>
@@ -9968,10 +9889,10 @@
         <v>97</v>
       </c>
       <c r="CU19" t="s">
-        <v>693</v>
+        <v>171</v>
       </c>
       <c r="CV19" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW19" s="5" t="s">
         <v>133</v>
@@ -9989,7 +9910,7 @@
         <v>131</v>
       </c>
       <c r="DB19" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="DC19" t="s">
         <v>139</v>
@@ -10001,13 +9922,13 @@
         <v>32</v>
       </c>
       <c r="DF19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="DG19">
         <v>661177228833</v>
       </c>
       <c r="DH19" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="DI19">
         <v>500001004</v>
@@ -10034,10 +9955,10 @@
         <v>32360</v>
       </c>
       <c r="DQ19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS19">
         <v>9988776655</v>
@@ -10049,7 +9970,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW19" t="s">
         <v>96</v>
@@ -10072,28 +9993,25 @@
       <c r="EC19">
         <v>156</v>
       </c>
-      <c r="ED19" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="20" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G20" t="s">
         <v>74</v>
@@ -10114,7 +10032,7 @@
         <v>79</v>
       </c>
       <c r="N20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O20" t="s">
         <v>80</v>
@@ -10135,16 +10053,16 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="W20" s="9">
         <v>556788901123</v>
       </c>
       <c r="X20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Y20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z20" t="s">
         <v>82</v>
@@ -10156,13 +10074,13 @@
         <v>1</v>
       </c>
       <c r="AD20" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AE20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AF20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG20" s="2">
         <v>44200</v>
@@ -10183,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="AN20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO20" t="s">
         <v>85</v>
@@ -10201,25 +10119,25 @@
         <v>7845066778</v>
       </c>
       <c r="AT20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AU20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AV20" s="8" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AW20" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AX20" t="b">
         <v>0</v>
       </c>
       <c r="AY20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="BA20" t="b">
         <v>1</v>
@@ -10228,16 +10146,16 @@
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="BD20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="BE20" s="2">
         <v>46007</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG20" t="s">
         <v>89</v>
@@ -10288,10 +10206,10 @@
         <v>45438</v>
       </c>
       <c r="BX20" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="BY20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ20" s="2">
         <v>45965</v>
@@ -10303,13 +10221,13 @@
         <v>81</v>
       </c>
       <c r="CC20" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="CD20" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="CF20" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG20">
         <v>400006</v>
@@ -10318,7 +10236,7 @@
         <v>98</v>
       </c>
       <c r="CI20" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ20" t="s">
         <v>121</v>
@@ -10333,7 +10251,7 @@
         <v>124</v>
       </c>
       <c r="CN20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO20" t="s">
         <v>125</v>
@@ -10354,10 +10272,10 @@
         <v>97</v>
       </c>
       <c r="CU20" t="s">
-        <v>688</v>
+        <v>171</v>
       </c>
       <c r="CV20" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW20" s="5" t="s">
         <v>133</v>
@@ -10375,7 +10293,7 @@
         <v>131</v>
       </c>
       <c r="DB20" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="DC20" t="s">
         <v>139</v>
@@ -10387,13 +10305,13 @@
         <v>32</v>
       </c>
       <c r="DF20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="DG20">
         <v>338844995500</v>
       </c>
       <c r="DH20" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="DI20">
         <v>500001004</v>
@@ -10420,10 +10338,10 @@
         <v>32361</v>
       </c>
       <c r="DQ20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS20">
         <v>9988776655</v>
@@ -10435,7 +10353,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW20" t="s">
         <v>96</v>
@@ -10458,28 +10376,25 @@
       <c r="EC20">
         <v>156</v>
       </c>
-      <c r="ED20" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="21" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:133" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G21" t="s">
         <v>74</v>
@@ -10500,7 +10415,7 @@
         <v>79</v>
       </c>
       <c r="N21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O21" t="s">
         <v>80</v>
@@ -10521,16 +10436,16 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="W21" s="9">
         <v>889011234456</v>
       </c>
       <c r="X21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z21" t="s">
         <v>82</v>
@@ -10542,13 +10457,13 @@
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AE21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AF21" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG21" s="2">
         <v>46235</v>
@@ -10569,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO21" t="s">
         <v>85</v>
@@ -10587,25 +10502,25 @@
         <v>6282077889</v>
       </c>
       <c r="AT21" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AU21" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AV21" s="8" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AW21" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AX21" t="b">
         <v>0</v>
       </c>
       <c r="AY21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AZ21" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="BA21" t="b">
         <v>1</v>
@@ -10614,16 +10529,16 @@
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="BD21" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="BE21" s="2">
         <v>46022</v>
       </c>
       <c r="BF21" s="2" t="s">
-        <v>696</v>
+        <v>565</v>
       </c>
       <c r="BG21" t="s">
         <v>89</v>
@@ -10674,10 +10589,10 @@
         <v>45439</v>
       </c>
       <c r="BX21" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="BY21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BZ21" s="2">
         <v>45596</v>
@@ -10689,22 +10604,22 @@
         <v>81</v>
       </c>
       <c r="CC21" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="CE21" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="CF21" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="CG21" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="CH21" t="s">
         <v>98</v>
       </c>
       <c r="CI21" s="8" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="CJ21" t="s">
         <v>121</v>
@@ -10719,7 +10634,7 @@
         <v>124</v>
       </c>
       <c r="CN21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="CO21" t="s">
         <v>125</v>
@@ -10740,10 +10655,10 @@
         <v>97</v>
       </c>
       <c r="CU21" t="s">
-        <v>689</v>
+        <v>171</v>
       </c>
       <c r="CV21" t="s">
-        <v>695</v>
+        <v>96</v>
       </c>
       <c r="CW21" s="5" t="s">
         <v>133</v>
@@ -10761,7 +10676,7 @@
         <v>131</v>
       </c>
       <c r="DB21" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="DC21" t="s">
         <v>142</v>
@@ -10773,13 +10688,13 @@
         <v>32</v>
       </c>
       <c r="DF21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="DG21">
         <v>994400551166</v>
       </c>
       <c r="DH21" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="DI21">
         <v>500001004</v>
@@ -10806,10 +10721,10 @@
         <v>32362</v>
       </c>
       <c r="DQ21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS21">
         <v>9988776655</v>
@@ -10821,7 +10736,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW21" t="s">
         <v>96</v>
@@ -10844,11 +10759,8 @@
       <c r="EC21">
         <v>156</v>
       </c>
-      <c r="ED21" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="22" spans="1:134" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:133" x14ac:dyDescent="0.35">
       <c r="DD22">
         <v>70</v>
       </c>
@@ -10856,13 +10768,13 @@
         <v>32</v>
       </c>
       <c r="DF22" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="DG22">
         <v>338844925500</v>
       </c>
       <c r="DH22" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="DI22">
         <v>500001004</v>
@@ -10889,10 +10801,10 @@
         <v>32363</v>
       </c>
       <c r="DQ22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="DR22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="DS22">
         <v>9988776655</v>
@@ -10904,7 +10816,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="DW22" t="s">
         <v>96</v>
@@ -10926,9 +10838,6 @@
       </c>
       <c r="EC22">
         <v>156</v>
-      </c>
-      <c r="ED22" t="s">
-        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/Jobs/Tasks/FileProcess/TempFile.xlsx
+++ b/Jobs/Tasks/FileProcess/TempFile.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="693">
   <si>
     <t>AgentCode</t>
   </si>
@@ -534,9 +534,6 @@
     <t>Sales Executive</t>
   </si>
   <si>
-    <t>Branch Manager</t>
-  </si>
-  <si>
     <t>PQRST3456U</t>
   </si>
   <si>
@@ -1716,9 +1713,6 @@
     <t>AM25</t>
   </si>
   <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>LIC006</t>
   </si>
   <si>
@@ -2089,6 +2083,21 @@
   </si>
   <si>
     <t>NPSTrngCompletionDate</t>
+  </si>
+  <si>
+    <t>Unit Manager</t>
+  </si>
+  <si>
+    <t>Unit Office</t>
+  </si>
+  <si>
+    <t>BranchDesc</t>
+  </si>
+  <si>
+    <t>Katraj unit Office</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
   </si>
 </sst>
 </file>
@@ -2492,7 +2501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:EC22"/>
+  <dimension ref="A1:ED22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -2553,8 +2562,8 @@
     <col min="56" max="56" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="16" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="11.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="12.26953125" style="8" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="23.26953125" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="17" bestFit="1" customWidth="1"/>
@@ -2575,7 +2584,7 @@
     <col min="79" max="79" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="80" max="80" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="81" max="83" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="6" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="9" bestFit="1" customWidth="1"/>
     <col min="86" max="86" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="28.1796875" style="8" bestFit="1" customWidth="1"/>
@@ -2624,9 +2633,10 @@
     <col min="131" max="131" width="19" bestFit="1" customWidth="1"/>
     <col min="132" max="132" width="14" bestFit="1" customWidth="1"/>
     <col min="133" max="133" width="16" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2652,7 +2662,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -2694,7 +2704,7 @@
         <v>19</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>20</v>
@@ -2801,14 +2811,14 @@
       <c r="BF1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="7" t="s">
         <v>56</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>57</v>
@@ -2817,7 +2827,7 @@
         <v>58</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>59</v>
@@ -2835,10 +2845,10 @@
         <v>63</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="BT1" s="1" t="s">
         <v>64</v>
@@ -2880,7 +2890,7 @@
         <v>94</v>
       </c>
       <c r="CG1" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="CH1" s="3" t="s">
         <v>95</v>
@@ -3026,26 +3036,29 @@
       <c r="EC1" s="3" t="s">
         <v>168</v>
       </c>
+      <c r="ED1" s="3" t="s">
+        <v>690</v>
+      </c>
     </row>
-    <row r="2" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
         <v>181</v>
-      </c>
-      <c r="B2" t="s">
-        <v>182</v>
       </c>
       <c r="C2" t="str">
         <f>TRIM(B2)</f>
         <v>Bell Murphy</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G2" t="s">
         <v>74</v>
@@ -3066,7 +3079,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O2" t="s">
         <v>80</v>
@@ -3087,16 +3100,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="W2" s="9">
         <v>291830217845</v>
       </c>
       <c r="X2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Y2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Z2" t="s">
         <v>82</v>
@@ -3108,13 +3121,13 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AE2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AF2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG2" s="2">
         <v>44082</v>
@@ -3135,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="AN2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AO2" t="s">
         <v>85</v>
@@ -3153,25 +3166,25 @@
         <v>8129055432</v>
       </c>
       <c r="AT2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AU2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AV2" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AW2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AX2" t="b">
         <v>0</v>
       </c>
       <c r="AY2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BA2" t="b">
         <v>1</v>
@@ -3180,21 +3193,21 @@
         <v>0</v>
       </c>
       <c r="BC2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="BD2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="BE2" s="2">
         <v>45671</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG2" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BH2" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI2" s="2">
@@ -3243,10 +3256,10 @@
         <v>45420</v>
       </c>
       <c r="BX2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="BY2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ2" s="2">
         <v>45377</v>
@@ -3258,16 +3271,16 @@
         <v>81</v>
       </c>
       <c r="CC2" t="s">
+        <v>586</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>587</v>
+      </c>
+      <c r="CE2" t="s">
         <v>588</v>
       </c>
-      <c r="CD2" t="s">
-        <v>589</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>590</v>
-      </c>
       <c r="CF2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG2">
         <v>400050</v>
@@ -3276,7 +3289,7 @@
         <v>98</v>
       </c>
       <c r="CI2" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ2" t="s">
         <v>121</v>
@@ -3291,7 +3304,7 @@
         <v>124</v>
       </c>
       <c r="CN2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO2" t="s">
         <v>125</v>
@@ -3312,10 +3325,10 @@
         <v>97</v>
       </c>
       <c r="CU2" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV2" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW2" s="5" t="s">
         <v>133</v>
@@ -3333,7 +3346,7 @@
         <v>131</v>
       </c>
       <c r="DB2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="DC2" t="s">
         <v>141</v>
@@ -3345,13 +3358,13 @@
         <v>32</v>
       </c>
       <c r="DF2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="DG2">
         <v>829104573612</v>
       </c>
       <c r="DH2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="DI2">
         <v>500001004</v>
@@ -3378,10 +3391,10 @@
         <v>32343</v>
       </c>
       <c r="DQ2" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR2" t="s">
         <v>172</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>173</v>
       </c>
       <c r="DS2">
         <v>9988776657</v>
@@ -3393,7 +3406,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW2" t="s">
         <v>96</v>
@@ -3416,25 +3429,28 @@
       <c r="EC2">
         <v>156</v>
       </c>
+      <c r="ED2" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="3" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G3" t="s">
         <v>74</v>
@@ -3455,7 +3471,7 @@
         <v>78</v>
       </c>
       <c r="N3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O3" t="s">
         <v>80</v>
@@ -3476,16 +3492,16 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="W3" s="9">
         <v>810344529012</v>
       </c>
       <c r="X3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Y3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Z3" t="s">
         <v>82</v>
@@ -3497,13 +3513,13 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AE3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AF3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG3" s="2">
         <v>45028</v>
@@ -3524,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="AN3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AO3" t="s">
         <v>85</v>
@@ -3542,25 +3558,25 @@
         <v>9847012345</v>
       </c>
       <c r="AT3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AU3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AV3" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AW3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AX3" t="b">
         <v>0</v>
       </c>
       <c r="AY3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BA3" t="b">
         <v>1</v>
@@ -3569,21 +3585,21 @@
         <v>0</v>
       </c>
       <c r="BC3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="BD3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="BE3" s="2">
         <v>45716</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG3" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BH3" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI3" s="2">
@@ -3632,10 +3648,10 @@
         <v>45421</v>
       </c>
       <c r="BX3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="BY3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ3" s="2">
         <v>45860</v>
@@ -3647,16 +3663,16 @@
         <v>81</v>
       </c>
       <c r="CC3" t="s">
+        <v>589</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>590</v>
+      </c>
+      <c r="CE3" t="s">
         <v>591</v>
       </c>
-      <c r="CD3" t="s">
-        <v>592</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>593</v>
-      </c>
       <c r="CF3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG3">
         <v>400053</v>
@@ -3665,7 +3681,7 @@
         <v>98</v>
       </c>
       <c r="CI3" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ3" t="s">
         <v>121</v>
@@ -3680,7 +3696,7 @@
         <v>124</v>
       </c>
       <c r="CN3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO3" t="s">
         <v>125</v>
@@ -3701,10 +3717,10 @@
         <v>97</v>
       </c>
       <c r="CU3" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV3" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW3" s="5" t="s">
         <v>133</v>
@@ -3722,7 +3738,7 @@
         <v>131</v>
       </c>
       <c r="DB3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="DC3" t="s">
         <v>140</v>
@@ -3734,13 +3750,13 @@
         <v>32</v>
       </c>
       <c r="DF3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="DG3" s="9">
         <v>473910284756</v>
       </c>
       <c r="DH3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="DI3">
         <v>500001004</v>
@@ -3767,10 +3783,10 @@
         <v>32344</v>
       </c>
       <c r="DQ3" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR3" t="s">
         <v>172</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>173</v>
       </c>
       <c r="DS3">
         <v>9988776655</v>
@@ -3782,7 +3798,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW3" t="s">
         <v>96</v>
@@ -3805,25 +3821,28 @@
       <c r="EC3">
         <v>156</v>
       </c>
+      <c r="ED3" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="4" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G4" t="s">
         <v>74</v>
@@ -3844,7 +3863,7 @@
         <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O4" t="s">
         <v>80</v>
@@ -3865,16 +3884,16 @@
         <v>1</v>
       </c>
       <c r="V4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="W4" s="9">
         <v>456712348901</v>
       </c>
       <c r="X4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Y4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z4" t="s">
         <v>82</v>
@@ -3886,13 +3905,13 @@
         <v>1</v>
       </c>
       <c r="AD4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AE4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AF4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG4" s="2">
         <v>45678</v>
@@ -3904,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="8" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AK4" s="8" t="s">
         <v>83</v>
@@ -3916,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="AN4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AO4" t="s">
         <v>85</v>
@@ -3934,25 +3953,25 @@
         <v>7736088990</v>
       </c>
       <c r="AT4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AU4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AW4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AX4" t="b">
         <v>0</v>
       </c>
       <c r="AY4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BA4" t="b">
         <v>1</v>
@@ -3961,21 +3980,21 @@
         <v>0</v>
       </c>
       <c r="BC4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BD4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="BE4" s="2">
         <v>45731</v>
       </c>
       <c r="BF4" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG4" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BH4" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI4" s="2">
@@ -4024,10 +4043,10 @@
         <v>45422</v>
       </c>
       <c r="BX4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="BY4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ4" s="2">
         <v>45423</v>
@@ -4039,16 +4058,16 @@
         <v>81</v>
       </c>
       <c r="CC4" t="s">
+        <v>592</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>593</v>
+      </c>
+      <c r="CE4" t="s">
         <v>594</v>
       </c>
-      <c r="CD4" t="s">
-        <v>595</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>596</v>
-      </c>
       <c r="CF4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG4">
         <v>400089</v>
@@ -4057,7 +4076,7 @@
         <v>98</v>
       </c>
       <c r="CI4" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ4" t="s">
         <v>121</v>
@@ -4072,7 +4091,7 @@
         <v>124</v>
       </c>
       <c r="CN4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO4" t="s">
         <v>125</v>
@@ -4093,10 +4112,10 @@
         <v>97</v>
       </c>
       <c r="CU4" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV4" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW4" s="5" t="s">
         <v>133</v>
@@ -4114,7 +4133,7 @@
         <v>131</v>
       </c>
       <c r="DB4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="DC4" t="s">
         <v>139</v>
@@ -4126,13 +4145,13 @@
         <v>32</v>
       </c>
       <c r="DF4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DG4">
         <v>109283746501</v>
       </c>
       <c r="DH4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="DI4">
         <v>500001004</v>
@@ -4159,10 +4178,10 @@
         <v>32345</v>
       </c>
       <c r="DQ4" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR4" t="s">
         <v>172</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>173</v>
       </c>
       <c r="DS4">
         <v>9988776655</v>
@@ -4174,7 +4193,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW4" t="s">
         <v>96</v>
@@ -4197,25 +4216,28 @@
       <c r="EC4">
         <v>156</v>
       </c>
+      <c r="ED4" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="5" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
         <v>74</v>
@@ -4236,7 +4258,7 @@
         <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O5" t="s">
         <v>80</v>
@@ -4257,16 +4279,16 @@
         <v>1</v>
       </c>
       <c r="V5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="W5" s="9">
         <v>773200193345</v>
       </c>
       <c r="X5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Y5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Z5" t="s">
         <v>82</v>
@@ -4278,13 +4300,13 @@
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AE5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AF5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG5" s="2">
         <v>44530</v>
@@ -4305,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="AN5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AO5" t="s">
         <v>85</v>
@@ -4323,25 +4345,25 @@
         <v>6235109876</v>
       </c>
       <c r="AT5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AU5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AV5" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AW5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AX5" t="b">
         <v>0</v>
       </c>
       <c r="AY5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="BA5" t="b">
         <v>1</v>
@@ -4350,21 +4372,21 @@
         <v>0</v>
       </c>
       <c r="BC5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BD5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="BE5" s="2">
         <v>45750</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG5" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH5" t="s">
+      <c r="BH5" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI5" s="2">
@@ -4413,10 +4435,10 @@
         <v>45423</v>
       </c>
       <c r="BX5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="BY5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ5" s="2">
         <v>45663</v>
@@ -4428,16 +4450,16 @@
         <v>81</v>
       </c>
       <c r="CC5" t="s">
+        <v>595</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>596</v>
+      </c>
+      <c r="CE5" t="s">
         <v>597</v>
       </c>
-      <c r="CD5" t="s">
-        <v>598</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>599</v>
-      </c>
       <c r="CF5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG5">
         <v>400028</v>
@@ -4446,7 +4468,7 @@
         <v>98</v>
       </c>
       <c r="CI5" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ5" t="s">
         <v>121</v>
@@ -4461,7 +4483,7 @@
         <v>124</v>
       </c>
       <c r="CN5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO5" t="s">
         <v>125</v>
@@ -4482,10 +4504,10 @@
         <v>97</v>
       </c>
       <c r="CU5" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV5" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW5" s="5" t="s">
         <v>133</v>
@@ -4503,7 +4525,7 @@
         <v>131</v>
       </c>
       <c r="DB5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="DC5" t="s">
         <v>139</v>
@@ -4515,13 +4537,13 @@
         <v>32</v>
       </c>
       <c r="DF5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="DG5">
         <v>556473829102</v>
       </c>
       <c r="DH5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="DI5">
         <v>500001004</v>
@@ -4548,10 +4570,10 @@
         <v>32346</v>
       </c>
       <c r="DQ5" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR5" t="s">
         <v>172</v>
-      </c>
-      <c r="DR5" t="s">
-        <v>173</v>
       </c>
       <c r="DS5">
         <v>9988776655</v>
@@ -4563,7 +4585,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW5" t="s">
         <v>96</v>
@@ -4586,25 +4608,28 @@
       <c r="EC5">
         <v>156</v>
       </c>
+      <c r="ED5" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="6" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G6" t="s">
         <v>74</v>
@@ -4625,7 +4650,7 @@
         <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O6" t="s">
         <v>80</v>
@@ -4646,16 +4671,16 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="W6" s="9">
         <v>109855672210</v>
       </c>
       <c r="X6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Y6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Z6" t="s">
         <v>82</v>
@@ -4667,13 +4692,13 @@
         <v>1</v>
       </c>
       <c r="AD6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AE6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AF6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG6" s="2">
         <v>45488</v>
@@ -4694,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="AN6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AO6" t="s">
         <v>85</v>
@@ -4712,25 +4737,25 @@
         <v>9447056789</v>
       </c>
       <c r="AT6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AU6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AV6" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AW6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AX6" t="b">
         <v>0</v>
       </c>
       <c r="AY6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BA6" t="b">
         <v>1</v>
@@ -4739,21 +4764,21 @@
         <v>0</v>
       </c>
       <c r="BC6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="BD6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="BE6" s="2">
         <v>45769</v>
       </c>
       <c r="BF6" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG6" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH6" t="s">
+      <c r="BH6" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI6" s="2">
@@ -4802,10 +4827,10 @@
         <v>45424</v>
       </c>
       <c r="BX6" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="BY6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ6" s="2">
         <v>45501</v>
@@ -4817,16 +4842,16 @@
         <v>81</v>
       </c>
       <c r="CC6" t="s">
+        <v>598</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>599</v>
+      </c>
+      <c r="CE6" t="s">
         <v>600</v>
       </c>
-      <c r="CD6" t="s">
-        <v>601</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>602</v>
-      </c>
       <c r="CF6" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG6">
         <v>400030</v>
@@ -4835,7 +4860,7 @@
         <v>98</v>
       </c>
       <c r="CI6" s="8" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="CJ6" t="s">
         <v>121</v>
@@ -4850,7 +4875,7 @@
         <v>124</v>
       </c>
       <c r="CN6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO6" t="s">
         <v>125</v>
@@ -4871,10 +4896,10 @@
         <v>97</v>
       </c>
       <c r="CU6" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV6" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW6" s="5" t="s">
         <v>133</v>
@@ -4892,7 +4917,7 @@
         <v>131</v>
       </c>
       <c r="DB6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="DC6" t="s">
         <v>142</v>
@@ -4904,13 +4929,13 @@
         <v>32</v>
       </c>
       <c r="DF6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="DG6">
         <v>901827364519</v>
       </c>
       <c r="DH6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="DI6">
         <v>500001004</v>
@@ -4937,10 +4962,10 @@
         <v>32347</v>
       </c>
       <c r="DQ6" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR6" t="s">
         <v>172</v>
-      </c>
-      <c r="DR6" t="s">
-        <v>173</v>
       </c>
       <c r="DS6">
         <v>9988776655</v>
@@ -4952,7 +4977,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW6" t="s">
         <v>96</v>
@@ -4975,25 +5000,28 @@
       <c r="EC6">
         <v>156</v>
       </c>
+      <c r="ED6" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="7" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G7" t="s">
         <v>74</v>
@@ -5014,7 +5042,7 @@
         <v>78</v>
       </c>
       <c r="N7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O7" t="s">
         <v>80</v>
@@ -5035,16 +5063,16 @@
         <v>1</v>
       </c>
       <c r="V7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="W7" s="9">
         <v>654399871123</v>
       </c>
       <c r="X7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Y7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Z7" t="s">
         <v>82</v>
@@ -5056,13 +5084,13 @@
         <v>1</v>
       </c>
       <c r="AD7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AE7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AF7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AG7" s="2">
         <v>46297</v>
@@ -5083,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="AN7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AO7" t="s">
         <v>85</v>
@@ -5101,25 +5129,25 @@
         <v>8547123456</v>
       </c>
       <c r="AT7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AU7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AV7" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AW7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AX7" t="b">
         <v>0</v>
       </c>
       <c r="AY7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="BA7" t="b">
         <v>1</v>
@@ -5128,21 +5156,21 @@
         <v>0</v>
       </c>
       <c r="BC7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="BD7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="BE7" s="2">
         <v>45787</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG7" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH7" t="s">
+      <c r="BH7" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI7" s="2">
@@ -5191,10 +5219,10 @@
         <v>45425</v>
       </c>
       <c r="BX7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="BY7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ7" s="2">
         <v>45826</v>
@@ -5206,16 +5234,16 @@
         <v>81</v>
       </c>
       <c r="CC7" t="s">
+        <v>601</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>602</v>
+      </c>
+      <c r="CE7" t="s">
         <v>603</v>
       </c>
-      <c r="CD7" t="s">
-        <v>604</v>
-      </c>
-      <c r="CE7" t="s">
-        <v>605</v>
-      </c>
       <c r="CF7" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG7">
         <v>400030</v>
@@ -5224,7 +5252,7 @@
         <v>98</v>
       </c>
       <c r="CI7" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ7" t="s">
         <v>121</v>
@@ -5239,7 +5267,7 @@
         <v>124</v>
       </c>
       <c r="CN7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO7" t="s">
         <v>125</v>
@@ -5260,10 +5288,10 @@
         <v>97</v>
       </c>
       <c r="CU7" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV7" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW7" s="5" t="s">
         <v>133</v>
@@ -5281,7 +5309,7 @@
         <v>131</v>
       </c>
       <c r="DB7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="DC7" t="s">
         <v>141</v>
@@ -5293,13 +5321,13 @@
         <v>32</v>
       </c>
       <c r="DF7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="DG7">
         <v>234567890123</v>
       </c>
       <c r="DH7" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="DI7">
         <v>500001004</v>
@@ -5326,10 +5354,10 @@
         <v>32348</v>
       </c>
       <c r="DQ7" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR7" t="s">
         <v>172</v>
-      </c>
-      <c r="DR7" t="s">
-        <v>173</v>
       </c>
       <c r="DS7">
         <v>9988776655</v>
@@ -5341,7 +5369,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW7" t="s">
         <v>96</v>
@@ -5364,25 +5392,28 @@
       <c r="EC7">
         <v>156</v>
       </c>
+      <c r="ED7" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="8" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
         <v>73</v>
@@ -5403,7 +5434,7 @@
         <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O8" t="s">
         <v>80</v>
@@ -5424,16 +5455,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W8" s="9">
         <v>334566784456</v>
       </c>
       <c r="X8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Y8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Z8" t="s">
         <v>82</v>
@@ -5445,13 +5476,13 @@
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AE8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AF8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG8" s="2">
         <v>43912</v>
@@ -5472,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="AN8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO8" t="s">
         <v>85</v>
@@ -5490,25 +5521,25 @@
         <v>7025034567</v>
       </c>
       <c r="AT8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AU8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AV8" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AW8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AX8" t="b">
         <v>0</v>
       </c>
       <c r="AY8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="BA8" t="b">
         <v>1</v>
@@ -5517,21 +5548,21 @@
         <v>0</v>
       </c>
       <c r="BC8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="BD8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BE8" s="2">
         <v>45815</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG8" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH8" t="s">
+      <c r="BH8" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI8" s="2">
@@ -5580,10 +5611,10 @@
         <v>45426</v>
       </c>
       <c r="BX8" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="BY8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ8" s="2">
         <v>45907</v>
@@ -5595,13 +5626,13 @@
         <v>81</v>
       </c>
       <c r="CC8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="CE8" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="CF8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG8">
         <v>400077</v>
@@ -5610,7 +5641,7 @@
         <v>98</v>
       </c>
       <c r="CI8" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ8" t="s">
         <v>121</v>
@@ -5625,7 +5656,7 @@
         <v>124</v>
       </c>
       <c r="CN8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO8" t="s">
         <v>125</v>
@@ -5646,10 +5677,10 @@
         <v>97</v>
       </c>
       <c r="CU8" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV8" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW8" s="5" t="s">
         <v>133</v>
@@ -5667,7 +5698,7 @@
         <v>131</v>
       </c>
       <c r="DB8" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="DC8" t="s">
         <v>140</v>
@@ -5679,13 +5710,13 @@
         <v>32</v>
       </c>
       <c r="DF8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="DG8">
         <v>678901234567</v>
       </c>
       <c r="DH8" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="DI8">
         <v>500001004</v>
@@ -5712,10 +5743,10 @@
         <v>32349</v>
       </c>
       <c r="DQ8" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR8" t="s">
         <v>172</v>
-      </c>
-      <c r="DR8" t="s">
-        <v>173</v>
       </c>
       <c r="DS8">
         <v>9988776655</v>
@@ -5727,7 +5758,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW8" t="s">
         <v>96</v>
@@ -5750,25 +5781,28 @@
       <c r="EC8">
         <v>156</v>
       </c>
+      <c r="ED8" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="9" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
         <v>74</v>
@@ -5789,7 +5823,7 @@
         <v>78</v>
       </c>
       <c r="N9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O9" t="s">
         <v>80</v>
@@ -5810,16 +5844,16 @@
         <v>1</v>
       </c>
       <c r="V9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="W9" s="9">
         <v>901233456789</v>
       </c>
       <c r="X9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Y9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Z9" t="s">
         <v>82</v>
@@ -5831,13 +5865,13 @@
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AE9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG9" s="2">
         <v>44792</v>
@@ -5858,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="AN9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AO9" t="s">
         <v>85</v>
@@ -5876,25 +5910,25 @@
         <v>6365045678</v>
       </c>
       <c r="AT9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AU9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AV9" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AW9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AX9" t="b">
         <v>0</v>
       </c>
       <c r="AY9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="BA9" t="b">
         <v>1</v>
@@ -5903,21 +5937,21 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BD9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="BE9" s="2">
         <v>45833</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG9" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="BH9" t="s">
+      <c r="BH9" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BI9" s="2">
@@ -5966,10 +6000,10 @@
         <v>45427</v>
       </c>
       <c r="BX9" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="BY9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ9" s="2">
         <v>45476</v>
@@ -5981,16 +6015,16 @@
         <v>81</v>
       </c>
       <c r="CC9" t="s">
+        <v>606</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>607</v>
+      </c>
+      <c r="CE9" t="s">
         <v>608</v>
       </c>
-      <c r="CD9" t="s">
-        <v>609</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>610</v>
-      </c>
       <c r="CF9" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG9">
         <v>400049</v>
@@ -5999,7 +6033,7 @@
         <v>98</v>
       </c>
       <c r="CI9" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ9" t="s">
         <v>121</v>
@@ -6014,7 +6048,7 @@
         <v>124</v>
       </c>
       <c r="CN9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO9" t="s">
         <v>125</v>
@@ -6035,10 +6069,10 @@
         <v>97</v>
       </c>
       <c r="CU9" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV9" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW9" s="5" t="s">
         <v>133</v>
@@ -6056,7 +6090,7 @@
         <v>131</v>
       </c>
       <c r="DB9" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="DC9" t="s">
         <v>139</v>
@@ -6068,13 +6102,13 @@
         <v>32</v>
       </c>
       <c r="DF9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="DG9">
         <v>345678901234</v>
       </c>
       <c r="DH9" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="DI9">
         <v>500001004</v>
@@ -6101,10 +6135,10 @@
         <v>32350</v>
       </c>
       <c r="DQ9" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR9" t="s">
         <v>172</v>
-      </c>
-      <c r="DR9" t="s">
-        <v>173</v>
       </c>
       <c r="DS9">
         <v>9988776655</v>
@@ -6116,7 +6150,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW9" t="s">
         <v>96</v>
@@ -6139,25 +6173,28 @@
       <c r="EC9">
         <v>156</v>
       </c>
+      <c r="ED9" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="10" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G10" t="s">
         <v>74</v>
@@ -6178,7 +6215,7 @@
         <v>78</v>
       </c>
       <c r="N10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O10" t="s">
         <v>80</v>
@@ -6199,16 +6236,16 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="W10" s="9">
         <v>556788901123</v>
       </c>
       <c r="X10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Y10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Z10" t="s">
         <v>82</v>
@@ -6220,13 +6257,13 @@
         <v>1</v>
       </c>
       <c r="AD10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AE10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AF10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG10" s="2">
         <v>45996</v>
@@ -6247,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO10" t="s">
         <v>85</v>
@@ -6265,25 +6302,25 @@
         <v>9946067890</v>
       </c>
       <c r="AT10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AU10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AV10" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AW10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AX10" t="b">
         <v>0</v>
       </c>
       <c r="AY10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ10" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="BA10" t="b">
         <v>1</v>
@@ -6292,18 +6329,18 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="BD10" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BE10" s="2">
         <v>45857</v>
       </c>
       <c r="BF10" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG10" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG10" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI10" s="2">
@@ -6352,10 +6389,10 @@
         <v>45428</v>
       </c>
       <c r="BX10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="BY10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ10" s="2">
         <v>45833</v>
@@ -6367,16 +6404,16 @@
         <v>81</v>
       </c>
       <c r="CC10" t="s">
+        <v>609</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>610</v>
+      </c>
+      <c r="CE10" t="s">
         <v>611</v>
       </c>
-      <c r="CD10" t="s">
-        <v>612</v>
-      </c>
-      <c r="CE10" t="s">
-        <v>613</v>
-      </c>
       <c r="CF10" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG10">
         <v>400049</v>
@@ -6385,7 +6422,7 @@
         <v>98</v>
       </c>
       <c r="CI10" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ10" t="s">
         <v>121</v>
@@ -6400,7 +6437,7 @@
         <v>124</v>
       </c>
       <c r="CN10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO10" t="s">
         <v>125</v>
@@ -6421,10 +6458,10 @@
         <v>97</v>
       </c>
       <c r="CU10" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV10" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW10" s="5" t="s">
         <v>133</v>
@@ -6442,7 +6479,7 @@
         <v>131</v>
       </c>
       <c r="DB10" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="DC10" t="s">
         <v>139</v>
@@ -6454,13 +6491,13 @@
         <v>32</v>
       </c>
       <c r="DF10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="DG10">
         <v>890123456789</v>
       </c>
       <c r="DH10" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="DI10">
         <v>500001004</v>
@@ -6487,10 +6524,10 @@
         <v>32351</v>
       </c>
       <c r="DQ10" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR10" t="s">
         <v>172</v>
-      </c>
-      <c r="DR10" t="s">
-        <v>173</v>
       </c>
       <c r="DS10">
         <v>9988776655</v>
@@ -6502,7 +6539,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW10" t="s">
         <v>96</v>
@@ -6525,25 +6562,28 @@
       <c r="EC10">
         <v>156</v>
       </c>
+      <c r="ED10" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="11" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G11" t="s">
         <v>74</v>
@@ -6564,7 +6604,7 @@
         <v>78</v>
       </c>
       <c r="N11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O11" t="s">
         <v>80</v>
@@ -6585,16 +6625,16 @@
         <v>1</v>
       </c>
       <c r="V11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="W11" s="9">
         <v>223455678890</v>
       </c>
       <c r="X11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Y11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Z11" t="s">
         <v>82</v>
@@ -6606,13 +6646,13 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AE11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AF11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG11" s="2">
         <v>45105</v>
@@ -6633,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="AN11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AO11" t="s">
         <v>85</v>
@@ -6651,25 +6691,25 @@
         <v>8891078901</v>
       </c>
       <c r="AT11" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AU11" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AW11" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AX11" t="b">
         <v>0</v>
       </c>
       <c r="AY11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="BA11" t="b">
         <v>1</v>
@@ -6678,18 +6718,18 @@
         <v>0</v>
       </c>
       <c r="BC11" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="BD11" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BE11" s="2">
         <v>45870</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG11" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG11" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI11" s="2">
@@ -6738,10 +6778,10 @@
         <v>45429</v>
       </c>
       <c r="BX11" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="BY11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ11" s="2">
         <v>45394</v>
@@ -6753,16 +6793,16 @@
         <v>81</v>
       </c>
       <c r="CC11" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="CD11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="CE11" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="CF11" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG11">
         <v>400049</v>
@@ -6771,7 +6811,7 @@
         <v>98</v>
       </c>
       <c r="CI11" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ11" t="s">
         <v>121</v>
@@ -6786,7 +6826,7 @@
         <v>124</v>
       </c>
       <c r="CN11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO11" t="s">
         <v>125</v>
@@ -6807,10 +6847,10 @@
         <v>97</v>
       </c>
       <c r="CU11" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV11" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW11" s="5" t="s">
         <v>133</v>
@@ -6828,7 +6868,7 @@
         <v>131</v>
       </c>
       <c r="DB11" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="DC11" t="s">
         <v>142</v>
@@ -6840,13 +6880,13 @@
         <v>32</v>
       </c>
       <c r="DF11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="DG11">
         <v>123456789012</v>
       </c>
       <c r="DH11" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="DI11">
         <v>500001004</v>
@@ -6873,10 +6913,10 @@
         <v>32352</v>
       </c>
       <c r="DQ11" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR11" t="s">
         <v>172</v>
-      </c>
-      <c r="DR11" t="s">
-        <v>173</v>
       </c>
       <c r="DS11">
         <v>9988776655</v>
@@ -6888,7 +6928,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW11" t="s">
         <v>96</v>
@@ -6911,25 +6951,28 @@
       <c r="EC11">
         <v>156</v>
       </c>
+      <c r="ED11" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="12" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" t="s">
         <v>74</v>
@@ -6950,7 +6993,7 @@
         <v>79</v>
       </c>
       <c r="N12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O12" t="s">
         <v>80</v>
@@ -6971,16 +7014,16 @@
         <v>1</v>
       </c>
       <c r="V12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="W12" s="9">
         <v>889011234456</v>
       </c>
       <c r="X12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Z12" t="s">
         <v>82</v>
@@ -6992,13 +7035,13 @@
         <v>1</v>
       </c>
       <c r="AD12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AE12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AF12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG12" s="2">
         <v>45336</v>
@@ -7019,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AO12" t="s">
         <v>85</v>
@@ -7037,25 +7080,25 @@
         <v>7558089012</v>
       </c>
       <c r="AT12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AU12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AV12" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AW12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AX12" t="b">
         <v>0</v>
       </c>
       <c r="AY12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="BA12" t="b">
         <v>1</v>
@@ -7064,18 +7107,18 @@
         <v>0</v>
       </c>
       <c r="BC12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BD12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BE12" s="2">
         <v>45886</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG12" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG12" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI12" s="2">
@@ -7124,10 +7167,10 @@
         <v>45430</v>
       </c>
       <c r="BX12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="BY12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ12" s="2">
         <v>45700</v>
@@ -7139,16 +7182,16 @@
         <v>81</v>
       </c>
       <c r="CC12" t="s">
+        <v>614</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>615</v>
+      </c>
+      <c r="CE12" t="s">
         <v>616</v>
       </c>
-      <c r="CD12" t="s">
-        <v>617</v>
-      </c>
-      <c r="CE12" t="s">
-        <v>618</v>
-      </c>
       <c r="CF12" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG12">
         <v>400020</v>
@@ -7157,7 +7200,7 @@
         <v>98</v>
       </c>
       <c r="CI12" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ12" t="s">
         <v>121</v>
@@ -7172,7 +7215,7 @@
         <v>124</v>
       </c>
       <c r="CN12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO12" t="s">
         <v>125</v>
@@ -7193,10 +7236,10 @@
         <v>97</v>
       </c>
       <c r="CU12" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV12" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW12" s="5" t="s">
         <v>133</v>
@@ -7214,7 +7257,7 @@
         <v>131</v>
       </c>
       <c r="DB12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="DC12" t="s">
         <v>141</v>
@@ -7226,13 +7269,13 @@
         <v>32</v>
       </c>
       <c r="DF12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="DG12">
         <v>778899001122</v>
       </c>
       <c r="DH12" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="DI12">
         <v>500001004</v>
@@ -7259,10 +7302,10 @@
         <v>32353</v>
       </c>
       <c r="DQ12" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR12" t="s">
         <v>172</v>
-      </c>
-      <c r="DR12" t="s">
-        <v>173</v>
       </c>
       <c r="DS12">
         <v>9988776655</v>
@@ -7274,7 +7317,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW12" t="s">
         <v>96</v>
@@ -7297,25 +7340,28 @@
       <c r="EC12">
         <v>156</v>
       </c>
+      <c r="ED12" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="13" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G13" t="s">
         <v>73</v>
@@ -7336,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O13" t="s">
         <v>80</v>
@@ -7357,16 +7403,16 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="W13" s="9">
         <v>667899012234</v>
       </c>
       <c r="X13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Y13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Z13" t="s">
         <v>82</v>
@@ -7378,13 +7424,13 @@
         <v>1</v>
       </c>
       <c r="AD13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AE13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AF13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG13" s="2">
         <v>44325</v>
@@ -7405,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="AN13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AO13" t="s">
         <v>85</v>
@@ -7423,25 +7469,25 @@
         <v>6005090123</v>
       </c>
       <c r="AT13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AU13" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AV13" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AW13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AX13" t="b">
         <v>0</v>
       </c>
       <c r="AY13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="BA13" t="b">
         <v>1</v>
@@ -7450,18 +7496,18 @@
         <v>0</v>
       </c>
       <c r="BC13" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BD13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="BE13" s="2">
         <v>45912</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG13" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG13" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI13" s="2">
@@ -7510,10 +7556,10 @@
         <v>45431</v>
       </c>
       <c r="BX13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="BY13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ13" s="2">
         <v>45521</v>
@@ -7525,16 +7571,16 @@
         <v>81</v>
       </c>
       <c r="CC13" t="s">
+        <v>617</v>
+      </c>
+      <c r="CD13" t="s">
+        <v>618</v>
+      </c>
+      <c r="CE13" t="s">
         <v>619</v>
       </c>
-      <c r="CD13" t="s">
-        <v>620</v>
-      </c>
-      <c r="CE13" t="s">
-        <v>621</v>
-      </c>
       <c r="CF13" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG13">
         <v>400026</v>
@@ -7543,7 +7589,7 @@
         <v>98</v>
       </c>
       <c r="CI13" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ13" t="s">
         <v>121</v>
@@ -7558,7 +7604,7 @@
         <v>124</v>
       </c>
       <c r="CN13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO13" t="s">
         <v>125</v>
@@ -7579,10 +7625,10 @@
         <v>97</v>
       </c>
       <c r="CU13" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV13" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW13" s="5" t="s">
         <v>133</v>
@@ -7600,7 +7646,7 @@
         <v>131</v>
       </c>
       <c r="DB13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="DC13" t="s">
         <v>140</v>
@@ -7612,13 +7658,13 @@
         <v>32</v>
       </c>
       <c r="DF13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="DG13">
         <v>445566778899</v>
       </c>
       <c r="DH13" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="DI13">
         <v>500001004</v>
@@ -7645,10 +7691,10 @@
         <v>32354</v>
       </c>
       <c r="DQ13" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR13" t="s">
         <v>172</v>
-      </c>
-      <c r="DR13" t="s">
-        <v>173</v>
       </c>
       <c r="DS13">
         <v>9988776655</v>
@@ -7660,7 +7706,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW13" t="s">
         <v>96</v>
@@ -7683,25 +7729,28 @@
       <c r="EC13">
         <v>156</v>
       </c>
+      <c r="ED13" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="14" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G14" t="s">
         <v>74</v>
@@ -7722,7 +7771,7 @@
         <v>79</v>
       </c>
       <c r="N14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O14" t="s">
         <v>80</v>
@@ -7743,16 +7792,16 @@
         <v>1</v>
       </c>
       <c r="V14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="W14" s="9">
         <v>112344567789</v>
       </c>
       <c r="X14" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Y14" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Z14" t="s">
         <v>82</v>
@@ -7764,13 +7813,13 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AF14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG14" s="2">
         <v>46142</v>
@@ -7791,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="AN14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AO14" t="s">
         <v>85</v>
@@ -7809,25 +7858,25 @@
         <v>9037001234</v>
       </c>
       <c r="AT14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AU14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AV14" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AW14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AX14" t="b">
         <v>0</v>
       </c>
       <c r="AY14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="BA14" t="b">
         <v>1</v>
@@ -7836,18 +7885,18 @@
         <v>0</v>
       </c>
       <c r="BC14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BD14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="BE14" s="2">
         <v>45930</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG14" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG14" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI14" s="2">
@@ -7896,10 +7945,10 @@
         <v>45432</v>
       </c>
       <c r="BX14" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="BY14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ14" s="2">
         <v>45837</v>
@@ -7911,16 +7960,16 @@
         <v>81</v>
       </c>
       <c r="CC14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="CD14" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="CE14" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="CF14" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG14">
         <v>400053</v>
@@ -7929,7 +7978,7 @@
         <v>98</v>
       </c>
       <c r="CI14" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ14" t="s">
         <v>121</v>
@@ -7944,7 +7993,7 @@
         <v>124</v>
       </c>
       <c r="CN14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO14" t="s">
         <v>125</v>
@@ -7965,10 +8014,10 @@
         <v>97</v>
       </c>
       <c r="CU14" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV14" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW14" s="5" t="s">
         <v>133</v>
@@ -7986,7 +8035,7 @@
         <v>131</v>
       </c>
       <c r="DB14" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="DC14" t="s">
         <v>139</v>
@@ -7998,13 +8047,13 @@
         <v>32</v>
       </c>
       <c r="DF14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DG14">
         <v>990011223344</v>
       </c>
       <c r="DH14" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="DI14">
         <v>500001004</v>
@@ -8031,10 +8080,10 @@
         <v>32355</v>
       </c>
       <c r="DQ14" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR14" t="s">
         <v>172</v>
-      </c>
-      <c r="DR14" t="s">
-        <v>173</v>
       </c>
       <c r="DS14">
         <v>9988776655</v>
@@ -8046,7 +8095,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW14" t="s">
         <v>96</v>
@@ -8069,25 +8118,28 @@
       <c r="EC14">
         <v>156</v>
       </c>
+      <c r="ED14" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="15" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G15" t="s">
         <v>74</v>
@@ -8108,7 +8160,7 @@
         <v>79</v>
       </c>
       <c r="N15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O15" t="s">
         <v>80</v>
@@ -8129,16 +8181,16 @@
         <v>1</v>
       </c>
       <c r="V15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="W15" s="9">
         <v>445677890012</v>
       </c>
       <c r="X15" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Y15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Z15" t="s">
         <v>82</v>
@@ -8150,13 +8202,13 @@
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AE15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AF15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG15" s="2">
         <v>44176</v>
@@ -8177,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="AN15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AO15" t="s">
         <v>85</v>
@@ -8195,25 +8247,25 @@
         <v>8301011223</v>
       </c>
       <c r="AT15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AU15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AV15" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AW15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AX15" t="b">
         <v>0</v>
       </c>
       <c r="AY15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="BA15" t="b">
         <v>1</v>
@@ -8222,18 +8274,18 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="BD15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="BE15" s="2">
         <v>45935</v>
       </c>
       <c r="BF15" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG15" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG15" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI15" s="2">
@@ -8282,10 +8334,10 @@
         <v>45433</v>
       </c>
       <c r="BX15" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="BY15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ15" s="2">
         <v>45656</v>
@@ -8297,13 +8349,13 @@
         <v>81</v>
       </c>
       <c r="CC15" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="CE15" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="CF15" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG15">
         <v>400063</v>
@@ -8312,7 +8364,7 @@
         <v>98</v>
       </c>
       <c r="CI15" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ15" t="s">
         <v>121</v>
@@ -8327,7 +8379,7 @@
         <v>124</v>
       </c>
       <c r="CN15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO15" t="s">
         <v>125</v>
@@ -8348,10 +8400,10 @@
         <v>97</v>
       </c>
       <c r="CU15" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV15" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW15" s="5" t="s">
         <v>133</v>
@@ -8369,7 +8421,7 @@
         <v>131</v>
       </c>
       <c r="DB15" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="DC15" t="s">
         <v>139</v>
@@ -8381,13 +8433,13 @@
         <v>32</v>
       </c>
       <c r="DF15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="DG15">
         <v>223344556677</v>
       </c>
       <c r="DH15" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="DI15">
         <v>500001004</v>
@@ -8414,10 +8466,10 @@
         <v>32356</v>
       </c>
       <c r="DQ15" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR15" t="s">
         <v>172</v>
-      </c>
-      <c r="DR15" t="s">
-        <v>173</v>
       </c>
       <c r="DS15">
         <v>9988776655</v>
@@ -8429,7 +8481,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW15" t="s">
         <v>96</v>
@@ -8452,25 +8504,28 @@
       <c r="EC15">
         <v>156</v>
       </c>
+      <c r="ED15" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="16" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G16" t="s">
         <v>74</v>
@@ -8491,7 +8546,7 @@
         <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O16" t="s">
         <v>80</v>
@@ -8512,16 +8567,16 @@
         <v>1</v>
       </c>
       <c r="V16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="W16" s="9">
         <v>990122345567</v>
       </c>
       <c r="X16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z16" t="s">
         <v>82</v>
@@ -8533,13 +8588,13 @@
         <v>1</v>
       </c>
       <c r="AD16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AE16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AF16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG16" s="2">
         <v>44859</v>
@@ -8560,7 +8615,7 @@
         <v>1</v>
       </c>
       <c r="AN16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO16" t="s">
         <v>85</v>
@@ -8578,25 +8633,25 @@
         <v>7205022334</v>
       </c>
       <c r="AT16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AU16" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AV16" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AW16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AX16" t="b">
         <v>0</v>
       </c>
       <c r="AY16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="BA16" t="b">
         <v>1</v>
@@ -8605,18 +8660,18 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="BD16" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="BE16" s="2">
         <v>45951</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG16" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG16" s="8" t="s">
         <v>88</v>
       </c>
       <c r="BI16" s="2">
@@ -8665,10 +8720,10 @@
         <v>45434</v>
       </c>
       <c r="BX16" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="BY16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ16" s="2">
         <v>45819</v>
@@ -8680,16 +8735,16 @@
         <v>81</v>
       </c>
       <c r="CC16" t="s">
+        <v>624</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>625</v>
+      </c>
+      <c r="CE16" t="s">
         <v>626</v>
       </c>
-      <c r="CD16" t="s">
-        <v>627</v>
-      </c>
-      <c r="CE16" t="s">
-        <v>628</v>
-      </c>
       <c r="CF16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG16">
         <v>400070</v>
@@ -8698,7 +8753,7 @@
         <v>98</v>
       </c>
       <c r="CI16" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ16" t="s">
         <v>121</v>
@@ -8713,7 +8768,7 @@
         <v>124</v>
       </c>
       <c r="CN16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO16" t="s">
         <v>125</v>
@@ -8734,10 +8789,10 @@
         <v>97</v>
       </c>
       <c r="CU16" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV16" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW16" s="5" t="s">
         <v>133</v>
@@ -8755,7 +8810,7 @@
         <v>131</v>
       </c>
       <c r="DB16" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="DC16" t="s">
         <v>142</v>
@@ -8767,13 +8822,13 @@
         <v>32</v>
       </c>
       <c r="DF16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="DG16">
         <v>550066117722</v>
       </c>
       <c r="DH16" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="DI16">
         <v>500001004</v>
@@ -8800,10 +8855,10 @@
         <v>32357</v>
       </c>
       <c r="DQ16" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR16" t="s">
         <v>172</v>
-      </c>
-      <c r="DR16" t="s">
-        <v>173</v>
       </c>
       <c r="DS16">
         <v>9988776655</v>
@@ -8815,7 +8870,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW16" t="s">
         <v>96</v>
@@ -8838,25 +8893,28 @@
       <c r="EC16">
         <v>156</v>
       </c>
+      <c r="ED16" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="17" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -8877,7 +8935,7 @@
         <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O17" t="s">
         <v>80</v>
@@ -8898,16 +8956,16 @@
         <v>1</v>
       </c>
       <c r="V17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="W17" s="9">
         <v>334566789901</v>
       </c>
       <c r="X17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Y17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Z17" t="s">
         <v>82</v>
@@ -8919,13 +8977,13 @@
         <v>1</v>
       </c>
       <c r="AD17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE17" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AF17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG17" s="2">
         <v>45845</v>
@@ -8946,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="AN17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AO17" t="s">
         <v>85</v>
@@ -8964,25 +9022,25 @@
         <v>6145033445</v>
       </c>
       <c r="AT17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AU17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AV17" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AW17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AX17" t="b">
         <v>0</v>
       </c>
       <c r="AY17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="BA17" t="b">
         <v>1</v>
@@ -8991,18 +9049,18 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="BD17" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="BE17" s="2">
         <v>45969</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG17" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG17" s="8" t="s">
         <v>89</v>
       </c>
       <c r="BI17" s="2">
@@ -9051,10 +9109,10 @@
         <v>45435</v>
       </c>
       <c r="BX17" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="BY17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ17" s="2">
         <v>45306</v>
@@ -9066,13 +9124,13 @@
         <v>81</v>
       </c>
       <c r="CC17" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="CE17" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="CF17" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG17">
         <v>400077</v>
@@ -9081,7 +9139,7 @@
         <v>98</v>
       </c>
       <c r="CI17" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ17" t="s">
         <v>121</v>
@@ -9096,7 +9154,7 @@
         <v>124</v>
       </c>
       <c r="CN17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO17" t="s">
         <v>125</v>
@@ -9117,10 +9175,10 @@
         <v>97</v>
       </c>
       <c r="CU17" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV17" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW17" s="5" t="s">
         <v>133</v>
@@ -9138,7 +9196,7 @@
         <v>131</v>
       </c>
       <c r="DB17" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="DC17" t="s">
         <v>141</v>
@@ -9150,13 +9208,13 @@
         <v>32</v>
       </c>
       <c r="DF17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="DG17">
         <v>883399440055</v>
       </c>
       <c r="DH17" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="DI17">
         <v>500001004</v>
@@ -9183,10 +9241,10 @@
         <v>32358</v>
       </c>
       <c r="DQ17" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR17" t="s">
         <v>172</v>
-      </c>
-      <c r="DR17" t="s">
-        <v>173</v>
       </c>
       <c r="DS17">
         <v>9988776655</v>
@@ -9198,7 +9256,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW17" t="s">
         <v>96</v>
@@ -9221,25 +9279,28 @@
       <c r="EC17">
         <v>156</v>
       </c>
+      <c r="ED17" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="18" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G18" t="s">
         <v>74</v>
@@ -9260,7 +9321,7 @@
         <v>79</v>
       </c>
       <c r="N18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O18" t="s">
         <v>80</v>
@@ -9281,16 +9342,16 @@
         <v>1</v>
       </c>
       <c r="V18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="W18" s="9">
         <v>778900123345</v>
       </c>
       <c r="X18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Y18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Z18" t="s">
         <v>82</v>
@@ -9302,13 +9363,13 @@
         <v>1</v>
       </c>
       <c r="AD18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AE18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AF18" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG18" s="2">
         <v>45186</v>
@@ -9329,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="AN18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AO18" t="s">
         <v>85</v>
@@ -9347,25 +9408,25 @@
         <v>9176044556</v>
       </c>
       <c r="AT18" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AU18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AV18" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AW18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AX18" t="b">
         <v>0</v>
       </c>
       <c r="AY18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BA18" t="b">
         <v>1</v>
@@ -9374,18 +9435,18 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="BD18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="BE18" s="2">
         <v>45990</v>
       </c>
       <c r="BF18" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG18" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG18" s="8" t="s">
         <v>89</v>
       </c>
       <c r="BI18" s="2">
@@ -9434,10 +9495,10 @@
         <v>45436</v>
       </c>
       <c r="BX18" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="BY18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ18" s="2">
         <v>45726</v>
@@ -9449,16 +9510,16 @@
         <v>81</v>
       </c>
       <c r="CC18" t="s">
+        <v>629</v>
+      </c>
+      <c r="CD18" t="s">
+        <v>630</v>
+      </c>
+      <c r="CE18" t="s">
         <v>631</v>
       </c>
-      <c r="CD18" t="s">
-        <v>632</v>
-      </c>
-      <c r="CE18" t="s">
-        <v>633</v>
-      </c>
       <c r="CF18" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG18">
         <v>400022</v>
@@ -9467,7 +9528,7 @@
         <v>98</v>
       </c>
       <c r="CI18" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ18" t="s">
         <v>121</v>
@@ -9482,7 +9543,7 @@
         <v>124</v>
       </c>
       <c r="CN18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO18" t="s">
         <v>125</v>
@@ -9503,10 +9564,10 @@
         <v>97</v>
       </c>
       <c r="CU18" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV18" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW18" s="5" t="s">
         <v>133</v>
@@ -9524,7 +9585,7 @@
         <v>131</v>
       </c>
       <c r="DB18" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="DC18" t="s">
         <v>140</v>
@@ -9536,13 +9597,13 @@
         <v>32</v>
       </c>
       <c r="DF18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="DG18">
         <v>116622773388</v>
       </c>
       <c r="DH18" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="DI18">
         <v>500001004</v>
@@ -9569,10 +9630,10 @@
         <v>32359</v>
       </c>
       <c r="DQ18" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR18" t="s">
         <v>172</v>
-      </c>
-      <c r="DR18" t="s">
-        <v>173</v>
       </c>
       <c r="DS18">
         <v>9988776655</v>
@@ -9584,7 +9645,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW18" t="s">
         <v>96</v>
@@ -9607,25 +9668,28 @@
       <c r="EC18">
         <v>156</v>
       </c>
+      <c r="ED18" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="19" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G19" t="s">
         <v>74</v>
@@ -9646,7 +9710,7 @@
         <v>79</v>
       </c>
       <c r="N19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O19" t="s">
         <v>80</v>
@@ -9667,16 +9731,16 @@
         <v>1</v>
       </c>
       <c r="V19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="W19" s="9">
         <v>1233456678</v>
       </c>
       <c r="X19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z19" t="s">
         <v>82</v>
@@ -9688,13 +9752,13 @@
         <v>1</v>
       </c>
       <c r="AD19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AE19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AF19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG19" s="2">
         <v>45616</v>
@@ -9715,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="AN19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO19" t="s">
         <v>85</v>
@@ -9733,25 +9797,25 @@
         <v>8606055667</v>
       </c>
       <c r="AT19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AU19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AV19" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AW19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AX19" t="b">
         <v>0</v>
       </c>
       <c r="AY19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="BA19" t="b">
         <v>1</v>
@@ -9760,18 +9824,18 @@
         <v>0</v>
       </c>
       <c r="BC19" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BD19" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="BE19" s="2">
         <v>45995</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG19" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG19" s="8" t="s">
         <v>89</v>
       </c>
       <c r="BI19" s="2">
@@ -9820,10 +9884,10 @@
         <v>45437</v>
       </c>
       <c r="BX19" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="BY19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ19" s="2">
         <v>45556</v>
@@ -9835,16 +9899,16 @@
         <v>81</v>
       </c>
       <c r="CC19" t="s">
+        <v>632</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>633</v>
+      </c>
+      <c r="CE19" t="s">
         <v>634</v>
       </c>
-      <c r="CD19" t="s">
-        <v>635</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>636</v>
-      </c>
       <c r="CF19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG19">
         <v>400005</v>
@@ -9853,7 +9917,7 @@
         <v>98</v>
       </c>
       <c r="CI19" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ19" t="s">
         <v>121</v>
@@ -9868,7 +9932,7 @@
         <v>124</v>
       </c>
       <c r="CN19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO19" t="s">
         <v>125</v>
@@ -9889,10 +9953,10 @@
         <v>97</v>
       </c>
       <c r="CU19" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV19" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW19" s="5" t="s">
         <v>133</v>
@@ -9910,7 +9974,7 @@
         <v>131</v>
       </c>
       <c r="DB19" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="DC19" t="s">
         <v>139</v>
@@ -9922,13 +9986,13 @@
         <v>32</v>
       </c>
       <c r="DF19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="DG19">
         <v>661177228833</v>
       </c>
       <c r="DH19" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="DI19">
         <v>500001004</v>
@@ -9955,10 +10019,10 @@
         <v>32360</v>
       </c>
       <c r="DQ19" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR19" t="s">
         <v>172</v>
-      </c>
-      <c r="DR19" t="s">
-        <v>173</v>
       </c>
       <c r="DS19">
         <v>9988776655</v>
@@ -9970,7 +10034,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW19" t="s">
         <v>96</v>
@@ -9993,25 +10057,28 @@
       <c r="EC19">
         <v>156</v>
       </c>
+      <c r="ED19" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="20" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F20" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G20" t="s">
         <v>74</v>
@@ -10032,7 +10099,7 @@
         <v>79</v>
       </c>
       <c r="N20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O20" t="s">
         <v>80</v>
@@ -10053,16 +10120,16 @@
         <v>1</v>
       </c>
       <c r="V20" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="W20" s="9">
         <v>556788901123</v>
       </c>
       <c r="X20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Z20" t="s">
         <v>82</v>
@@ -10074,13 +10141,13 @@
         <v>1</v>
       </c>
       <c r="AD20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AE20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AF20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG20" s="2">
         <v>44200</v>
@@ -10101,7 +10168,7 @@
         <v>1</v>
       </c>
       <c r="AN20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO20" t="s">
         <v>85</v>
@@ -10119,25 +10186,25 @@
         <v>7845066778</v>
       </c>
       <c r="AT20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AU20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AV20" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AW20" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AX20" t="b">
         <v>0</v>
       </c>
       <c r="AY20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BA20" t="b">
         <v>1</v>
@@ -10146,18 +10213,18 @@
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="BD20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="BE20" s="2">
         <v>46007</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG20" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG20" s="8" t="s">
         <v>89</v>
       </c>
       <c r="BI20" s="2">
@@ -10206,10 +10273,10 @@
         <v>45438</v>
       </c>
       <c r="BX20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BY20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ20" s="2">
         <v>45965</v>
@@ -10221,13 +10288,13 @@
         <v>81</v>
       </c>
       <c r="CC20" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="CD20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="CF20" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG20">
         <v>400006</v>
@@ -10236,7 +10303,7 @@
         <v>98</v>
       </c>
       <c r="CI20" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ20" t="s">
         <v>121</v>
@@ -10251,7 +10318,7 @@
         <v>124</v>
       </c>
       <c r="CN20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO20" t="s">
         <v>125</v>
@@ -10272,10 +10339,10 @@
         <v>97</v>
       </c>
       <c r="CU20" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV20" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW20" s="5" t="s">
         <v>133</v>
@@ -10293,7 +10360,7 @@
         <v>131</v>
       </c>
       <c r="DB20" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="DC20" t="s">
         <v>139</v>
@@ -10305,13 +10372,13 @@
         <v>32</v>
       </c>
       <c r="DF20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="DG20">
         <v>338844995500</v>
       </c>
       <c r="DH20" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="DI20">
         <v>500001004</v>
@@ -10338,10 +10405,10 @@
         <v>32361</v>
       </c>
       <c r="DQ20" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR20" t="s">
         <v>172</v>
-      </c>
-      <c r="DR20" t="s">
-        <v>173</v>
       </c>
       <c r="DS20">
         <v>9988776655</v>
@@ -10353,7 +10420,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW20" t="s">
         <v>96</v>
@@ -10376,25 +10443,28 @@
       <c r="EC20">
         <v>156</v>
       </c>
+      <c r="ED20" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="21" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:134" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G21" t="s">
         <v>74</v>
@@ -10415,7 +10485,7 @@
         <v>79</v>
       </c>
       <c r="N21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O21" t="s">
         <v>80</v>
@@ -10436,16 +10506,16 @@
         <v>1</v>
       </c>
       <c r="V21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="W21" s="9">
         <v>889011234456</v>
       </c>
       <c r="X21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Z21" t="s">
         <v>82</v>
@@ -10457,13 +10527,13 @@
         <v>1</v>
       </c>
       <c r="AD21" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AE21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AF21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG21" s="2">
         <v>46235</v>
@@ -10484,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AO21" t="s">
         <v>85</v>
@@ -10502,25 +10572,25 @@
         <v>6282077889</v>
       </c>
       <c r="AT21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AU21" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AV21" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AW21" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AX21" t="b">
         <v>0</v>
       </c>
       <c r="AY21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AZ21" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="BA21" t="b">
         <v>1</v>
@@ -10529,18 +10599,18 @@
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="BD21" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="BE21" s="2">
         <v>46022</v>
       </c>
       <c r="BF21" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="BG21" t="s">
+        <v>692</v>
+      </c>
+      <c r="BG21" s="8" t="s">
         <v>89</v>
       </c>
       <c r="BI21" s="2">
@@ -10589,10 +10659,10 @@
         <v>45439</v>
       </c>
       <c r="BX21" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="BY21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BZ21" s="2">
         <v>45596</v>
@@ -10604,22 +10674,22 @@
         <v>81</v>
       </c>
       <c r="CC21" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="CE21" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="CF21" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="CG21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="CH21" t="s">
         <v>98</v>
       </c>
       <c r="CI21" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="CJ21" t="s">
         <v>121</v>
@@ -10634,7 +10704,7 @@
         <v>124</v>
       </c>
       <c r="CN21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CO21" t="s">
         <v>125</v>
@@ -10655,10 +10725,10 @@
         <v>97</v>
       </c>
       <c r="CU21" t="s">
-        <v>171</v>
+        <v>688</v>
       </c>
       <c r="CV21" t="s">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="CW21" s="5" t="s">
         <v>133</v>
@@ -10676,7 +10746,7 @@
         <v>131</v>
       </c>
       <c r="DB21" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="DC21" t="s">
         <v>142</v>
@@ -10688,13 +10758,13 @@
         <v>32</v>
       </c>
       <c r="DF21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="DG21">
         <v>994400551166</v>
       </c>
       <c r="DH21" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="DI21">
         <v>500001004</v>
@@ -10721,10 +10791,10 @@
         <v>32362</v>
       </c>
       <c r="DQ21" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR21" t="s">
         <v>172</v>
-      </c>
-      <c r="DR21" t="s">
-        <v>173</v>
       </c>
       <c r="DS21">
         <v>9988776655</v>
@@ -10736,7 +10806,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW21" t="s">
         <v>96</v>
@@ -10759,8 +10829,11 @@
       <c r="EC21">
         <v>156</v>
       </c>
+      <c r="ED21" t="s">
+        <v>691</v>
+      </c>
     </row>
-    <row r="22" spans="1:133" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:134" x14ac:dyDescent="0.35">
       <c r="DD22">
         <v>70</v>
       </c>
@@ -10768,13 +10841,13 @@
         <v>32</v>
       </c>
       <c r="DF22" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="DG22">
         <v>338844925500</v>
       </c>
       <c r="DH22" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="DI22">
         <v>500001004</v>
@@ -10801,10 +10874,10 @@
         <v>32363</v>
       </c>
       <c r="DQ22" t="s">
+        <v>171</v>
+      </c>
+      <c r="DR22" t="s">
         <v>172</v>
-      </c>
-      <c r="DR22" t="s">
-        <v>173</v>
       </c>
       <c r="DS22">
         <v>9988776655</v>
@@ -10816,7 +10889,7 @@
         <v>4060004321</v>
       </c>
       <c r="DV22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="DW22" t="s">
         <v>96</v>
@@ -10838,6 +10911,9 @@
       </c>
       <c r="EC22">
         <v>156</v>
+      </c>
+      <c r="ED22" t="s">
+        <v>691</v>
       </c>
     </row>
   </sheetData>
